--- a/cv_zmm.xlsx
+++ b/cv_zmm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wcs1-my.sharepoint.com/personal/zmoore_wcs_org/Documents/Data/r projects/zacharymilosmoore.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="14_{08B98A92-493A-4C26-8167-4BB5471433C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C64E11A-2672-462E-B44C-09BD93913F0D}"/>
+  <xr:revisionPtr revIDLastSave="579" documentId="14_{08B98A92-493A-4C26-8167-4BB5471433C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E980225-29A6-4FB7-84AE-211EF1DB5A99}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{4154936E-D054-4D45-B3AE-FD317E846EC6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4154936E-D054-4D45-B3AE-FD317E846EC6}"/>
   </bookViews>
   <sheets>
     <sheet name="CV" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,9 @@
     <definedName name="Volunteering">lists.table[Volunteering]</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="21" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -53,8 +56,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={4561C0B0-076A-4881-B63D-B1744702D4A7}</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{4561C0B0-076A-4881-B63D-B1744702D4A7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Could link to CV items and extract date, but could also link items to a list of skills...</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="688">
   <si>
     <t>Category</t>
   </si>
@@ -1976,21 +1997,170 @@
     <t>Website Developer</t>
   </si>
   <si>
-    <t>www.mooremanordesigns.com</t>
-  </si>
-  <si>
     <t>Moore Manor Designs Website</t>
   </si>
   <si>
     <t>Designed simple website for local artist (and family member)</t>
+  </si>
+  <si>
+    <t>https://mooremanordesigns.com/</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>Shiny</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>Microsoft SQL Server</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Experience (Years)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>R Markdown</t>
+  </si>
+  <si>
+    <t>ArcGIS Pro</t>
+  </si>
+  <si>
+    <t>Tabular Data</t>
+  </si>
+  <si>
+    <t>Spatial Data</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>Personal Projects</t>
+  </si>
+  <si>
+    <t>Pages &amp; Website Development</t>
+  </si>
+  <si>
+    <t>Organizational Projects</t>
+  </si>
+  <si>
+    <t>Basic Excel</t>
+  </si>
+  <si>
+    <t>Basic Word</t>
+  </si>
+  <si>
+    <t>CV_List</t>
+  </si>
+  <si>
+    <t>Personal Website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Designed personal CV website using GitHub Pages and R Markdown. </t>
+  </si>
+  <si>
+    <t>https://zacharymilosmoore.ca/</t>
+  </si>
+  <si>
+    <t>Zachary Milos Moore Personal Website</t>
+  </si>
+  <si>
+    <t>MS Office</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>GIS</t>
+  </si>
+  <si>
+    <t>PostgreSQL</t>
+  </si>
+  <si>
+    <t>MySQL</t>
+  </si>
+  <si>
+    <t>Database Design</t>
+  </si>
+  <si>
+    <t>Mail Merge</t>
+  </si>
+  <si>
+    <t>Power Query</t>
+  </si>
+  <si>
+    <t>Power BI</t>
+  </si>
+  <si>
+    <t>QGIS</t>
+  </si>
+  <si>
+    <t>Avenza (Survey Design)</t>
+  </si>
+  <si>
+    <t>ESRI Field Maps (Survey Design)</t>
+  </si>
+  <si>
+    <t>Survey123 (Survey Design)</t>
+  </si>
+  <si>
+    <t>QField (Survey Design)</t>
+  </si>
+  <si>
+    <t>Power Pivot</t>
+  </si>
+  <si>
+    <t>VBA (Macros)</t>
+  </si>
+  <si>
+    <t>Expert</t>
+  </si>
+  <si>
+    <t>ArcGIS Toolbox Development</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Learning</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>Self-identified Level</t>
+  </si>
+  <si>
+    <t>Database Management</t>
+  </si>
+  <si>
+    <t>Database Maintenance</t>
+  </si>
+  <si>
+    <t>Years of Professional Exposure</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -2182,7 +2352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2276,32 +2446,31 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="66">
     <dxf>
       <font>
         <b/>
         <i val="0"/>
       </font>
-      <numFmt numFmtId="165" formatCode="&quot;Present&quot;"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="&quot;Present&quot;"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="&quot;Present&quot;"/>
+      <numFmt numFmtId="167" formatCode="&quot;Present&quot;"/>
     </dxf>
     <dxf>
       <fill>
@@ -2803,6 +2972,22 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Tw Cen MT"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3593,6 +3778,12 @@
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="yyyy"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3606,85 +3797,1760 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[cv_zmm.xlsx]Skills!PivotTable1</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Skills!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Skills!$G$2:$G$35</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="27"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Basic Word</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Basic Excel</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Mail Merge</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Power Pivot</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>VBA (Macros)</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Power Query</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Power BI</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>ArcGIS Pro</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Avenza (Survey Design)</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>QGIS</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ESRI Field Maps (Survey Design)</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>QField (Survey Design)</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Survey123 (Survey Design)</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Tabular Data</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>Spatial Data</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>R Markdown</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>Shiny</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>Personal Projects</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>Pages &amp; Website Development</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>Organizational Projects</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>Database Design</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>PostgreSQL</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>Microsoft SQL Server</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>Database Management</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>Database Maintenance</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>MySQL</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>ArcGIS Toolbox Development</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>MS Office</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>GIS</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>R</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>GitHub</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>SQL</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>Python</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Skills!$H$2:$H$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>12.799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.79999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.79999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11.1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-78E3-4244-8382-0D6F7E73C5DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1923927472"/>
+        <c:axId val="1923926992"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1923927472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1923926992"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1923926992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-CA"/>
+                  <a:t>Years of Experience</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1923927472"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>65314</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>60414</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>446314</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>54427</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{991B9AD5-6B12-04F0-55AB-E6D398321AC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Moore, Zachary" id="{1133B71F-68C0-40D2-9664-A8D8B7789B1E}" userId="S::zmoore@wcs.org::9d0c74f4-275e-4d53-a190-4bcf987eaaa0" providerId="AD"/>
+</personList>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Moore, Zachary" refreshedDate="46188.488545717591" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="27" xr:uid="{F6ED3B8B-1A78-4223-A864-14D164002041}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table2"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="16">
+        <s v="GIS"/>
+        <s v="GitHub"/>
+        <s v="MS Office"/>
+        <s v="Python"/>
+        <s v="R"/>
+        <s v="SQL"/>
+        <s v="Biology" u="1"/>
+        <s v="Geographic Information Systems (GIS)" u="1"/>
+        <s v="Databases" u="1"/>
+        <s v="Microsoft Office" u="1"/>
+        <s v="R Programming" u="1"/>
+        <s v="Structured Query Language (SQL)" u="1"/>
+        <s v="ArcGIS" u="1"/>
+        <s v="Microsoft Excel" u="1"/>
+        <s v="Microsoft Word" u="1"/>
+        <s v="Excel" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Skill" numFmtId="0">
+      <sharedItems containsBlank="1" count="38">
+        <s v="ArcGIS Pro"/>
+        <s v="QGIS"/>
+        <s v="ESRI Field Maps (Survey Design)"/>
+        <s v="Survey123 (Survey Design)"/>
+        <s v="Avenza (Survey Design)"/>
+        <s v="QField (Survey Design)"/>
+        <s v="Personal Projects"/>
+        <s v="Pages &amp; Website Development"/>
+        <s v="Organizational Projects"/>
+        <s v="Basic Excel"/>
+        <s v="Basic Word"/>
+        <s v="Mail Merge"/>
+        <s v="Power Query"/>
+        <s v="Power BI"/>
+        <s v="Power Pivot"/>
+        <s v="VBA (Macros)"/>
+        <s v="ArcGIS Toolbox Development"/>
+        <s v="Tabular Data"/>
+        <s v="Spatial Data"/>
+        <s v="R Markdown"/>
+        <s v="Shiny"/>
+        <s v="Microsoft SQL Server"/>
+        <s v="PostgreSQL"/>
+        <s v="MySQL"/>
+        <s v="Database Design"/>
+        <s v="Database Management"/>
+        <s v="Database Maintenance"/>
+        <s v="Conservation" u="1"/>
+        <s v="Ecological Research" u="1"/>
+        <m u="1"/>
+        <s v="Power Pivot (Excel)" u="1"/>
+        <s v="ESRI Field Maps" u="1"/>
+        <s v="Avenza" u="1"/>
+        <s v="Google Earth" u="1"/>
+        <s v="Basic Usage" u="1"/>
+        <s v="Basic Data Manipulation &amp; Analysis" u="1"/>
+        <s v="Tabular Data Manipulation &amp; Analysis" u="1"/>
+        <s v="Spatial Data Analysis &amp; Visualization" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Self-identified Level" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Start" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2013-09-01T00:00:00" maxDate="2026-01-02T00:00:00"/>
+    </cacheField>
+    <cacheField name="Years of Experience" numFmtId="166">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.5" maxValue="12.799999999999999"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="27">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Expert"/>
+    <d v="2018-09-01T00:00:00"/>
+    <n v="7.8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Instructor"/>
+    <d v="2019-10-01T00:00:00"/>
+    <n v="6.8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Instructor"/>
+    <d v="2020-09-01T00:00:00"/>
+    <n v="5.8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Intermediate"/>
+    <d v="2025-09-01T00:00:00"/>
+    <n v="0.79999999999999993"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Intermediate"/>
+    <d v="2019-10-01T00:00:00"/>
+    <n v="6.8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="Learning"/>
+    <d v="2025-09-01T00:00:00"/>
+    <n v="0.79999999999999993"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <s v="Intermediate"/>
+    <d v="2020-09-01T00:00:00"/>
+    <n v="5.8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <s v="Advanced"/>
+    <d v="2021-01-01T00:00:00"/>
+    <n v="5.5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <s v="Intermediate"/>
+    <d v="2022-01-01T00:00:00"/>
+    <n v="4.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <s v="Instructor"/>
+    <d v="2013-09-01T00:00:00"/>
+    <n v="12.799999999999999"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <s v="Instructor"/>
+    <d v="2013-09-01T00:00:00"/>
+    <n v="12.799999999999999"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <s v="Intermediate"/>
+    <d v="2021-01-01T00:00:00"/>
+    <n v="5.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="12"/>
+    <s v="Instructor"/>
+    <d v="2024-01-01T00:00:00"/>
+    <n v="2.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="13"/>
+    <s v="Learning"/>
+    <d v="2026-01-01T00:00:00"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="14"/>
+    <s v="Intermediate"/>
+    <d v="2024-01-01T00:00:00"/>
+    <n v="2.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="15"/>
+    <s v="Learning"/>
+    <d v="2024-01-01T00:00:00"/>
+    <n v="2.5"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="16"/>
+    <s v="Learning"/>
+    <d v="2026-01-01T00:00:00"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="17"/>
+    <s v="Instructor"/>
+    <d v="2015-06-01T00:00:00"/>
+    <n v="11.1"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="18"/>
+    <s v="Instructor"/>
+    <d v="2020-09-01T00:00:00"/>
+    <n v="5.8"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="19"/>
+    <s v="Advanced"/>
+    <d v="2022-01-01T00:00:00"/>
+    <n v="4.5"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="20"/>
+    <s v="Learning"/>
+    <d v="2025-01-01T00:00:00"/>
+    <n v="1.5"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="21"/>
+    <s v="Instructor"/>
+    <d v="2024-01-01T00:00:00"/>
+    <n v="2.5"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="22"/>
+    <s v="Intermediate"/>
+    <d v="2023-01-01T00:00:00"/>
+    <n v="3.5"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="23"/>
+    <s v="Learning"/>
+    <d v="2026-01-01T00:00:00"/>
+    <n v="0.5"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="24"/>
+    <s v="Instructor"/>
+    <d v="2022-01-01T00:00:00"/>
+    <n v="4.5"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="25"/>
+    <s v="Intermediate"/>
+    <d v="2025-01-01T00:00:00"/>
+    <n v="1.5"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="26"/>
+    <s v="Intermediate"/>
+    <d v="2025-01-01T00:00:00"/>
+    <n v="1.5"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D2C8C371-0CF2-4E47-B790-EF157E0D2441}" name="PivotTable1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Categories">
+  <location ref="G1:H35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="17">
+        <item m="1" x="8"/>
+        <item m="1" x="15"/>
+        <item m="1" x="7"/>
+        <item m="1" x="10"/>
+        <item m="1" x="13"/>
+        <item m="1" x="12"/>
+        <item m="1" x="14"/>
+        <item x="1"/>
+        <item m="1" x="9"/>
+        <item m="1" x="11"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item m="1" x="6"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="39">
+        <item m="1" x="35"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item m="1" x="37"/>
+        <item m="1" x="36"/>
+        <item m="1" x="29"/>
+        <item x="0"/>
+        <item x="19"/>
+        <item m="1" x="34"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item m="1" x="31"/>
+        <item m="1" x="32"/>
+        <item m="1" x="33"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item m="1" x="30"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item m="1" x="27"/>
+        <item m="1" x="28"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="2" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="34">
+    <i>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="28"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="36"/>
+    </i>
+    <i r="1">
+      <x v="37"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Experience (Years)" fld="4" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E6C429B5-94AF-4DF8-8EEB-230783D5C112}" name="cv.table" displayName="cv.table" ref="A1:AM91" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
-  <autoFilter ref="A1:AM91" xr:uid="{51C5574A-10F4-4984-BAF7-4488D8AC8419}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AM91">
-    <sortCondition ref="I1:I91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E6C429B5-94AF-4DF8-8EEB-230783D5C112}" name="cv.table" displayName="cv.table" ref="A1:AN92" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="A1:AN92" xr:uid="{51C5574A-10F4-4984-BAF7-4488D8AC8419}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AM92">
+    <sortCondition ref="I1:I92"/>
   </sortState>
-  <tableColumns count="39">
-    <tableColumn id="7" xr3:uid="{EC86C6DE-554D-4F33-AEC2-DF6E1CA6068F}" name="Organization" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{26CD9B61-38AB-4312-B98A-E2A336BF9AB7}" name="Org_Acr" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{2BE7F400-F53C-40A9-BB7D-530918FE5571}" name="Title" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{33E88F9D-A2A0-44DD-84D2-308042D95210}" name="Title_Acr" dataDxfId="59"/>
-    <tableColumn id="26" xr3:uid="{9B11C92F-E956-4444-BEFF-953F753416F5}" name="CV" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{34502BA5-FB1E-4B40-8788-421DADDD3E97}" name="Branch" dataDxfId="57"/>
-    <tableColumn id="1" xr3:uid="{70612BCC-1448-430F-9D24-28D063F5A2A3}" name="Category" dataDxfId="56"/>
-    <tableColumn id="18" xr3:uid="{5E4EDA0C-2B9B-42CE-A32B-4403948C8E7B}" name="Type" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{6738E286-0938-42F9-B68F-D49892936B3D}" name="Start" dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{F83278BD-725D-4108-95A1-F217E27DC898}" name="End" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{802621DE-7866-4555-8E12-DD03949FA7E7}" name="Start_Month" dataDxfId="52">
+  <tableColumns count="40">
+    <tableColumn id="7" xr3:uid="{EC86C6DE-554D-4F33-AEC2-DF6E1CA6068F}" name="Organization" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{26CD9B61-38AB-4312-B98A-E2A336BF9AB7}" name="Org_Acr" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{2BE7F400-F53C-40A9-BB7D-530918FE5571}" name="Title" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{33E88F9D-A2A0-44DD-84D2-308042D95210}" name="Title_Acr" dataDxfId="58"/>
+    <tableColumn id="26" xr3:uid="{9B11C92F-E956-4444-BEFF-953F753416F5}" name="CV" dataDxfId="57"/>
+    <tableColumn id="11" xr3:uid="{34502BA5-FB1E-4B40-8788-421DADDD3E97}" name="Branch" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{70612BCC-1448-430F-9D24-28D063F5A2A3}" name="Category" dataDxfId="55"/>
+    <tableColumn id="18" xr3:uid="{5E4EDA0C-2B9B-42CE-A32B-4403948C8E7B}" name="Type" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{6738E286-0938-42F9-B68F-D49892936B3D}" name="Start" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{F83278BD-725D-4108-95A1-F217E27DC898}" name="End" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{802621DE-7866-4555-8E12-DD03949FA7E7}" name="Start_Month" dataDxfId="51">
       <calculatedColumnFormula>MONTH(cv.table[[#This Row],[Start]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{C6566D99-33F8-4C29-9F77-57CB96E0A79F}" name="Start_Year" dataDxfId="51">
+    <tableColumn id="20" xr3:uid="{C6566D99-33F8-4C29-9F77-57CB96E0A79F}" name="Start_Year" dataDxfId="50">
       <calculatedColumnFormula>YEAR(cv.table[[#This Row],[Start]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{6BF152A0-7851-42D9-985D-3CC266F2660D}" name="End_Month" dataDxfId="50">
+    <tableColumn id="22" xr3:uid="{6BF152A0-7851-42D9-985D-3CC266F2660D}" name="End_Month" dataDxfId="49">
       <calculatedColumnFormula>MONTH(cv.table[[#This Row],[End]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{FEEC95E2-B833-448E-AC76-6DBAE4E45591}" name="End_Year" dataDxfId="49">
+    <tableColumn id="21" xr3:uid="{FEEC95E2-B833-448E-AC76-6DBAE4E45591}" name="End_Year" dataDxfId="48">
       <calculatedColumnFormula>YEAR(cv.table[[#This Row],[End]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7BB222DF-5EE2-4BC9-9EF1-E1A53AFE31F4}" name="Time" dataDxfId="48">
+    <tableColumn id="5" xr3:uid="{7BB222DF-5EE2-4BC9-9EF1-E1A53AFE31F4}" name="Time" dataDxfId="47">
       <calculatedColumnFormula>IF((P2="Days"),((J2-I2+1)),IF(P2="Months",((J2-I2)/30),((J2-I2)/365)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{436D180E-D520-4622-BF48-C117C2F3D72D}" name="Time_Unit" dataDxfId="47"/>
-    <tableColumn id="14" xr3:uid="{0AC0D461-4004-4A64-B5A7-5BCBB135C7C9}" name="Loc_Small" dataDxfId="46"/>
-    <tableColumn id="15" xr3:uid="{604F7BAB-42A3-455E-8C18-202B68AEBC37}" name="Loc_Large" dataDxfId="45"/>
-    <tableColumn id="12" xr3:uid="{1CAEFFF7-88CF-4AB8-88EF-1DC65D78A14C}" name="Description" dataDxfId="44"/>
-    <tableColumn id="19" xr3:uid="{B4A2DCCB-9505-42D1-97AE-1B44581F30F1}" name="Tasks" dataDxfId="43"/>
-    <tableColumn id="16" xr3:uid="{9AA8F708-1C30-48AB-8EDD-8C5BF442D6ED}" name="Lessons" dataDxfId="42"/>
-    <tableColumn id="17" xr3:uid="{CAB8C078-3C62-4846-9AC3-0B17AD693416}" name="Achievements" dataDxfId="41"/>
-    <tableColumn id="13" xr3:uid="{982B9A83-407B-47DD-AE12-B9AF5B9B6C73}" name="Notes" dataDxfId="40"/>
-    <tableColumn id="23" xr3:uid="{4C96C715-152C-4914-BB38-FEFF25E58297}" name="M1" dataDxfId="39"/>
-    <tableColumn id="31" xr3:uid="{ABB7B8F1-D658-471C-B518-50B31EDEA024}" name="M1_Type" dataDxfId="38"/>
-    <tableColumn id="25" xr3:uid="{AB48772A-9139-4A74-BF34-9532AF007D28}" name="M1_Desc" dataDxfId="37"/>
-    <tableColumn id="27" xr3:uid="{AA368EEC-19E0-4A9A-90A5-B309B7AE3A50}" name="M2" dataDxfId="36"/>
-    <tableColumn id="39" xr3:uid="{CDFAF1DD-71C7-4BE5-985F-753C0AC61716}" name="M2_Type" dataDxfId="35"/>
-    <tableColumn id="28" xr3:uid="{65DF71FF-E9EE-4AAB-A467-1B0F813F20A6}" name="M2_Desc" dataDxfId="34"/>
-    <tableColumn id="29" xr3:uid="{C2677FEE-8349-4A02-B596-66E45AD44952}" name="M3" dataDxfId="33"/>
-    <tableColumn id="38" xr3:uid="{70C3692F-FB1A-483A-8240-B37C7497B7B9}" name="M3_Type" dataDxfId="32"/>
-    <tableColumn id="30" xr3:uid="{1E758BB4-3C89-4653-80DA-C549531B5244}" name="M3_Desc" dataDxfId="31"/>
-    <tableColumn id="32" xr3:uid="{FEE44D7E-69A0-4B71-AB66-1461C45267FF}" name="L1" dataDxfId="30"/>
-    <tableColumn id="33" xr3:uid="{21C268AA-32E8-4627-82E0-7A62468157B5}" name="L1_Desc" dataDxfId="29"/>
-    <tableColumn id="34" xr3:uid="{E85C2701-53A9-4B93-B733-9B7CD3138938}" name="L2" dataDxfId="28"/>
-    <tableColumn id="35" xr3:uid="{8E33C990-20D6-41EA-81EB-AF8C09425D76}" name="L2_Desc" dataDxfId="27"/>
-    <tableColumn id="36" xr3:uid="{FF798E68-0DB4-421A-AE12-25569247C412}" name="L3" dataDxfId="26"/>
-    <tableColumn id="37" xr3:uid="{BF4D3938-CF08-433F-8B81-A515F3E1BBB7}" name="L3_Desc" dataDxfId="25"/>
-    <tableColumn id="40" xr3:uid="{253CE8A7-249E-41AF-AF8F-0BF5333B36DA}" name="Org_Link" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{436D180E-D520-4622-BF48-C117C2F3D72D}" name="Time_Unit" dataDxfId="46"/>
+    <tableColumn id="14" xr3:uid="{0AC0D461-4004-4A64-B5A7-5BCBB135C7C9}" name="Loc_Small" dataDxfId="45"/>
+    <tableColumn id="15" xr3:uid="{604F7BAB-42A3-455E-8C18-202B68AEBC37}" name="Loc_Large" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{1CAEFFF7-88CF-4AB8-88EF-1DC65D78A14C}" name="Description" dataDxfId="43"/>
+    <tableColumn id="19" xr3:uid="{B4A2DCCB-9505-42D1-97AE-1B44581F30F1}" name="Tasks" dataDxfId="42"/>
+    <tableColumn id="16" xr3:uid="{9AA8F708-1C30-48AB-8EDD-8C5BF442D6ED}" name="Lessons" dataDxfId="41"/>
+    <tableColumn id="17" xr3:uid="{CAB8C078-3C62-4846-9AC3-0B17AD693416}" name="Achievements" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{982B9A83-407B-47DD-AE12-B9AF5B9B6C73}" name="Notes" dataDxfId="39"/>
+    <tableColumn id="23" xr3:uid="{4C96C715-152C-4914-BB38-FEFF25E58297}" name="M1" dataDxfId="38"/>
+    <tableColumn id="31" xr3:uid="{ABB7B8F1-D658-471C-B518-50B31EDEA024}" name="M1_Type" dataDxfId="37"/>
+    <tableColumn id="25" xr3:uid="{AB48772A-9139-4A74-BF34-9532AF007D28}" name="M1_Desc" dataDxfId="36"/>
+    <tableColumn id="27" xr3:uid="{AA368EEC-19E0-4A9A-90A5-B309B7AE3A50}" name="M2" dataDxfId="35"/>
+    <tableColumn id="39" xr3:uid="{CDFAF1DD-71C7-4BE5-985F-753C0AC61716}" name="M2_Type" dataDxfId="34"/>
+    <tableColumn id="28" xr3:uid="{65DF71FF-E9EE-4AAB-A467-1B0F813F20A6}" name="M2_Desc" dataDxfId="33"/>
+    <tableColumn id="29" xr3:uid="{C2677FEE-8349-4A02-B596-66E45AD44952}" name="M3" dataDxfId="32"/>
+    <tableColumn id="38" xr3:uid="{70C3692F-FB1A-483A-8240-B37C7497B7B9}" name="M3_Type" dataDxfId="31"/>
+    <tableColumn id="30" xr3:uid="{1E758BB4-3C89-4653-80DA-C549531B5244}" name="M3_Desc" dataDxfId="30"/>
+    <tableColumn id="32" xr3:uid="{FEE44D7E-69A0-4B71-AB66-1461C45267FF}" name="L1" dataDxfId="29"/>
+    <tableColumn id="33" xr3:uid="{21C268AA-32E8-4627-82E0-7A62468157B5}" name="L1_Desc" dataDxfId="28"/>
+    <tableColumn id="34" xr3:uid="{E85C2701-53A9-4B93-B733-9B7CD3138938}" name="L2" dataDxfId="27"/>
+    <tableColumn id="35" xr3:uid="{8E33C990-20D6-41EA-81EB-AF8C09425D76}" name="L2_Desc" dataDxfId="26"/>
+    <tableColumn id="36" xr3:uid="{FF798E68-0DB4-421A-AE12-25569247C412}" name="L3" dataDxfId="25"/>
+    <tableColumn id="37" xr3:uid="{BF4D3938-CF08-433F-8B81-A515F3E1BBB7}" name="L3_Desc" dataDxfId="24"/>
+    <tableColumn id="40" xr3:uid="{253CE8A7-249E-41AF-AF8F-0BF5333B36DA}" name="Org_Link" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{7227EDDE-23E8-491F-9948-DDACA373C3A1}" name="CV_List" dataDxfId="22">
+      <calculatedColumnFormula>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7A7031F1-2203-44EF-8965-9D3E7E6E20C7}" name="lists.table" displayName="lists.table" ref="A1:N12" totalsRowShown="0" headerRowDxfId="23" dataDxfId="21" headerRowBorderDxfId="22" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EA82C731-37AB-4BD9-A9C7-425663939105}" name="Table2" displayName="Table2" ref="A1:E28" totalsRowShown="0">
+  <autoFilter ref="A1:E28" xr:uid="{EA82C731-37AB-4BD9-A9C7-425663939105}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E26">
+    <sortCondition ref="A1:A26"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{DDB5D190-EAF5-4053-B13F-BF9B72D0EA69}" name="Category"/>
+    <tableColumn id="2" xr3:uid="{2523D3CF-788F-45BB-B72F-086EF71557AB}" name="Skill"/>
+    <tableColumn id="8" xr3:uid="{B9516D00-F602-459E-9ACF-C72D7D50B6E6}" name="Self-identified Level"/>
+    <tableColumn id="3" xr3:uid="{7E897B0B-F15B-4405-9756-3C2BCA461366}" name="Start" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{D69837BC-B8F5-4FBC-AA68-E8F2B0D0C8D5}" name="Years of Professional Exposure" dataDxfId="64">
+      <calculatedColumnFormula>ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7A7031F1-2203-44EF-8965-9D3E7E6E20C7}" name="lists.table" displayName="lists.table" ref="A1:N12" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="A1:N12" xr:uid="{F02DA2C5-59F4-4989-BB36-1611149FB962}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{308CFDE8-BE03-456B-84E3-E26E079B0F80}" name="Branch" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{4D4C6EDC-3308-4CFE-89F0-A12C8F5152D6}" name="Category" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{F8982A44-14CE-484F-B8CB-BB3EC9A5ED07}" name="Accreditations" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{6D21A9C5-BEA7-476E-A983-243C0B9BEC34}" name="Awards" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{C1A44E26-D96B-4ADC-A0DE-C7DE9818C883}" name="Certifications" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{5878EC92-DA44-448C-8DFE-354AB46F1B50}" name="Conferences" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{B8C94F22-10CD-4485-A36C-EF94EFB8544F}" name="Education" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{36320B06-26D8-4E21-A082-28EFC253ECC4}" name="Employment" dataDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{B8A7732C-558E-473D-8687-D8C49EC103D8}" name="Media" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{EF5D7AD2-86C4-4842-A36A-B12726CEFC56}" name="Memberships" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{99E16863-6982-4C99-8470-DD986AA46E8E}" name="Publications" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{F05A780B-4496-4C27-9705-F129B2480E2D}" name="Projects" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{8FF5F1B6-1539-487D-A296-90D274FBA601}" name="Volunteering" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{932C090C-7AD8-4B1D-90AE-36BA3B8B76F8}" name="Application.Stage" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{308CFDE8-BE03-456B-84E3-E26E079B0F80}" name="Branch" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{4D4C6EDC-3308-4CFE-89F0-A12C8F5152D6}" name="Category" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{F8982A44-14CE-484F-B8CB-BB3EC9A5ED07}" name="Accreditations" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{6D21A9C5-BEA7-476E-A983-243C0B9BEC34}" name="Awards" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{C1A44E26-D96B-4ADC-A0DE-C7DE9818C883}" name="Certifications" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{5878EC92-DA44-448C-8DFE-354AB46F1B50}" name="Conferences" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{B8C94F22-10CD-4485-A36C-EF94EFB8544F}" name="Education" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{36320B06-26D8-4E21-A082-28EFC253ECC4}" name="Employment" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{B8A7732C-558E-473D-8687-D8C49EC103D8}" name="Media" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{EF5D7AD2-86C4-4842-A36A-B12726CEFC56}" name="Memberships" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{99E16863-6982-4C99-8470-DD986AA46E8E}" name="Publications" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{F05A780B-4496-4C27-9705-F129B2480E2D}" name="Projects" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{8FF5F1B6-1539-487D-A296-90D274FBA601}" name="Volunteering" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{932C090C-7AD8-4B1D-90AE-36BA3B8B76F8}" name="Application.Stage" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3985,10 +5851,18 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D1" dT="2026-06-15T13:41:31.49" personId="{1133B71F-68C0-40D2-9664-A8D8B7789B1E}" id="{4561C0B0-076A-4881-B63D-B1744702D4A7}">
+    <text>Could link to CV items and extract date, but could also link items to a list of skills...</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6961E3D5-6E55-490E-8BC2-FDE92C6153D9}">
-  <dimension ref="A1:AT91"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AN92"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.33203125" style="31" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" style="31" bestFit="1" customWidth="1"/>
@@ -4024,16 +5898,16 @@
     <col min="36" max="37" width="18.5546875" customWidth="1"/>
     <col min="38" max="38" width="18.5546875" style="1" customWidth="1"/>
     <col min="39" max="39" width="26.6640625" customWidth="1"/>
-    <col min="40" max="40" width="25" style="1" hidden="1" customWidth="1"/>
-    <col min="41" max="41" width="8.44140625" style="1" hidden="1" customWidth="1"/>
-    <col min="42" max="42" width="27.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="21.33203125" style="1" hidden="1" customWidth="1"/>
-    <col min="44" max="44" width="8.33203125" style="1" hidden="1" customWidth="1"/>
-    <col min="45" max="46" width="26.109375" style="1" hidden="1" customWidth="1"/>
-    <col min="47" max="16384" width="8.44140625" style="1" hidden="1"/>
+    <col min="40" max="40" width="25" style="1" customWidth="1"/>
+    <col min="41" max="41" width="8.44140625" style="1" customWidth="1"/>
+    <col min="42" max="42" width="27.77734375" style="1" customWidth="1"/>
+    <col min="43" max="43" width="21.33203125" style="1" customWidth="1"/>
+    <col min="44" max="44" width="8.33203125" style="1" customWidth="1"/>
+    <col min="45" max="46" width="26.109375" style="1" customWidth="1"/>
+    <col min="47" max="16384" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -4151,8 +6025,11 @@
       <c r="AM1" s="3" t="s">
         <v>288</v>
       </c>
+      <c r="AN1" s="2" t="s">
+        <v>657</v>
+      </c>
     </row>
-    <row r="2" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>70</v>
       </c>
@@ -4235,8 +6112,12 @@
       <c r="AK2" s="17"/>
       <c r="AL2" s="24"/>
       <c r="AM2" s="18"/>
+      <c r="AN2" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Line Kitchen Staff (Various Restaurants)</v>
+      </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>68</v>
       </c>
@@ -4315,8 +6196,12 @@
       <c r="AK3" s="17"/>
       <c r="AL3" s="24"/>
       <c r="AM3" s="18"/>
+      <c r="AN3" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>General Labourer (DMA Contracting)</v>
+      </c>
     </row>
-    <row r="4" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>132</v>
       </c>
@@ -4397,8 +6282,12 @@
       <c r="AM4" s="26" t="s">
         <v>334</v>
       </c>
+      <c r="AN4" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Defensive Driving Course (Young Driver's of Canada)</v>
+      </c>
     </row>
-    <row r="5" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>440</v>
       </c>
@@ -4424,7 +6313,7 @@
       </c>
       <c r="J5" s="22">
         <f ca="1">NOW()</f>
-        <v>46187.657905439817</v>
+        <v>46188.50092766204</v>
       </c>
       <c r="K5" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -4444,7 +6333,7 @@
       </c>
       <c r="O5" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>13.963446316273471</v>
+        <v>13.965755966197371</v>
       </c>
       <c r="P5" s="17" t="s">
         <v>28</v>
@@ -4478,8 +6367,12 @@
       <c r="AM5" s="26" t="s">
         <v>338</v>
       </c>
+      <c r="AN5" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Ontario G-Class Driver's Licence (Ontario Ministry of Transportation)</v>
+      </c>
     </row>
-    <row r="6" spans="1:39" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>66</v>
       </c>
@@ -4568,8 +6461,12 @@
       <c r="AK6" s="17"/>
       <c r="AL6" s="24"/>
       <c r="AM6" s="17"/>
+      <c r="AN6" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Service Technician/ Health and Safety Inspector (MBM Installations Inc.)</v>
+      </c>
     </row>
-    <row r="7" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>7</v>
       </c>
@@ -4660,8 +6557,12 @@
       <c r="AM7" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN7" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Honour's Bachelor of Arts and Science (University of Toronto)</v>
+      </c>
     </row>
-    <row r="8" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>7</v>
       </c>
@@ -4744,8 +6645,12 @@
       <c r="AM8" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN8" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Research Assistant (Agrawal Lab) (University of Toronto)</v>
+      </c>
     </row>
-    <row r="9" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>7</v>
       </c>
@@ -4834,8 +6739,12 @@
       <c r="AM9" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN9" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Scientific Researcher: Population and Community Ecology (University of Toronto)</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>7</v>
       </c>
@@ -4950,8 +6859,12 @@
       <c r="AM10" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN10" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Daphnia Fishery: Experimental Population Destabilization from Harvesting (University of Toronto)</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>7</v>
       </c>
@@ -5034,8 +6947,12 @@
       <c r="AM11" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN11" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Laboratory Biosafety (University of Toronto)</v>
+      </c>
     </row>
-    <row r="12" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>96</v>
       </c>
@@ -5118,8 +7035,12 @@
       <c r="AM12" s="26" t="s">
         <v>331</v>
       </c>
+      <c r="AN12" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Senior Demonstrator (Scihigh - Lunenfield Research Institute)</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>127</v>
       </c>
@@ -5198,8 +7119,12 @@
       <c r="AM13" s="26" t="s">
         <v>337</v>
       </c>
+      <c r="AN13" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Ontario Working at Heights (Ontario Ministry of Labour)</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>7</v>
       </c>
@@ -5284,8 +7209,12 @@
       <c r="AM14" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN14" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Natural Science and Engineering Research Council Undergraduate Student Research Award Recipient (University of Toronto)</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>285</v>
       </c>
@@ -5370,8 +7299,12 @@
       <c r="AM15" s="26" t="s">
         <v>321</v>
       </c>
+      <c r="AN15" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Undergraduate Student Research Award (Natural Sciences and Engineering Research Council )</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>101</v>
       </c>
@@ -5462,8 +7395,12 @@
       <c r="AM16" s="26" t="s">
         <v>316</v>
       </c>
+      <c r="AN16" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>2016 Conference (Ontario Ecology, Ethology and Evolution Conference)</v>
+      </c>
     </row>
-    <row r="17" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>7</v>
       </c>
@@ -5554,8 +7491,12 @@
       <c r="AM17" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN17" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>2016 Undergraduate Student Research Fair (University of Toronto)</v>
+      </c>
     </row>
-    <row r="18" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>275</v>
       </c>
@@ -5648,8 +7589,12 @@
       <c r="AM18" s="26" t="s">
         <v>333</v>
       </c>
+      <c r="AN18" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Turf Wars: Understory Turf Transplant Success (Laurentian University)</v>
+      </c>
     </row>
-    <row r="19" spans="1:39" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:40" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>7</v>
       </c>
@@ -5760,8 +7705,12 @@
       <c r="AM19" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN19" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Aphid Farm: Tritrophic Community Interactions (University of Toronto)</v>
+      </c>
     </row>
-    <row r="20" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>7</v>
       </c>
@@ -5848,8 +7797,12 @@
       <c r="AM20" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN20" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>UofT MedStores Staff (University of Toronto)</v>
+      </c>
     </row>
-    <row r="21" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>7</v>
       </c>
@@ -5942,8 +7895,12 @@
       <c r="AM21" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN21" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>2017 Undergraduate Student Research Fair  (University of Toronto)</v>
+      </c>
     </row>
-    <row r="22" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>7</v>
       </c>
@@ -6028,8 +7985,12 @@
       <c r="AM22" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN22" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Koffler Science Reserve Undergraduate Student Research Award Recipient (University of Toronto)</v>
+      </c>
     </row>
-    <row r="23" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>283</v>
       </c>
@@ -6114,8 +8075,12 @@
       <c r="AM23" s="26" t="s">
         <v>320</v>
       </c>
+      <c r="AN23" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Undergraduate Student Research Award (Koffler Scientific Reserve)</v>
+      </c>
     </row>
-    <row r="24" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>7</v>
       </c>
@@ -6198,8 +8163,12 @@
       <c r="AM24" s="26" t="s">
         <v>306</v>
       </c>
+      <c r="AN24" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Research Technician (Gilbert Lab) (University of Toronto)</v>
+      </c>
     </row>
-    <row r="25" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>62</v>
       </c>
@@ -6284,8 +8253,12 @@
       <c r="AM25" s="17" t="s">
         <v>446</v>
       </c>
+      <c r="AN25" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Math and Science Instructor (Oxford Learning Centres Inc.)</v>
+      </c>
     </row>
-    <row r="26" spans="1:39" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:40" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
         <v>45</v>
       </c>
@@ -6372,8 +8345,12 @@
       <c r="AM26" s="26" t="s">
         <v>311</v>
       </c>
+      <c r="AN26" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Tree Farm Hand (Earthbound Trees)</v>
+      </c>
     </row>
-    <row r="27" spans="1:39" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:40" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>61</v>
       </c>
@@ -6460,8 +8437,12 @@
       <c r="AM27" s="26" t="s">
         <v>312</v>
       </c>
+      <c r="AN27" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Ecological Program Developer (Earthbound Kids)</v>
+      </c>
     </row>
-    <row r="28" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>6</v>
       </c>
@@ -6544,8 +8525,12 @@
       <c r="AM28" s="26" t="s">
         <v>307</v>
       </c>
+      <c r="AN28" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Niagara River Invasive Species Management (Niagara College)</v>
+      </c>
     </row>
-    <row r="29" spans="1:39" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:40" ht="132" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
         <v>6</v>
       </c>
@@ -6636,8 +8621,12 @@
       <c r="AM29" s="26" t="s">
         <v>307</v>
       </c>
+      <c r="AN29" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Post-Graduate Certificate in Ecosystem Restoration (Niagara College)</v>
+      </c>
     </row>
-    <row r="30" spans="1:39" ht="66" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:40" ht="66" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
         <v>6</v>
       </c>
@@ -6734,8 +8723,12 @@
       <c r="AM30" s="26" t="s">
         <v>307</v>
       </c>
+      <c r="AN30" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Terrestrial Insect Restoration Responses (Niagara College)</v>
+      </c>
     </row>
-    <row r="31" spans="1:39" ht="66" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:40" ht="66" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
         <v>10</v>
       </c>
@@ -6826,8 +8819,12 @@
       <c r="AM31" s="26" t="s">
         <v>327</v>
       </c>
+      <c r="AN31" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Niagara College Student Association Vice President (Society for Ecological Restoration)</v>
+      </c>
     </row>
-    <row r="32" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
         <v>330</v>
       </c>
@@ -6912,8 +8909,12 @@
       <c r="AM32" s="26" t="s">
         <v>329</v>
       </c>
+      <c r="AN32" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>River Corridor Restoration Technician (Conservation Halton)</v>
+      </c>
     </row>
-    <row r="33" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>121</v>
       </c>
@@ -6941,7 +8942,7 @@
       </c>
       <c r="J33" s="22">
         <f ca="1">NOW()</f>
-        <v>46187.657905439817</v>
+        <v>46188.50092766204</v>
       </c>
       <c r="K33" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -6961,7 +8962,7 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>7.7086517957255261</v>
+        <v>7.710961445649426</v>
       </c>
       <c r="P33" s="17" t="s">
         <v>28</v>
@@ -6995,8 +8996,12 @@
       <c r="AM33" s="26" t="s">
         <v>319</v>
       </c>
+      <c r="AN33" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Restricted Operator's Certificate - Aeronautical Communications  (Industry Canada)</v>
+      </c>
     </row>
-    <row r="34" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
         <v>119</v>
       </c>
@@ -7075,8 +9080,12 @@
       <c r="AM34" s="26" t="s">
         <v>303</v>
       </c>
+      <c r="AN34" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Wilderness and Remote First Aid/ CPR &amp; AED C (Canadian Red Cross)</v>
+      </c>
     </row>
-    <row r="35" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
         <v>117</v>
       </c>
@@ -7157,8 +9166,12 @@
       <c r="AM35" s="26" t="s">
         <v>339</v>
       </c>
+      <c r="AN35" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Backpack Electrofishing Crew Lead (Class 2) (Trout Unlimited Canada)</v>
+      </c>
     </row>
-    <row r="36" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
         <v>439</v>
       </c>
@@ -7241,8 +9254,12 @@
       <c r="AM36" s="26" t="s">
         <v>343</v>
       </c>
+      <c r="AN36" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Unmanned Aerial Vehicle Ground School (Waterloo Wellington Flight Centre)</v>
+      </c>
     </row>
-    <row r="37" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
         <v>6</v>
       </c>
@@ -7327,8 +9344,12 @@
       <c r="AM37" s="26" t="s">
         <v>307</v>
       </c>
+      <c r="AN37" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Athletics and Recreation Centre Staff (Niagara College)</v>
+      </c>
     </row>
-    <row r="38" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
         <v>112</v>
       </c>
@@ -7409,8 +9430,12 @@
       <c r="AM38" s="26" t="s">
         <v>315</v>
       </c>
+      <c r="AN38" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Ontario Benthos Biomonitoring Network Participant (Ontario Ministry of Environment, Conservation and Parks)</v>
+      </c>
     </row>
-    <row r="39" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A39" s="18" t="s">
         <v>111</v>
       </c>
@@ -7438,7 +9463,7 @@
       </c>
       <c r="J39" s="22">
         <f ca="1">NOW()</f>
-        <v>46187.657905439817</v>
+        <v>46188.50092766204</v>
       </c>
       <c r="K39" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -7458,7 +9483,7 @@
       </c>
       <c r="O39" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>7.4565970012049787</v>
+        <v>7.4589066511288777</v>
       </c>
       <c r="P39" s="17" t="s">
         <v>28</v>
@@ -7492,8 +9517,12 @@
       <c r="AM39" s="26" t="s">
         <v>318</v>
       </c>
+      <c r="AN39" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Pleasure Craft Operators Card (Transportation Canada)</v>
+      </c>
     </row>
-    <row r="40" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A40" s="18" t="s">
         <v>97</v>
       </c>
@@ -7580,8 +9609,12 @@
       <c r="AM40" s="26" t="s">
         <v>332</v>
       </c>
+      <c r="AN40" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Designing Change for a Living Planet Competition (World Wildlife Fund)</v>
+      </c>
     </row>
-    <row r="41" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A41" s="18" t="s">
         <v>10</v>
       </c>
@@ -7664,8 +9697,12 @@
       <c r="AM41" s="26" t="s">
         <v>317</v>
       </c>
+      <c r="AN41" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Certified Ecological Restoration Practitioner in Training (Society for Ecological Restoration)</v>
+      </c>
     </row>
-    <row r="42" spans="1:39" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A42" s="18" t="s">
         <v>127</v>
       </c>
@@ -7746,8 +9783,12 @@
       <c r="AM42" s="26" t="s">
         <v>340</v>
       </c>
+      <c r="AN42" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Workplace Hazardous Materials Information System (Ontario Ministry of Labour)</v>
+      </c>
     </row>
-    <row r="43" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A43" s="18" t="s">
         <v>33</v>
       </c>
@@ -7828,8 +9869,12 @@
       <c r="AM43" s="26" t="s">
         <v>335</v>
       </c>
+      <c r="AN43" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Ed Gregor Stewardship Day Volunteer (Crownest Conservation Society)</v>
+      </c>
     </row>
-    <row r="44" spans="1:39" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A44" s="18" t="s">
         <v>43</v>
       </c>
@@ -7920,8 +9965,12 @@
       <c r="AM44" s="26" t="s">
         <v>309</v>
       </c>
+      <c r="AN44" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Natural Area Assistant - Waterton (Nature Conservancy Canada)</v>
+      </c>
     </row>
-    <row r="45" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A45" s="18" t="s">
         <v>87</v>
       </c>
@@ -8006,8 +10055,12 @@
       <c r="AM45" s="26" t="s">
         <v>328</v>
       </c>
+      <c r="AN45" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Stewardship Event Volunteer (Castle Crown Wilderness Coalition)</v>
+      </c>
     </row>
-    <row r="46" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A46" s="18" t="s">
         <v>31</v>
       </c>
@@ -8092,8 +10145,12 @@
       <c r="AM46" s="26" t="s">
         <v>323</v>
       </c>
+      <c r="AN46" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Rough Runner Event Volunteer (Wildr)</v>
+      </c>
     </row>
-    <row r="47" spans="1:39" ht="66" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" ht="66" x14ac:dyDescent="0.3">
       <c r="A47" s="18" t="s">
         <v>23</v>
       </c>
@@ -8180,8 +10237,12 @@
       <c r="AM47" s="26" t="s">
         <v>326</v>
       </c>
+      <c r="AN47" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Trail Building and Maintenance Committee Member (Great Divide Trail Association)</v>
+      </c>
     </row>
-    <row r="48" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A48" s="18" t="s">
         <v>79</v>
       </c>
@@ -8264,8 +10325,12 @@
       <c r="AM48" s="26" t="s">
         <v>336</v>
       </c>
+      <c r="AN48" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Annual Field Tour (Southwest Invasive Managers)</v>
+      </c>
     </row>
-    <row r="49" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A49" s="18" t="s">
         <v>136</v>
       </c>
@@ -8346,8 +10411,12 @@
       <c r="AM49" s="26" t="s">
         <v>341</v>
       </c>
+      <c r="AN49" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Alberta Class 5 Driver's Licence (Government of Alberta)</v>
+      </c>
     </row>
-    <row r="50" spans="1:39" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:40" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A50" s="18" t="s">
         <v>485</v>
       </c>
@@ -8436,8 +10505,12 @@
       <c r="AK50" s="17"/>
       <c r="AL50" s="24"/>
       <c r="AM50" s="18"/>
+      <c r="AN50" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Biophysical Inventory (Private Land Owner)</v>
+      </c>
     </row>
-    <row r="51" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A51" s="18" t="s">
         <v>10</v>
       </c>
@@ -8518,8 +10591,12 @@
       <c r="AM51" s="26" t="s">
         <v>325</v>
       </c>
+      <c r="AN51" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Western Canada Chapter Annual General Meeting (Society for Ecological Restoration)</v>
+      </c>
     </row>
-    <row r="52" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A52" s="18" t="s">
         <v>10</v>
       </c>
@@ -8604,8 +10681,12 @@
       <c r="AM52" s="26" t="s">
         <v>325</v>
       </c>
+      <c r="AN52" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Western Canada Chapter Director (Society for Ecological Restoration)</v>
+      </c>
     </row>
-    <row r="53" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A53" s="18" t="s">
         <v>84</v>
       </c>
@@ -8688,8 +10769,12 @@
       <c r="AM53" s="26" t="s">
         <v>324</v>
       </c>
+      <c r="AN53" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>CABIN with STREAM DNA Metabarcoding Sample Collection (Living Lakes Canada)</v>
+      </c>
     </row>
-    <row r="54" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A54" s="18" t="s">
         <v>304</v>
       </c>
@@ -8770,8 +10855,12 @@
       <c r="AM54" s="26" t="s">
         <v>305</v>
       </c>
+      <c r="AN54" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Canadian Aquatic Biomonitoring Network Field Assistant (Canadian Rivers Institute)</v>
+      </c>
     </row>
-    <row r="55" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A55" s="18" t="s">
         <v>164</v>
       </c>
@@ -8852,8 +10941,12 @@
       <c r="AM55" s="26" t="s">
         <v>301</v>
       </c>
+      <c r="AN55" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Board Governance Introduction (Alberta Ministry of Culture, Multiculturalism, and the Status of Women)</v>
+      </c>
     </row>
-    <row r="56" spans="1:39" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:40" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A56" s="18" t="s">
         <v>43</v>
       </c>
@@ -8954,8 +11047,12 @@
       <c r="AM56" s="26" t="s">
         <v>309</v>
       </c>
+      <c r="AN56" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Rangeland and Riparian Health Database (Nature Conservancy Canada)</v>
+      </c>
     </row>
-    <row r="57" spans="1:39" ht="66" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:40" ht="66" x14ac:dyDescent="0.3">
       <c r="A57" s="18" t="s">
         <v>10</v>
       </c>
@@ -9052,8 +11149,12 @@
       <c r="AM57" s="26" t="s">
         <v>325</v>
       </c>
+      <c r="AN57" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Western Canada Restoration Practitioner Survey (Society for Ecological Restoration)</v>
+      </c>
     </row>
-    <row r="58" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A58" s="18" t="s">
         <v>159</v>
       </c>
@@ -9138,8 +11239,12 @@
       <c r="AM58" s="26" t="s">
         <v>342</v>
       </c>
+      <c r="AN58" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Trail Monitor (Mountain Bluebird Trail Conservation Society)</v>
+      </c>
     </row>
-    <row r="59" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A59" s="18" t="s">
         <v>161</v>
       </c>
@@ -9220,8 +11325,12 @@
       <c r="AM59" s="26" t="s">
         <v>300</v>
       </c>
+      <c r="AN59" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Administration Committee Chair (Adaptable Outdoors)</v>
+      </c>
     </row>
-    <row r="60" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
         <v>11</v>
       </c>
@@ -9304,8 +11413,12 @@
       <c r="AM60" s="26" t="s">
         <v>302</v>
       </c>
+      <c r="AN60" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Biologist in Training (Alberta Society for Professional Biologists)</v>
+      </c>
     </row>
-    <row r="61" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
         <v>166</v>
       </c>
@@ -9390,8 +11503,12 @@
       <c r="AM61" s="26" t="s">
         <v>322</v>
       </c>
+      <c r="AN61" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Project Lead - Growing Healthy Food Boxes (Pincher Creek and District Food Centre)</v>
+      </c>
     </row>
-    <row r="62" spans="1:39" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:40" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
         <v>210</v>
       </c>
@@ -9490,8 +11607,12 @@
       <c r="AM62" s="26" t="s">
         <v>346</v>
       </c>
+      <c r="AN62" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Grassland Birds in the Waterton Foothills Parkland (University of Manitoba)</v>
+      </c>
     </row>
-    <row r="63" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A63" s="18" t="s">
         <v>43</v>
       </c>
@@ -9576,8 +11697,12 @@
       <c r="AM63" s="26" t="s">
         <v>309</v>
       </c>
+      <c r="AN63" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Conservation Science Fellowship (Nature Conservancy Canada)</v>
+      </c>
     </row>
-    <row r="64" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A64" s="18" t="s">
         <v>210</v>
       </c>
@@ -9668,8 +11793,12 @@
       <c r="AM64" s="26" t="s">
         <v>346</v>
       </c>
+      <c r="AN64" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Master's of Natural Resources Management (University of Manitoba)</v>
+      </c>
     </row>
-    <row r="65" spans="1:39" ht="72" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:40" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
         <v>43</v>
       </c>
@@ -9756,8 +11885,12 @@
       <c r="AK65" s="17"/>
       <c r="AL65" s="24"/>
       <c r="AM65" s="27"/>
+      <c r="AN65" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>NCC Magazine (Fall 2020) (Nature Conservancy Canada)</v>
+      </c>
     </row>
-    <row r="66" spans="1:39" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:40" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A66" s="18" t="s">
         <v>210</v>
       </c>
@@ -9803,7 +11936,7 @@
         <v>2020</v>
       </c>
       <c r="O66" s="20">
-        <f t="shared" ref="O66:O91" si="2">IF((P66="Days"),((J66-I66+1)),IF(P66="Months",((J66-I66)/30),((J66-I66)/365)))</f>
+        <f t="shared" ref="O66:O92" si="2">IF((P66="Days"),((J66-I66+1)),IF(P66="Months",((J66-I66)/30),((J66-I66)/365)))</f>
         <v>3.0333333333333332</v>
       </c>
       <c r="P66" s="17" t="s">
@@ -9858,8 +11991,12 @@
       <c r="AM66" s="26" t="s">
         <v>346</v>
       </c>
+      <c r="AN66" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Using Google Trends to Predict Park Visitation (University of Manitoba)</v>
+      </c>
     </row>
-    <row r="67" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A67" s="18" t="s">
         <v>589</v>
       </c>
@@ -9942,8 +12079,12 @@
       <c r="AM67" s="27" t="s">
         <v>588</v>
       </c>
+      <c r="AN67" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Data Analyst (Unlock)</v>
+      </c>
     </row>
-    <row r="68" spans="1:39" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:40" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A68" s="18" t="s">
         <v>277</v>
       </c>
@@ -10044,8 +12185,12 @@
       <c r="AM68" s="26" t="s">
         <v>308</v>
       </c>
+      <c r="AN68" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Inventorying Living Heritage Conservation in SK (Heritage Saskatchewan)</v>
+      </c>
     </row>
-    <row r="69" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:40" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="18" t="s">
         <v>10</v>
       </c>
@@ -10134,8 +12279,12 @@
       <c r="AM69" s="27" t="s">
         <v>558</v>
       </c>
+      <c r="AN69" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>2021 9th Annual World Conference (Society for Ecological Restoration)</v>
+      </c>
     </row>
-    <row r="70" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:40" ht="66" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
         <v>441</v>
       </c>
@@ -10220,8 +12369,12 @@
       <c r="AM70" s="26" t="s">
         <v>445</v>
       </c>
+      <c r="AN70" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Restoration Assistant (Niagara Peninsula Conservation Authority)</v>
+      </c>
     </row>
-    <row r="71" spans="1:39" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:40" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A71" s="18" t="s">
         <v>159</v>
       </c>
@@ -10306,8 +12459,12 @@
       <c r="AM71" s="26" t="s">
         <v>342</v>
       </c>
+      <c r="AN71" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Mountain Bluebird Nesting Success in Response to Landscape Structure (Mountain Bluebird Trail Conservation Society)</v>
+      </c>
     </row>
-    <row r="72" spans="1:39" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:40" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A72" s="18" t="s">
         <v>475</v>
       </c>
@@ -10337,7 +12494,7 @@
       </c>
       <c r="J72" s="22">
         <f ca="1">NOW()</f>
-        <v>46187.657905439817</v>
+        <v>46188.50092766204</v>
       </c>
       <c r="K72" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -10357,7 +12514,7 @@
       </c>
       <c r="O72" s="20">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4538572751775813</v>
+        <v>4.4561669251014804</v>
       </c>
       <c r="P72" s="17" t="s">
         <v>28</v>
@@ -10403,8 +12560,12 @@
       <c r="AM72" s="27" t="s">
         <v>600</v>
       </c>
+      <c r="AN72" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Key Biodiversity Area Assessment and Technical Support Coordinator (Wildlife Conservation Society Canada)</v>
+      </c>
     </row>
-    <row r="73" spans="1:39" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:40" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A73" s="18" t="s">
         <v>480</v>
       </c>
@@ -10489,8 +12650,12 @@
       <c r="AM73" s="27" t="s">
         <v>578</v>
       </c>
+      <c r="AN73" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Data Analyst (Blood Tribe Land Management)</v>
+      </c>
     </row>
-    <row r="74" spans="1:39" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:40" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A74" s="18" t="s">
         <v>488</v>
       </c>
@@ -10569,8 +12734,12 @@
       <c r="AK74" s="17"/>
       <c r="AL74" s="24"/>
       <c r="AM74" s="17"/>
+      <c r="AN74" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Experimental evidence of size-selective harvest and environmental stochasticity effects on population demography, fluctuations, and nonlinearity (Ecology Letters)</v>
+      </c>
     </row>
-    <row r="75" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A75" s="18" t="s">
         <v>478</v>
       </c>
@@ -10659,8 +12828,12 @@
       <c r="AM75" s="27" t="s">
         <v>555</v>
       </c>
+      <c r="AN75" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>2023 Annual Conference: Birds as Bridges (Society for Canadian Orithologists)</v>
+      </c>
     </row>
-    <row r="76" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:40" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76" s="18" t="s">
         <v>494</v>
       </c>
@@ -10747,8 +12920,12 @@
       <c r="AK76" s="17"/>
       <c r="AL76" s="24"/>
       <c r="AM76" s="17"/>
+      <c r="AN76" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Key Biodiversity Areas in Manitoba (CTV News Winnnipeg)</v>
+      </c>
     </row>
-    <row r="77" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:40" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="18" t="s">
         <v>633</v>
       </c>
@@ -10775,8 +12952,7 @@
         <v>44927</v>
       </c>
       <c r="J77" s="38">
-        <f ca="1">NOW()</f>
-        <v>46187.657905439817</v>
+        <v>45292</v>
       </c>
       <c r="K77" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -10787,26 +12963,26 @@
         <v>2023</v>
       </c>
       <c r="M77" s="23">
-        <f ca="1">MONTH(cv.table[[#This Row],[End]])</f>
-        <v>6</v>
+        <f>MONTH(cv.table[[#This Row],[End]])</f>
+        <v>1</v>
       </c>
       <c r="N77" s="23">
-        <f ca="1">YEAR(cv.table[[#This Row],[End]])</f>
-        <v>2026</v>
+        <f>YEAR(cv.table[[#This Row],[End]])</f>
+        <v>2024</v>
       </c>
       <c r="O77" s="20">
-        <f ca="1">IF((P77="Days"),((J77-I77+1)),IF(P77="Months",((J77-I77)/30),((J77-I77)/365)))</f>
-        <v>3.4538572751775813</v>
+        <f>IF((P77="Days"),((J77-I77+1)),IF(P77="Months",((J77-I77)/30),((J77-I77)/365)))</f>
+        <v>1</v>
       </c>
       <c r="P77" s="17" t="s">
-        <v>28</v>
+        <v>397</v>
       </c>
       <c r="Q77" s="17"/>
       <c r="R77" s="17" t="s">
         <v>154</v>
       </c>
       <c r="S77" s="17" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="T77" s="17"/>
       <c r="U77" s="17"/>
@@ -10822,45 +12998,49 @@
       <c r="AE77" s="17"/>
       <c r="AF77" s="24"/>
       <c r="AG77" s="27" t="s">
+        <v>638</v>
+      </c>
+      <c r="AH77" s="24" t="s">
         <v>636</v>
-      </c>
-      <c r="AH77" s="24" t="s">
-        <v>637</v>
       </c>
       <c r="AI77" s="17"/>
       <c r="AJ77" s="24"/>
       <c r="AK77" s="17"/>
       <c r="AL77" s="24"/>
       <c r="AM77" s="27" t="s">
-        <v>636</v>
+        <v>638</v>
+      </c>
+      <c r="AN77" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Website Developer (Moore Manor Designs)</v>
       </c>
     </row>
-    <row r="78" spans="1:39" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:40" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="18" t="s">
-        <v>508</v>
+        <v>658</v>
       </c>
       <c r="B78" s="30"/>
       <c r="C78" s="18" t="s">
-        <v>509</v>
+        <v>635</v>
       </c>
       <c r="D78" s="29"/>
       <c r="E78" s="17" t="s">
         <v>228</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>499</v>
+        <v>289</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="I78" s="22">
-        <v>44942</v>
-      </c>
-      <c r="J78" s="22">
-        <v>44942</v>
+        <v>181</v>
+      </c>
+      <c r="I78" s="38">
+        <v>44562</v>
+      </c>
+      <c r="J78" s="38">
+        <v>44927</v>
       </c>
       <c r="K78" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -10868,7 +13048,7 @@
       </c>
       <c r="L78" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="M78" s="23">
         <f>MONTH(cv.table[[#This Row],[End]])</f>
@@ -10879,20 +13059,18 @@
         <v>2023</v>
       </c>
       <c r="O78" s="20">
-        <f t="shared" si="2"/>
+        <f>IF((P78="Days"),((J78-I78+1)),IF(P78="Months",((J78-I78)/30),((J78-I78)/365)))</f>
         <v>1</v>
       </c>
       <c r="P78" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q78" s="17" t="s">
-        <v>214</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="Q78" s="17"/>
       <c r="R78" s="17" t="s">
-        <v>215</v>
+        <v>154</v>
       </c>
       <c r="S78" s="17" t="s">
-        <v>497</v>
+        <v>659</v>
       </c>
       <c r="T78" s="17"/>
       <c r="U78" s="17"/>
@@ -10908,49 +13086,53 @@
       <c r="AE78" s="17"/>
       <c r="AF78" s="24"/>
       <c r="AG78" s="27" t="s">
-        <v>510</v>
+        <v>660</v>
       </c>
       <c r="AH78" s="24" t="s">
-        <v>583</v>
+        <v>661</v>
       </c>
       <c r="AI78" s="17"/>
       <c r="AJ78" s="24"/>
       <c r="AK78" s="17"/>
       <c r="AL78" s="24"/>
-      <c r="AM78" s="17"/>
+      <c r="AM78" s="27" t="s">
+        <v>660</v>
+      </c>
+      <c r="AN78" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Website Developer (Personal Website)</v>
+      </c>
     </row>
-    <row r="79" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:40" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A79" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>211</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="B79" s="30"/>
       <c r="C79" s="18" t="s">
-        <v>591</v>
+        <v>509</v>
       </c>
       <c r="D79" s="29"/>
       <c r="E79" s="17" t="s">
-        <v>498</v>
+        <v>228</v>
       </c>
       <c r="F79" s="17" t="s">
         <v>42</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>5</v>
+        <v>499</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>124</v>
+        <v>188</v>
       </c>
       <c r="I79" s="22">
-        <v>44977</v>
+        <v>44942</v>
       </c>
       <c r="J79" s="22">
-        <v>44989</v>
+        <v>44942</v>
       </c>
       <c r="K79" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L79" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
@@ -10958,7 +13140,7 @@
       </c>
       <c r="M79" s="23">
         <f>MONTH(cv.table[[#This Row],[End]])</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N79" s="23">
         <f>YEAR(cv.table[[#This Row],[End]])</f>
@@ -10966,23 +13148,21 @@
       </c>
       <c r="O79" s="20">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="P79" s="17" t="s">
         <v>29</v>
       </c>
       <c r="Q79" s="17" t="s">
-        <v>592</v>
+        <v>214</v>
       </c>
       <c r="R79" s="17" t="s">
-        <v>593</v>
+        <v>215</v>
       </c>
       <c r="S79" s="17" t="s">
-        <v>594</v>
-      </c>
-      <c r="T79" s="17" t="s">
-        <v>595</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="T79" s="17"/>
       <c r="U79" s="17"/>
       <c r="V79" s="24"/>
       <c r="W79" s="24"/>
@@ -10995,46 +13175,54 @@
       <c r="AD79" s="17"/>
       <c r="AE79" s="17"/>
       <c r="AF79" s="24"/>
-      <c r="AG79" s="17"/>
-      <c r="AH79" s="24"/>
+      <c r="AG79" s="27" t="s">
+        <v>510</v>
+      </c>
+      <c r="AH79" s="24" t="s">
+        <v>583</v>
+      </c>
       <c r="AI79" s="17"/>
       <c r="AJ79" s="24"/>
       <c r="AK79" s="17"/>
       <c r="AL79" s="24"/>
       <c r="AM79" s="17"/>
+      <c r="AN79" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Many key biodiversity areas identified in Manitoba (Manitoba Cooperator)</v>
+      </c>
     </row>
-    <row r="80" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A80" s="18" t="s">
-        <v>512</v>
+        <v>210</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>511</v>
+        <v>211</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>564</v>
+        <v>591</v>
       </c>
       <c r="D80" s="29"/>
       <c r="E80" s="17" t="s">
-        <v>228</v>
+        <v>498</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>42</v>
       </c>
       <c r="G80" s="17" t="s">
-        <v>447</v>
+        <v>5</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="I80" s="22">
-        <v>45009</v>
+        <v>44977</v>
       </c>
       <c r="J80" s="22">
-        <v>45011</v>
+        <v>44989</v>
       </c>
       <c r="K80" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L80" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
@@ -11050,35 +13238,29 @@
       </c>
       <c r="O80" s="20">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P80" s="17" t="s">
         <v>29</v>
       </c>
       <c r="Q80" s="17" t="s">
-        <v>513</v>
+        <v>592</v>
       </c>
       <c r="R80" s="17" t="s">
-        <v>51</v>
+        <v>593</v>
       </c>
       <c r="S80" s="17" t="s">
-        <v>458</v>
+        <v>594</v>
       </c>
       <c r="T80" s="17" t="s">
-        <v>557</v>
+        <v>595</v>
       </c>
       <c r="U80" s="17"/>
       <c r="V80" s="24"/>
       <c r="W80" s="24"/>
-      <c r="X80" s="17" t="s">
-        <v>576</v>
-      </c>
-      <c r="Y80" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z80" s="24" t="s">
-        <v>586</v>
-      </c>
+      <c r="X80" s="17"/>
+      <c r="Y80" s="17"/>
+      <c r="Z80" s="24"/>
       <c r="AA80" s="17"/>
       <c r="AB80" s="17"/>
       <c r="AC80" s="24"/>
@@ -11091,42 +13273,44 @@
       <c r="AJ80" s="24"/>
       <c r="AK80" s="17"/>
       <c r="AL80" s="24"/>
-      <c r="AM80" s="27" t="s">
-        <v>556</v>
+      <c r="AM80" s="17"/>
+      <c r="AN80" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Conservation in Small Island Developing States (University of Manitoba)</v>
       </c>
     </row>
-    <row r="81" spans="1:39" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A81" s="18" t="s">
-        <v>210</v>
+        <v>512</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>211</v>
+        <v>511</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>482</v>
+        <v>564</v>
       </c>
       <c r="D81" s="29"/>
       <c r="E81" s="17" t="s">
         <v>228</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>30</v>
+        <v>447</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>623</v>
+        <v>100</v>
       </c>
       <c r="I81" s="22">
-        <v>45046</v>
+        <v>45009</v>
       </c>
       <c r="J81" s="22">
-        <v>45076</v>
+        <v>45011</v>
       </c>
       <c r="K81" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L81" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
@@ -11134,37 +13318,43 @@
       </c>
       <c r="M81" s="23">
         <f>MONTH(cv.table[[#This Row],[End]])</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N81" s="23">
         <f>YEAR(cv.table[[#This Row],[End]])</f>
         <v>2023</v>
       </c>
       <c r="O81" s="20">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF((P81="Days"),((J81-I81+1)),IF(P81="Months",((J81-I81)/30),((J81-I81)/365)))</f>
+        <v>3</v>
       </c>
       <c r="P81" s="17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q81" s="17" t="s">
-        <v>592</v>
+        <v>513</v>
       </c>
       <c r="R81" s="17" t="s">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="S81" s="17" t="s">
-        <v>596</v>
+        <v>458</v>
       </c>
       <c r="T81" s="17" t="s">
-        <v>602</v>
+        <v>557</v>
       </c>
       <c r="U81" s="17"/>
       <c r="V81" s="24"/>
       <c r="W81" s="24"/>
-      <c r="X81" s="17"/>
-      <c r="Y81" s="17"/>
-      <c r="Z81" s="24"/>
+      <c r="X81" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="Y81" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="Z81" s="24" t="s">
+        <v>586</v>
+      </c>
       <c r="AA81" s="17"/>
       <c r="AB81" s="17"/>
       <c r="AC81" s="24"/>
@@ -11177,44 +13367,46 @@
       <c r="AJ81" s="24"/>
       <c r="AK81" s="17"/>
       <c r="AL81" s="24"/>
-      <c r="AM81" s="26" t="s">
-        <v>346</v>
+      <c r="AM81" s="27" t="s">
+        <v>556</v>
+      </c>
+      <c r="AN81" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>2023 Annual Meeting: Methods in Wildlife Research (Ontario Chapter of the Wildlife Society)</v>
       </c>
     </row>
-    <row r="82" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:40" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A82" s="18" t="s">
-        <v>536</v>
+        <v>210</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>537</v>
+        <v>211</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>610</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>541</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="D82" s="29"/>
       <c r="E82" s="17" t="s">
         <v>228</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>178</v>
+        <v>623</v>
       </c>
       <c r="I82" s="22">
-        <v>45047</v>
+        <v>45046</v>
       </c>
       <c r="J82" s="22">
-        <v>46174</v>
+        <v>45076</v>
       </c>
       <c r="K82" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L82" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
@@ -11222,28 +13414,30 @@
       </c>
       <c r="M82" s="23">
         <f>MONTH(cv.table[[#This Row],[End]])</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N82" s="23">
         <f>YEAR(cv.table[[#This Row],[End]])</f>
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="O82" s="20">
         <f t="shared" si="2"/>
-        <v>3.0876712328767124</v>
+        <v>1</v>
       </c>
       <c r="P82" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q82" s="17"/>
+        <v>27</v>
+      </c>
+      <c r="Q82" s="17" t="s">
+        <v>592</v>
+      </c>
       <c r="R82" s="17" t="s">
-        <v>542</v>
+        <v>593</v>
       </c>
       <c r="S82" s="17" t="s">
-        <v>543</v>
+        <v>596</v>
       </c>
       <c r="T82" s="17" t="s">
-        <v>264</v>
+        <v>602</v>
       </c>
       <c r="U82" s="17"/>
       <c r="V82" s="24"/>
@@ -11257,27 +13451,33 @@
       <c r="AD82" s="17"/>
       <c r="AE82" s="17"/>
       <c r="AF82" s="24"/>
-      <c r="AG82" s="27"/>
+      <c r="AG82" s="17"/>
       <c r="AH82" s="24"/>
       <c r="AI82" s="17"/>
       <c r="AJ82" s="24"/>
       <c r="AK82" s="17"/>
       <c r="AL82" s="24"/>
-      <c r="AM82" s="27" t="s">
-        <v>540</v>
+      <c r="AM82" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="AN82" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Data Analyst (University of Manitoba)</v>
       </c>
     </row>
-    <row r="83" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A83" s="18" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>566</v>
-      </c>
-      <c r="D83" s="29"/>
+        <v>610</v>
+      </c>
+      <c r="D83" s="25" t="s">
+        <v>541</v>
+      </c>
       <c r="E83" s="17" t="s">
         <v>228</v>
       </c>
@@ -11285,20 +13485,20 @@
         <v>42</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>447</v>
+        <v>13</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="I83" s="22">
-        <v>45088</v>
+        <v>45047</v>
       </c>
       <c r="J83" s="22">
-        <v>45091</v>
+        <v>46174</v>
       </c>
       <c r="K83" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L83" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
@@ -11310,64 +13510,60 @@
       </c>
       <c r="N83" s="23">
         <f>YEAR(cv.table[[#This Row],[End]])</f>
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="O83" s="20">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3.0876712328767124</v>
       </c>
       <c r="P83" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q83" s="17" t="s">
-        <v>214</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="Q83" s="17"/>
       <c r="R83" s="17" t="s">
-        <v>215</v>
+        <v>542</v>
       </c>
       <c r="S83" s="17" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="T83" s="17" t="s">
-        <v>557</v>
+        <v>264</v>
       </c>
       <c r="U83" s="17"/>
-      <c r="V83" s="24" t="s">
-        <v>575</v>
-      </c>
+      <c r="V83" s="24"/>
       <c r="W83" s="24"/>
-      <c r="X83" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="Y83" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z83" s="24" t="s">
-        <v>574</v>
-      </c>
+      <c r="X83" s="17"/>
+      <c r="Y83" s="17"/>
+      <c r="Z83" s="24"/>
       <c r="AA83" s="17"/>
       <c r="AB83" s="17"/>
       <c r="AC83" s="24"/>
       <c r="AD83" s="17"/>
       <c r="AE83" s="17"/>
       <c r="AF83" s="24"/>
-      <c r="AG83" s="17"/>
+      <c r="AG83" s="27"/>
       <c r="AH83" s="24"/>
       <c r="AI83" s="17"/>
       <c r="AJ83" s="24"/>
       <c r="AK83" s="17"/>
       <c r="AL83" s="24"/>
       <c r="AM83" s="27" t="s">
-        <v>559</v>
+        <v>540</v>
+      </c>
+      <c r="AN83" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>North America Regional Director (Society for Conservation Biology)</v>
       </c>
     </row>
-    <row r="84" spans="1:39" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A84" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="B84" s="30"/>
+        <v>514</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>515</v>
+      </c>
       <c r="C84" s="18" t="s">
-        <v>517</v>
+        <v>566</v>
       </c>
       <c r="D84" s="29"/>
       <c r="E84" s="17" t="s">
@@ -11377,20 +13573,20 @@
         <v>42</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>499</v>
+        <v>447</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="I84" s="22">
-        <v>45138</v>
+        <v>45088</v>
       </c>
       <c r="J84" s="22">
-        <v>45138</v>
+        <v>45091</v>
       </c>
       <c r="K84" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L84" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
@@ -11398,7 +13594,7 @@
       </c>
       <c r="M84" s="23">
         <f>MONTH(cv.table[[#This Row],[End]])</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N84" s="23">
         <f>YEAR(cv.table[[#This Row],[End]])</f>
@@ -11406,54 +13602,64 @@
       </c>
       <c r="O84" s="20">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P84" s="17" t="s">
         <v>29</v>
       </c>
       <c r="Q84" s="17" t="s">
-        <v>484</v>
+        <v>214</v>
       </c>
       <c r="R84" s="17" t="s">
-        <v>51</v>
+        <v>215</v>
       </c>
       <c r="S84" s="17" t="s">
-        <v>518</v>
-      </c>
-      <c r="T84" s="17"/>
+        <v>535</v>
+      </c>
+      <c r="T84" s="17" t="s">
+        <v>557</v>
+      </c>
       <c r="U84" s="17"/>
-      <c r="V84" s="24"/>
+      <c r="V84" s="24" t="s">
+        <v>575</v>
+      </c>
       <c r="W84" s="24"/>
-      <c r="X84" s="17"/>
-      <c r="Y84" s="17"/>
-      <c r="Z84" s="24"/>
+      <c r="X84" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="Y84" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="Z84" s="24" t="s">
+        <v>574</v>
+      </c>
       <c r="AA84" s="17"/>
       <c r="AB84" s="17"/>
       <c r="AC84" s="24"/>
       <c r="AD84" s="17"/>
       <c r="AE84" s="17"/>
       <c r="AF84" s="24"/>
-      <c r="AG84" s="27" t="s">
-        <v>519</v>
-      </c>
-      <c r="AH84" s="24" t="s">
-        <v>582</v>
-      </c>
+      <c r="AG84" s="17"/>
+      <c r="AH84" s="24"/>
       <c r="AI84" s="17"/>
       <c r="AJ84" s="24"/>
       <c r="AK84" s="17"/>
       <c r="AL84" s="24"/>
-      <c r="AM84" s="27"/>
+      <c r="AM84" s="27" t="s">
+        <v>559</v>
+      </c>
+      <c r="AN84" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>2023 Joint Annual Meeting with Canadian Botanical Association (Canadian Society for Ecology and Evolution)</v>
+      </c>
     </row>
-    <row r="85" spans="1:39" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:40" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A85" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B85" s="30" t="s">
-        <v>44</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="B85" s="30"/>
       <c r="C85" s="18" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D85" s="29"/>
       <c r="E85" s="17" t="s">
@@ -11469,14 +13675,14 @@
         <v>188</v>
       </c>
       <c r="I85" s="22">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="J85" s="22">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="K85" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L85" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
@@ -11484,7 +13690,7 @@
       </c>
       <c r="M85" s="23">
         <f>MONTH(cv.table[[#This Row],[End]])</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N85" s="23">
         <f>YEAR(cv.table[[#This Row],[End]])</f>
@@ -11498,13 +13704,13 @@
         <v>29</v>
       </c>
       <c r="Q85" s="17" t="s">
-        <v>545</v>
+        <v>484</v>
       </c>
       <c r="R85" s="17" t="s">
-        <v>546</v>
+        <v>51</v>
       </c>
       <c r="S85" s="17" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="T85" s="17"/>
       <c r="U85" s="17"/>
@@ -11520,26 +13726,30 @@
       <c r="AE85" s="17"/>
       <c r="AF85" s="24"/>
       <c r="AG85" s="27" t="s">
-        <v>544</v>
+        <v>519</v>
       </c>
       <c r="AH85" s="24" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="AI85" s="17"/>
       <c r="AJ85" s="24"/>
       <c r="AK85" s="17"/>
       <c r="AL85" s="24"/>
       <c r="AM85" s="27"/>
+      <c r="AN85" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Our World: Ecosystem Restoration - United Nations and Western Canada (Food for the Future (Global News Radio))</v>
+      </c>
     </row>
-    <row r="86" spans="1:39" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:40" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A86" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B86" s="19" t="s">
-        <v>14</v>
+        <v>43</v>
+      </c>
+      <c r="B86" s="30" t="s">
+        <v>44</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>606</v>
+        <v>520</v>
       </c>
       <c r="D86" s="29"/>
       <c r="E86" s="17" t="s">
@@ -11549,59 +13759,52 @@
         <v>42</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>30</v>
+        <v>499</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="I86" s="22">
-        <v>45292</v>
+        <v>45169</v>
       </c>
       <c r="J86" s="22">
-        <f ca="1">NOW()</f>
-        <v>46187.657905439817</v>
+        <v>45169</v>
       </c>
       <c r="K86" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L86" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="M86" s="23">
-        <f ca="1">MONTH(cv.table[[#This Row],[End]])</f>
-        <v>6</v>
+        <f>MONTH(cv.table[[#This Row],[End]])</f>
+        <v>8</v>
       </c>
       <c r="N86" s="23">
-        <f ca="1">YEAR(cv.table[[#This Row],[End]])</f>
-        <v>2026</v>
+        <f>YEAR(cv.table[[#This Row],[End]])</f>
+        <v>2023</v>
       </c>
       <c r="O86" s="20">
-        <f t="shared" ca="1" si="2"/>
-        <v>2.4538572751775813</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="P86" s="17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q86" s="17" t="s">
-        <v>50</v>
+        <v>545</v>
       </c>
       <c r="R86" s="17" t="s">
-        <v>51</v>
+        <v>546</v>
       </c>
       <c r="S86" s="17" t="s">
-        <v>622</v>
-      </c>
-      <c r="T86" s="17" t="s">
-        <v>625</v>
-      </c>
-      <c r="U86" s="17" t="s">
-        <v>624</v>
-      </c>
-      <c r="V86" s="24" t="s">
-        <v>626</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="T86" s="17"/>
+      <c r="U86" s="17"/>
+      <c r="V86" s="24"/>
       <c r="W86" s="24"/>
       <c r="X86" s="17"/>
       <c r="Y86" s="17"/>
@@ -11612,25 +13815,31 @@
       <c r="AD86" s="17"/>
       <c r="AE86" s="17"/>
       <c r="AF86" s="24"/>
-      <c r="AG86" s="17"/>
-      <c r="AH86" s="24"/>
+      <c r="AG86" s="27" t="s">
+        <v>544</v>
+      </c>
+      <c r="AH86" s="24" t="s">
+        <v>585</v>
+      </c>
       <c r="AI86" s="17"/>
       <c r="AJ86" s="24"/>
       <c r="AK86" s="17"/>
       <c r="AL86" s="24"/>
-      <c r="AM86" s="27" t="s">
-        <v>627</v>
+      <c r="AM86" s="27"/>
+      <c r="AN86" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>NCC Magazine (Fall 2023) (Nature Conservancy Canada)</v>
       </c>
     </row>
-    <row r="87" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:40" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A87" s="18" t="s">
-        <v>536</v>
+        <v>6</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>537</v>
+        <v>14</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>568</v>
+        <v>606</v>
       </c>
       <c r="D87" s="29"/>
       <c r="E87" s="17" t="s">
@@ -11640,54 +13849,59 @@
         <v>42</v>
       </c>
       <c r="G87" s="17" t="s">
-        <v>447</v>
+        <v>30</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>522</v>
+        <v>92</v>
       </c>
       <c r="I87" s="22">
-        <v>45466</v>
+        <v>45292</v>
       </c>
       <c r="J87" s="22">
-        <v>45471</v>
+        <f ca="1">NOW()</f>
+        <v>46188.50092766204</v>
       </c>
       <c r="K87" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L87" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
         <v>2024</v>
       </c>
       <c r="M87" s="23">
-        <f>MONTH(cv.table[[#This Row],[End]])</f>
+        <f ca="1">MONTH(cv.table[[#This Row],[End]])</f>
         <v>6</v>
       </c>
       <c r="N87" s="23">
-        <f>YEAR(cv.table[[#This Row],[End]])</f>
-        <v>2024</v>
+        <f ca="1">YEAR(cv.table[[#This Row],[End]])</f>
+        <v>2026</v>
       </c>
       <c r="O87" s="20">
-        <f t="shared" si="2"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>2.4561669251014804</v>
       </c>
       <c r="P87" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q87" s="17" t="s">
-        <v>523</v>
+        <v>50</v>
       </c>
       <c r="R87" s="17" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="S87" s="17" t="s">
-        <v>535</v>
+        <v>622</v>
       </c>
       <c r="T87" s="17" t="s">
-        <v>538</v>
-      </c>
-      <c r="U87" s="17"/>
-      <c r="V87" s="24"/>
+        <v>625</v>
+      </c>
+      <c r="U87" s="17" t="s">
+        <v>624</v>
+      </c>
+      <c r="V87" s="24" t="s">
+        <v>626</v>
+      </c>
       <c r="W87" s="24"/>
       <c r="X87" s="17"/>
       <c r="Y87" s="17"/>
@@ -11698,25 +13912,29 @@
       <c r="AD87" s="17"/>
       <c r="AE87" s="17"/>
       <c r="AF87" s="24"/>
-      <c r="AG87" s="27"/>
+      <c r="AG87" s="17"/>
       <c r="AH87" s="24"/>
       <c r="AI87" s="17"/>
       <c r="AJ87" s="24"/>
       <c r="AK87" s="17"/>
       <c r="AL87" s="24"/>
       <c r="AM87" s="27" t="s">
-        <v>539</v>
+        <v>627</v>
+      </c>
+      <c r="AN87" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Part-time Professor (Niagara College)</v>
       </c>
     </row>
-    <row r="88" spans="1:39" ht="66" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A88" s="18" t="s">
-        <v>10</v>
+        <v>536</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>15</v>
+        <v>537</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D88" s="29"/>
       <c r="E88" s="17" t="s">
@@ -11732,14 +13950,14 @@
         <v>522</v>
       </c>
       <c r="I88" s="22">
-        <v>45593</v>
+        <v>45466</v>
       </c>
       <c r="J88" s="22">
-        <v>45597</v>
+        <v>45471</v>
       </c>
       <c r="K88" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L88" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
@@ -11747,7 +13965,7 @@
       </c>
       <c r="M88" s="23">
         <f>MONTH(cv.table[[#This Row],[End]])</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N88" s="23">
         <f>YEAR(cv.table[[#This Row],[End]])</f>
@@ -11755,7 +13973,7 @@
       </c>
       <c r="O88" s="20">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P88" s="17" t="s">
         <v>29</v>
@@ -11767,10 +13985,10 @@
         <v>56</v>
       </c>
       <c r="S88" s="17" t="s">
-        <v>607</v>
+        <v>535</v>
       </c>
       <c r="T88" s="17" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="U88" s="17"/>
       <c r="V88" s="24"/>
@@ -11791,41 +14009,45 @@
       <c r="AK88" s="17"/>
       <c r="AL88" s="24"/>
       <c r="AM88" s="27" t="s">
-        <v>524</v>
+        <v>539</v>
+      </c>
+      <c r="AN88" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>2024 SCB North American Congress for Conservation Biology (Society for Conservation Biology)</v>
       </c>
     </row>
-    <row r="89" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:40" ht="66" x14ac:dyDescent="0.3">
       <c r="A89" s="18" t="s">
-        <v>349</v>
+        <v>10</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>350</v>
+        <v>15</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>482</v>
+        <v>567</v>
       </c>
       <c r="D89" s="29"/>
       <c r="E89" s="17" t="s">
         <v>228</v>
       </c>
       <c r="F89" s="17" t="s">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>30</v>
+        <v>447</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>623</v>
-      </c>
-      <c r="I89" s="38">
+        <v>522</v>
+      </c>
+      <c r="I89" s="22">
+        <v>45593</v>
+      </c>
+      <c r="J89" s="22">
         <v>45597</v>
-      </c>
-      <c r="J89" s="38">
-        <v>45962</v>
       </c>
       <c r="K89" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L89" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
@@ -11837,26 +14059,26 @@
       </c>
       <c r="N89" s="23">
         <f>YEAR(cv.table[[#This Row],[End]])</f>
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="O89" s="20">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P89" s="17" t="s">
-        <v>397</v>
+        <v>29</v>
       </c>
       <c r="Q89" s="17" t="s">
-        <v>52</v>
+        <v>523</v>
       </c>
       <c r="R89" s="17" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="S89" s="17" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="T89" s="17" t="s">
-        <v>618</v>
+        <v>525</v>
       </c>
       <c r="U89" s="17"/>
       <c r="V89" s="24"/>
@@ -11870,52 +14092,60 @@
       <c r="AD89" s="17"/>
       <c r="AE89" s="17"/>
       <c r="AF89" s="24"/>
-      <c r="AG89" s="26"/>
+      <c r="AG89" s="27"/>
       <c r="AH89" s="24"/>
       <c r="AI89" s="17"/>
       <c r="AJ89" s="24"/>
       <c r="AK89" s="17"/>
       <c r="AL89" s="24"/>
-      <c r="AM89" s="26"/>
+      <c r="AM89" s="27" t="s">
+        <v>524</v>
+      </c>
+      <c r="AN89" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>2024 SER North America Conference (Society for Ecological Restoration)</v>
+      </c>
     </row>
-    <row r="90" spans="1:39" ht="198" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A90" s="18" t="s">
-        <v>619</v>
-      </c>
-      <c r="B90" s="30"/>
+        <v>349</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>350</v>
+      </c>
       <c r="C90" s="18" t="s">
-        <v>620</v>
+        <v>482</v>
       </c>
       <c r="D90" s="29"/>
       <c r="E90" s="17" t="s">
         <v>228</v>
       </c>
       <c r="F90" s="17" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="G90" s="17" t="s">
-        <v>499</v>
+        <v>30</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>500</v>
+        <v>623</v>
       </c>
       <c r="I90" s="38">
-        <v>45797</v>
+        <v>45597</v>
       </c>
       <c r="J90" s="38">
-        <v>45797</v>
+        <v>45962</v>
       </c>
       <c r="K90" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L90" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="M90" s="23">
         <f>MONTH(cv.table[[#This Row],[End]])</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N90" s="23">
         <f>YEAR(cv.table[[#This Row],[End]])</f>
@@ -11926,16 +14156,20 @@
         <v>1</v>
       </c>
       <c r="P90" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q90" s="17"/>
+        <v>397</v>
+      </c>
+      <c r="Q90" s="17" t="s">
+        <v>52</v>
+      </c>
       <c r="R90" s="17" t="s">
-        <v>154</v>
+        <v>51</v>
       </c>
       <c r="S90" s="17" t="s">
-        <v>617</v>
-      </c>
-      <c r="T90" s="17"/>
+        <v>609</v>
+      </c>
+      <c r="T90" s="17" t="s">
+        <v>618</v>
+      </c>
       <c r="U90" s="17"/>
       <c r="V90" s="24"/>
       <c r="W90" s="24"/>
@@ -11948,32 +14182,32 @@
       <c r="AD90" s="17"/>
       <c r="AE90" s="17"/>
       <c r="AF90" s="24"/>
-      <c r="AG90" s="27" t="s">
-        <v>616</v>
-      </c>
-      <c r="AH90" s="24" t="s">
-        <v>621</v>
-      </c>
+      <c r="AG90" s="26"/>
+      <c r="AH90" s="24"/>
       <c r="AI90" s="17"/>
       <c r="AJ90" s="24"/>
       <c r="AK90" s="17"/>
       <c r="AL90" s="24"/>
       <c r="AM90" s="26"/>
+      <c r="AN90" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Data Analyst (Swim, Drink, Fish)</v>
+      </c>
     </row>
-    <row r="91" spans="1:39" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:40" ht="211.2" x14ac:dyDescent="0.3">
       <c r="A91" s="18" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B91" s="30"/>
       <c r="C91" s="18" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D91" s="29"/>
       <c r="E91" s="17" t="s">
         <v>228</v>
       </c>
       <c r="F91" s="17" t="s">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="G91" s="17" t="s">
         <v>499</v>
@@ -11982,14 +14216,14 @@
         <v>500</v>
       </c>
       <c r="I91" s="38">
-        <v>45938</v>
+        <v>45797</v>
       </c>
       <c r="J91" s="38">
-        <v>45938</v>
+        <v>45797</v>
       </c>
       <c r="K91" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L91" s="23">
         <f>YEAR(cv.table[[#This Row],[Start]])</f>
@@ -11997,7 +14231,7 @@
       </c>
       <c r="M91" s="23">
         <f>MONTH(cv.table[[#This Row],[End]])</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N91" s="23">
         <f>YEAR(cv.table[[#This Row],[End]])</f>
@@ -12012,10 +14246,10 @@
       </c>
       <c r="Q91" s="17"/>
       <c r="R91" s="17" t="s">
-        <v>215</v>
+        <v>154</v>
       </c>
       <c r="S91" s="17" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="T91" s="17"/>
       <c r="U91" s="17"/>
@@ -12031,53 +14265,133 @@
       <c r="AE91" s="17"/>
       <c r="AF91" s="24"/>
       <c r="AG91" s="27" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="AH91" s="24" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="AI91" s="17"/>
       <c r="AJ91" s="24"/>
       <c r="AK91" s="17"/>
       <c r="AL91" s="24"/>
-      <c r="AM91" s="17"/>
+      <c r="AM91" s="26"/>
+      <c r="AN91" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>Canada's Mountainous Marvels: Safeguarding Unique Ecosystems and Species (State of the Mountains)</v>
+      </c>
+    </row>
+    <row r="92" spans="1:40" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="B92" s="30"/>
+      <c r="C92" s="18" t="s">
+        <v>614</v>
+      </c>
+      <c r="D92" s="29"/>
+      <c r="E92" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="F92" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="G92" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="H92" s="24" t="s">
+        <v>500</v>
+      </c>
+      <c r="I92" s="38">
+        <v>45938</v>
+      </c>
+      <c r="J92" s="38">
+        <v>45938</v>
+      </c>
+      <c r="K92" s="23">
+        <f>MONTH(cv.table[[#This Row],[Start]])</f>
+        <v>10</v>
+      </c>
+      <c r="L92" s="23">
+        <f>YEAR(cv.table[[#This Row],[Start]])</f>
+        <v>2025</v>
+      </c>
+      <c r="M92" s="23">
+        <f>MONTH(cv.table[[#This Row],[End]])</f>
+        <v>10</v>
+      </c>
+      <c r="N92" s="23">
+        <f>YEAR(cv.table[[#This Row],[End]])</f>
+        <v>2025</v>
+      </c>
+      <c r="O92" s="20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="P92" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q92" s="17"/>
+      <c r="R92" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="S92" s="17" t="s">
+        <v>615</v>
+      </c>
+      <c r="T92" s="17"/>
+      <c r="U92" s="17"/>
+      <c r="V92" s="24"/>
+      <c r="W92" s="24"/>
+      <c r="X92" s="17"/>
+      <c r="Y92" s="17"/>
+      <c r="Z92" s="24"/>
+      <c r="AA92" s="17"/>
+      <c r="AB92" s="17"/>
+      <c r="AC92" s="24"/>
+      <c r="AD92" s="17"/>
+      <c r="AE92" s="17"/>
+      <c r="AF92" s="24"/>
+      <c r="AG92" s="27" t="s">
+        <v>611</v>
+      </c>
+      <c r="AH92" s="24" t="s">
+        <v>612</v>
+      </c>
+      <c r="AI92" s="17"/>
+      <c r="AJ92" s="24"/>
+      <c r="AK92" s="17"/>
+      <c r="AL92" s="24"/>
+      <c r="AM92" s="17"/>
+      <c r="AN92" s="44" t="str">
+        <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
+        <v>A rare ecological treasure (The Manitoban)</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A2:AM91">
-    <cfRule type="expression" dxfId="4" priority="3">
+  <conditionalFormatting sqref="A2:AN92">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$E2="Exclude"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>$E2="Include"</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="2" priority="5" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="0" priority="5" timePeriod="today">
       <formula>FLOOR(A2,1)=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J66 J67:N69">
-    <cfRule type="timePeriod" dxfId="1" priority="7" timePeriod="today">
-      <formula>FLOOR(J66,1)=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:N65 K66:N66 J71:N73">
-    <cfRule type="timePeriod" dxfId="0" priority="11" timePeriod="today">
-      <formula>FLOOR(J1,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="1168" yWindow="886" count="8">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="What was the position?" sqref="S2:S63 T30:T32 T46:T47" xr:uid="{DFFB3205-BD66-4B32-A076-E848052A5B1A}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Tasks" prompt="What did you actually do?" sqref="T2:T29 T33:T45 T48:T74" xr:uid="{5B09CA76-B76C-4EFC-93E7-51ADFF39ECBC}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Achievements" prompt="What were you able to accomplish?" sqref="V2:V91" xr:uid="{F198362A-9CD5-4B7D-91B0-5DE89BA44CA6}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Lessons" prompt="What did you learn?" sqref="U2:U91" xr:uid="{08B32566-C755-4266-AD84-F0DF9F2CF7AF}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G91" xr:uid="{D7AFE9C3-998F-44D9-8631-27D45959B0FA}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Achievements" prompt="What were you able to accomplish?" sqref="V2:V92" xr:uid="{F198362A-9CD5-4B7D-91B0-5DE89BA44CA6}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Lessons" prompt="What did you learn?" sqref="U2:U92" xr:uid="{08B32566-C755-4266-AD84-F0DF9F2CF7AF}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G92" xr:uid="{D7AFE9C3-998F-44D9-8631-27D45959B0FA}">
       <formula1>Category</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F91" xr:uid="{4C036C20-1026-41D3-A102-75B014022A86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F92" xr:uid="{4C036C20-1026-41D3-A102-75B014022A86}">
       <formula1>Branch</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Notes" prompt="Non-displayed entry notes" sqref="W2:W91" xr:uid="{F58D462A-025C-49EB-8CEE-5C27C7C59311}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H91" xr:uid="{2D12E60C-44BF-4035-9CD9-285BCB7B7676}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Notes" prompt="Non-displayed entry notes" sqref="W2:W92" xr:uid="{F58D462A-025C-49EB-8CEE-5C27C7C59311}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H92" xr:uid="{2D12E60C-44BF-4035-9CD9-285BCB7B7676}">
       <formula1>INDIRECT(G2)</formula1>
     </dataValidation>
   </dataValidations>
@@ -12148,43 +14462,792 @@
     <hyperlink ref="AM71" r:id="rId64" xr:uid="{96087071-4009-4CE1-9AC1-323355268DE6}"/>
     <hyperlink ref="AG65" r:id="rId65" xr:uid="{6DA8FDCE-C424-4E2D-910F-60F65FC00086}"/>
     <hyperlink ref="AG74" r:id="rId66" xr:uid="{AC53ED54-CCA8-4E0F-85B8-D400BDA66D04}"/>
-    <hyperlink ref="AG78" r:id="rId67" xr:uid="{1928F5CC-41A8-4F6B-B92D-6FF788B73610}"/>
-    <hyperlink ref="AM82" r:id="rId68" xr:uid="{5F4711C6-A818-47D8-9DAF-2D2C9404B54F}"/>
-    <hyperlink ref="AM88" r:id="rId69" xr:uid="{66941300-BD4C-4A15-8EB1-29A262DC58A6}"/>
-    <hyperlink ref="AM87" r:id="rId70" xr:uid="{2BFE37BF-313D-4061-AD97-35F83F6DA34B}"/>
+    <hyperlink ref="AG79" r:id="rId67" xr:uid="{1928F5CC-41A8-4F6B-B92D-6FF788B73610}"/>
+    <hyperlink ref="AM83" r:id="rId68" xr:uid="{5F4711C6-A818-47D8-9DAF-2D2C9404B54F}"/>
+    <hyperlink ref="AM89" r:id="rId69" xr:uid="{66941300-BD4C-4A15-8EB1-29A262DC58A6}"/>
+    <hyperlink ref="AM88" r:id="rId70" xr:uid="{2BFE37BF-313D-4061-AD97-35F83F6DA34B}"/>
     <hyperlink ref="AG76" r:id="rId71" xr:uid="{16A559BC-C550-455B-8634-DCC6EF88C07B}"/>
-    <hyperlink ref="AG85" r:id="rId72" xr:uid="{00F946AD-0FB4-472A-A714-54C4AA4B6433}"/>
-    <hyperlink ref="AG84" r:id="rId73" xr:uid="{16B912A6-D880-42C8-B8D4-71FBCE0F29F5}"/>
+    <hyperlink ref="AG86" r:id="rId72" xr:uid="{00F946AD-0FB4-472A-A714-54C4AA4B6433}"/>
+    <hyperlink ref="AG85" r:id="rId73" xr:uid="{16B912A6-D880-42C8-B8D4-71FBCE0F29F5}"/>
     <hyperlink ref="AM75" r:id="rId74" xr:uid="{9FE09915-578F-4115-B37E-D8A4B471254F}"/>
-    <hyperlink ref="AM80" r:id="rId75" xr:uid="{2AD7B1F9-2A63-4B70-AEE9-C75509166B76}"/>
+    <hyperlink ref="AM81" r:id="rId75" xr:uid="{2AD7B1F9-2A63-4B70-AEE9-C75509166B76}"/>
     <hyperlink ref="AM69" r:id="rId76" xr:uid="{AC73CD60-6FB0-45AA-B7B2-ECBDF2701C05}"/>
-    <hyperlink ref="AM83" r:id="rId77" xr:uid="{2EE300EB-A40B-46BA-AAA6-D341C24B36CC}"/>
+    <hyperlink ref="AM84" r:id="rId77" xr:uid="{2EE300EB-A40B-46BA-AAA6-D341C24B36CC}"/>
     <hyperlink ref="AM73" r:id="rId78" xr:uid="{92103350-519E-4B58-8F41-71B01EDB2C31}"/>
     <hyperlink ref="AM67" r:id="rId79" xr:uid="{5819C53E-E8A7-4B39-A39A-7520BDC7CB9F}"/>
-    <hyperlink ref="AM81" r:id="rId80" xr:uid="{84A2AC56-6EA8-407F-A588-FAD5D68646F0}"/>
+    <hyperlink ref="AM82" r:id="rId80" xr:uid="{84A2AC56-6EA8-407F-A588-FAD5D68646F0}"/>
     <hyperlink ref="AM72" r:id="rId81" xr:uid="{F1C20FFE-6C3E-4368-A270-89B950C0FF29}"/>
     <hyperlink ref="AG72" r:id="rId82" xr:uid="{70FAC708-C292-4492-9018-05820621C442}"/>
-    <hyperlink ref="AG91" r:id="rId83" xr:uid="{C98D162F-5C95-4AD1-B3C5-D1F4CB8E7451}"/>
-    <hyperlink ref="AG90" r:id="rId84" xr:uid="{20BB5C2D-1157-4146-9E24-83428E1E1DED}"/>
-    <hyperlink ref="AM86" r:id="rId85" xr:uid="{1E93A6EF-A3B9-460B-82B4-415FA7F956E6}"/>
+    <hyperlink ref="AG92" r:id="rId83" xr:uid="{C98D162F-5C95-4AD1-B3C5-D1F4CB8E7451}"/>
+    <hyperlink ref="AG91" r:id="rId84" xr:uid="{20BB5C2D-1157-4146-9E24-83428E1E1DED}"/>
+    <hyperlink ref="AM87" r:id="rId85" xr:uid="{1E93A6EF-A3B9-460B-82B4-415FA7F956E6}"/>
     <hyperlink ref="AG62" r:id="rId86" xr:uid="{4EFC5AD9-ABDA-4394-9846-A04568B85921}"/>
-    <hyperlink ref="AG77" r:id="rId87" xr:uid="{07056D2D-D65E-474F-8041-04DD48BE32BF}"/>
-    <hyperlink ref="AM77" r:id="rId88" xr:uid="{8ACA34EC-47A5-4BEC-BEF9-139B868A9D5D}"/>
+    <hyperlink ref="AM77" r:id="rId87" xr:uid="{8ACA34EC-47A5-4BEC-BEF9-139B868A9D5D}"/>
+    <hyperlink ref="AG77" r:id="rId88" xr:uid="{07056D2D-D65E-474F-8041-04DD48BE32BF}"/>
+    <hyperlink ref="AG78" r:id="rId89" xr:uid="{CD7C4BFB-708D-41DA-A0DC-D9EC9D101C41}"/>
+    <hyperlink ref="AM78" r:id="rId90" xr:uid="{17410996-AA20-4D84-B438-FC7A4E3897D9}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId89"/>
+  <pageSetup orientation="landscape" r:id="rId91"/>
   <tableParts count="1">
-    <tablePart r:id="rId90"/>
+    <tablePart r:id="rId92"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376035FC-43A2-492E-A452-9F7A1A76C10E}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376035FC-43A2-492E-A452-9F7A1A76C10E}">
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="34.88671875" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="7" max="7" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C1" t="s">
+        <v>684</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>687</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>646</v>
+      </c>
+      <c r="H1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C2" t="s">
+        <v>678</v>
+      </c>
+      <c r="D2" s="40">
+        <v>43344</v>
+      </c>
+      <c r="E2" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>7.8</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>662</v>
+      </c>
+      <c r="H2" s="39">
+        <v>39.099999999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C3" t="s">
+        <v>681</v>
+      </c>
+      <c r="D3" s="40">
+        <v>43739</v>
+      </c>
+      <c r="E3" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>6.8</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>656</v>
+      </c>
+      <c r="H3" s="39">
+        <v>12.799999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>664</v>
+      </c>
+      <c r="B4" t="s">
+        <v>673</v>
+      </c>
+      <c r="C4" t="s">
+        <v>681</v>
+      </c>
+      <c r="D4" s="40">
+        <v>44075</v>
+      </c>
+      <c r="E4" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>5.8</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>655</v>
+      </c>
+      <c r="H4" s="39">
+        <v>12.799999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>664</v>
+      </c>
+      <c r="B5" t="s">
+        <v>674</v>
+      </c>
+      <c r="C5" t="s">
+        <v>680</v>
+      </c>
+      <c r="D5" s="40">
+        <v>45901</v>
+      </c>
+      <c r="E5" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>668</v>
+      </c>
+      <c r="H5" s="39">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>664</v>
+      </c>
+      <c r="B6" t="s">
+        <v>672</v>
+      </c>
+      <c r="C6" t="s">
+        <v>680</v>
+      </c>
+      <c r="D6" s="40">
+        <v>43739</v>
+      </c>
+      <c r="E6" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>6.8</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>676</v>
+      </c>
+      <c r="H6" s="39">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>664</v>
+      </c>
+      <c r="B7" t="s">
+        <v>675</v>
+      </c>
+      <c r="C7" t="s">
+        <v>682</v>
+      </c>
+      <c r="D7" s="40">
+        <v>45901</v>
+      </c>
+      <c r="E7" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>677</v>
+      </c>
+      <c r="H7" s="39">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>651</v>
+      </c>
+      <c r="B8" t="s">
+        <v>652</v>
+      </c>
+      <c r="C8" t="s">
+        <v>680</v>
+      </c>
+      <c r="D8" s="40">
+        <v>44075</v>
+      </c>
+      <c r="E8" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>5.8</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>669</v>
+      </c>
+      <c r="H8" s="39">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>651</v>
+      </c>
+      <c r="B9" t="s">
+        <v>653</v>
+      </c>
+      <c r="C9" t="s">
+        <v>683</v>
+      </c>
+      <c r="D9" s="40">
+        <v>44197</v>
+      </c>
+      <c r="E9" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>5.5</v>
+      </c>
+      <c r="G9" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="H9" s="39">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>651</v>
+      </c>
+      <c r="B10" t="s">
+        <v>654</v>
+      </c>
+      <c r="C10" t="s">
+        <v>680</v>
+      </c>
+      <c r="D10" s="40">
+        <v>44562</v>
+      </c>
+      <c r="E10" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>4.5</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>664</v>
+      </c>
+      <c r="H10" s="39">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>662</v>
+      </c>
+      <c r="B11" t="s">
+        <v>655</v>
+      </c>
+      <c r="C11" t="s">
+        <v>681</v>
+      </c>
+      <c r="D11" s="40">
+        <v>41518</v>
+      </c>
+      <c r="E11" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>12.799999999999999</v>
+      </c>
+      <c r="G11" s="43" t="s">
+        <v>648</v>
+      </c>
+      <c r="H11" s="39">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>662</v>
+      </c>
+      <c r="B12" t="s">
+        <v>656</v>
+      </c>
+      <c r="C12" t="s">
+        <v>681</v>
+      </c>
+      <c r="D12" s="40">
+        <v>41518</v>
+      </c>
+      <c r="E12" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>12.799999999999999</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>672</v>
+      </c>
+      <c r="H12" s="39">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>662</v>
+      </c>
+      <c r="B13" t="s">
+        <v>668</v>
+      </c>
+      <c r="C13" t="s">
+        <v>680</v>
+      </c>
+      <c r="D13" s="40">
+        <v>44197</v>
+      </c>
+      <c r="E13" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>5.5</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>671</v>
+      </c>
+      <c r="H13" s="39">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>662</v>
+      </c>
+      <c r="B14" t="s">
+        <v>669</v>
+      </c>
+      <c r="C14" t="s">
+        <v>681</v>
+      </c>
+      <c r="D14" s="40">
+        <v>45292</v>
+      </c>
+      <c r="E14" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>2.5</v>
+      </c>
+      <c r="G14" s="43" t="s">
+        <v>673</v>
+      </c>
+      <c r="H14" s="39">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>662</v>
+      </c>
+      <c r="B15" t="s">
+        <v>670</v>
+      </c>
+      <c r="C15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D15" s="40">
+        <v>46023</v>
+      </c>
+      <c r="E15" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>675</v>
+      </c>
+      <c r="H15" s="39">
+        <v>0.79999999999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>662</v>
+      </c>
+      <c r="B16" t="s">
+        <v>676</v>
+      </c>
+      <c r="C16" t="s">
+        <v>680</v>
+      </c>
+      <c r="D16" s="40">
+        <v>45292</v>
+      </c>
+      <c r="E16" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>2.5</v>
+      </c>
+      <c r="G16" s="43" t="s">
+        <v>674</v>
+      </c>
+      <c r="H16" s="39">
+        <v>0.79999999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>662</v>
+      </c>
+      <c r="B17" t="s">
+        <v>677</v>
+      </c>
+      <c r="C17" t="s">
+        <v>682</v>
+      </c>
+      <c r="D17" s="40">
+        <v>45292</v>
+      </c>
+      <c r="E17" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>2.5</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>663</v>
+      </c>
+      <c r="H17" s="39">
+        <v>22.900000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>643</v>
+      </c>
+      <c r="B18" t="s">
+        <v>679</v>
+      </c>
+      <c r="C18" t="s">
+        <v>682</v>
+      </c>
+      <c r="D18" s="40">
+        <v>46023</v>
+      </c>
+      <c r="E18" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="43" t="s">
+        <v>649</v>
+      </c>
+      <c r="H18" s="39">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>663</v>
+      </c>
+      <c r="B19" t="s">
+        <v>649</v>
+      </c>
+      <c r="C19" t="s">
+        <v>681</v>
+      </c>
+      <c r="D19" s="40">
+        <v>42156</v>
+      </c>
+      <c r="E19" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>11.1</v>
+      </c>
+      <c r="G19" s="43" t="s">
+        <v>650</v>
+      </c>
+      <c r="H19" s="39">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>663</v>
+      </c>
+      <c r="B20" t="s">
+        <v>650</v>
+      </c>
+      <c r="C20" t="s">
+        <v>681</v>
+      </c>
+      <c r="D20" s="40">
+        <v>44075</v>
+      </c>
+      <c r="E20" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>5.8</v>
+      </c>
+      <c r="G20" s="43" t="s">
+        <v>647</v>
+      </c>
+      <c r="H20" s="39">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>663</v>
+      </c>
+      <c r="B21" t="s">
+        <v>647</v>
+      </c>
+      <c r="C21" t="s">
+        <v>683</v>
+      </c>
+      <c r="D21" s="40">
+        <v>44562</v>
+      </c>
+      <c r="E21" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>4.5</v>
+      </c>
+      <c r="G21" s="43" t="s">
+        <v>640</v>
+      </c>
+      <c r="H21" s="39">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>663</v>
+      </c>
+      <c r="B22" t="s">
+        <v>640</v>
+      </c>
+      <c r="C22" t="s">
+        <v>682</v>
+      </c>
+      <c r="D22" s="40">
+        <v>45658</v>
+      </c>
+      <c r="E22" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>1.5</v>
+      </c>
+      <c r="G22" s="42" t="s">
+        <v>651</v>
+      </c>
+      <c r="H22" s="39">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>641</v>
+      </c>
+      <c r="B23" t="s">
+        <v>642</v>
+      </c>
+      <c r="C23" t="s">
+        <v>681</v>
+      </c>
+      <c r="D23" s="40">
+        <v>45292</v>
+      </c>
+      <c r="E23" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>2.5</v>
+      </c>
+      <c r="G23" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="H23" s="39">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>641</v>
+      </c>
+      <c r="B24" t="s">
+        <v>665</v>
+      </c>
+      <c r="C24" t="s">
+        <v>680</v>
+      </c>
+      <c r="D24" s="40">
+        <v>44927</v>
+      </c>
+      <c r="E24" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>3.5</v>
+      </c>
+      <c r="G24" s="43" t="s">
+        <v>653</v>
+      </c>
+      <c r="H24" s="39">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>641</v>
+      </c>
+      <c r="B25" t="s">
+        <v>666</v>
+      </c>
+      <c r="C25" t="s">
+        <v>682</v>
+      </c>
+      <c r="D25" s="40">
+        <v>46023</v>
+      </c>
+      <c r="E25" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G25" s="43" t="s">
+        <v>654</v>
+      </c>
+      <c r="H25" s="39">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>641</v>
+      </c>
+      <c r="B26" t="s">
+        <v>667</v>
+      </c>
+      <c r="C26" t="s">
+        <v>681</v>
+      </c>
+      <c r="D26" s="40">
+        <v>44562</v>
+      </c>
+      <c r="E26" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>4.5</v>
+      </c>
+      <c r="G26" s="42" t="s">
+        <v>641</v>
+      </c>
+      <c r="H26" s="39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>641</v>
+      </c>
+      <c r="B27" t="s">
+        <v>685</v>
+      </c>
+      <c r="C27" t="s">
+        <v>680</v>
+      </c>
+      <c r="D27" s="40">
+        <v>45658</v>
+      </c>
+      <c r="E27" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>1.5</v>
+      </c>
+      <c r="G27" s="43" t="s">
+        <v>667</v>
+      </c>
+      <c r="H27" s="39">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>641</v>
+      </c>
+      <c r="B28" t="s">
+        <v>686</v>
+      </c>
+      <c r="C28" t="s">
+        <v>680</v>
+      </c>
+      <c r="D28" s="40">
+        <v>45658</v>
+      </c>
+      <c r="E28" s="45">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>1.5</v>
+      </c>
+      <c r="G28" s="43" t="s">
+        <v>665</v>
+      </c>
+      <c r="H28" s="39">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G29" s="43" t="s">
+        <v>642</v>
+      </c>
+      <c r="H29" s="39">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G30" s="43" t="s">
+        <v>685</v>
+      </c>
+      <c r="H30" s="39">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G31" s="43" t="s">
+        <v>686</v>
+      </c>
+      <c r="H31" s="39">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G32" s="43" t="s">
+        <v>666</v>
+      </c>
+      <c r="H32" s="39">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G33" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="H33" s="39">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G34" s="43" t="s">
+        <v>679</v>
+      </c>
+      <c r="H34" s="39">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G35" s="42" t="s">
+        <v>645</v>
+      </c>
+      <c r="H35" s="39">
+        <v>121.09999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C28" xr:uid="{E4AEB1FF-66B5-4FE5-B190-7572A8D46C61}">
+      <formula1>"Learning,Intermediate,Advanced,Expert,Instructor"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/cv_zmm.xlsx
+++ b/cv_zmm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wcs1-my.sharepoint.com/personal/zmoore_wcs_org/Documents/Data/r projects/zacharymilosmoore.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="579" documentId="14_{08B98A92-493A-4C26-8167-4BB5471433C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E980225-29A6-4FB7-84AE-211EF1DB5A99}"/>
+  <xr:revisionPtr revIDLastSave="659" documentId="14_{08B98A92-493A-4C26-8167-4BB5471433C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{114AD122-2A1A-430A-A489-49BE8314D488}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4154936E-D054-4D45-B3AE-FD317E846EC6}"/>
   </bookViews>
@@ -35,7 +35,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="21" r:id="rId4"/>
+    <pivotCache cacheId="25" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="690">
   <si>
     <t>Category</t>
   </si>
@@ -792,9 +792,6 @@
   </si>
   <si>
     <t>Conducted scientific literature reviews and experiments.</t>
-  </si>
-  <si>
-    <t>Presented results at three scientific conferences. Awarded two undergraduate student research awards (USRAs).</t>
   </si>
   <si>
     <t>Scientific Researcher: Population and Community Ecology</t>
@@ -1916,9 +1913,6 @@
     <t xml:space="preserve">Learned how to identify own epistemological biases. Improved skills in scientific study design. Linked theoretical ecological concepts to conservation management. </t>
   </si>
   <si>
-    <t>Short term contract conducting data analyses and consulting on data management protocols.</t>
-  </si>
-  <si>
     <t>North America Regional Director</t>
   </si>
   <si>
@@ -2021,9 +2015,6 @@
     <t>Python</t>
   </si>
   <si>
-    <t>Experience (Years)</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -2151,6 +2142,21 @@
   </si>
   <si>
     <t>Years of Professional Exposure</t>
+  </si>
+  <si>
+    <t>Published one peer-reveiwed article in a prestigious scientific journal. Presented results at three scientific conferences. Awarded two undergraduate student research awards (USRAs).</t>
+  </si>
+  <si>
+    <t>Short term contract conducting analyses and consulting on data management protocols.</t>
+  </si>
+  <si>
+    <t>Professional Exposure (Years)</t>
+  </si>
+  <si>
+    <t>ArcGIS Dashboards</t>
+  </si>
+  <si>
+    <t>Basic Scripting</t>
   </si>
 </sst>
 </file>
@@ -2352,7 +2358,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2446,7 +2452,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2972,6 +2977,12 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -3778,12 +3789,6 @@
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="yyyy"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3873,6 +3878,62 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -3906,110 +3967,116 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Skills!$G$2:$G$35</c:f>
+              <c:f>Skills!$G$2:$G$37</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="29"/>
                 <c:lvl>
                   <c:pt idx="0">
+                    <c:v>Database Design</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>PostgreSQL</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Microsoft SQL Server</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Database Management</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Database Maintenance</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>MySQL</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Tabular Data</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Spatial Data</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>R Markdown</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Shiny</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Basic Scripting</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>ArcGIS Toolbox Development</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
                     <c:v>Basic Word</c:v>
                   </c:pt>
-                  <c:pt idx="1">
+                  <c:pt idx="13">
                     <c:v>Basic Excel</c:v>
                   </c:pt>
-                  <c:pt idx="2">
+                  <c:pt idx="14">
                     <c:v>Mail Merge</c:v>
                   </c:pt>
-                  <c:pt idx="3">
+                  <c:pt idx="15">
                     <c:v>Power Pivot</c:v>
                   </c:pt>
-                  <c:pt idx="4">
+                  <c:pt idx="16">
                     <c:v>VBA (Macros)</c:v>
                   </c:pt>
-                  <c:pt idx="5">
+                  <c:pt idx="17">
                     <c:v>Power Query</c:v>
                   </c:pt>
-                  <c:pt idx="6">
+                  <c:pt idx="18">
                     <c:v>Power BI</c:v>
                   </c:pt>
-                  <c:pt idx="7">
+                  <c:pt idx="19">
+                    <c:v>Personal Projects</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>Pages &amp; Website Development</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>Organizational Projects</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
                     <c:v>ArcGIS Pro</c:v>
                   </c:pt>
-                  <c:pt idx="8">
+                  <c:pt idx="23">
                     <c:v>Avenza (Survey Design)</c:v>
                   </c:pt>
-                  <c:pt idx="9">
+                  <c:pt idx="24">
                     <c:v>QGIS</c:v>
                   </c:pt>
-                  <c:pt idx="10">
+                  <c:pt idx="25">
                     <c:v>ESRI Field Maps (Survey Design)</c:v>
                   </c:pt>
-                  <c:pt idx="11">
+                  <c:pt idx="26">
+                    <c:v>ArcGIS Dashboards</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
                     <c:v>QField (Survey Design)</c:v>
                   </c:pt>
-                  <c:pt idx="12">
+                  <c:pt idx="28">
                     <c:v>Survey123 (Survey Design)</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>Tabular Data</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>Spatial Data</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>R Markdown</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>Shiny</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>Personal Projects</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>Pages &amp; Website Development</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>Organizational Projects</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>Database Design</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>PostgreSQL</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>Microsoft SQL Server</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>Database Management</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>Database Maintenance</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>MySQL</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>ArcGIS Toolbox Development</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
+                    <c:v>SQL</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>R</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Python</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
                     <c:v>MS Office</c:v>
                   </c:pt>
-                  <c:pt idx="7">
-                    <c:v>GIS</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>R</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
+                  <c:pt idx="19">
                     <c:v>GitHub</c:v>
                   </c:pt>
-                  <c:pt idx="20">
-                    <c:v>SQL</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>Python</c:v>
+                  <c:pt idx="22">
+                    <c:v>GIS</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -4017,97 +4084,103 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Skills!$H$2:$H$35</c:f>
+              <c:f>Skills!$H$2:$H$37</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>12.799999999999999</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.799999999999999</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>5.5</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="15">
                   <c:v>2.5</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="16">
                   <c:v>2.5</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="17">
                   <c:v>2.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="18">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="19">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>7.8</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="23">
                   <c:v>6.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="24">
                   <c:v>6.8</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="25">
                   <c:v>5.8</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="26">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>0.79999999999999993</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="28">
                   <c:v>0.79999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>11.1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5.8</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5.8</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-78E3-4244-8382-0D6F7E73C5DA}"/>
+              <c16:uniqueId val="{00000000-6B9F-4754-BEF0-45F5A36552FE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4216,8 +4289,13 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-CA"/>
-                  <a:t>Years of Experience</a:t>
+                  <a:t>Years of</a:t>
                 </a:r>
+                <a:r>
+                  <a:rPr lang="en-CA" baseline="0"/>
+                  <a:t> Professional Exposure</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-CA"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -4901,15 +4979,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>65314</xdr:colOff>
+      <xdr:colOff>108857</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>60414</xdr:rowOff>
+      <xdr:rowOff>5986</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>446314</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>54427</xdr:rowOff>
+      <xdr:colOff>489857</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4944,7 +5022,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Moore, Zachary" refreshedDate="46188.488545717591" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="27" xr:uid="{F6ED3B8B-1A78-4223-A864-14D164002041}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Moore, Zachary" refreshedDate="46188.572499884256" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="29" xr:uid="{F6ED3B8B-1A78-4223-A864-14D164002041}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table2"/>
   </cacheSource>
@@ -4970,13 +5048,14 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Skill" numFmtId="0">
-      <sharedItems containsBlank="1" count="38">
+      <sharedItems containsBlank="1" count="40">
         <s v="ArcGIS Pro"/>
         <s v="QGIS"/>
         <s v="ESRI Field Maps (Survey Design)"/>
         <s v="Survey123 (Survey Design)"/>
         <s v="Avenza (Survey Design)"/>
         <s v="QField (Survey Design)"/>
+        <s v="ArcGIS Dashboards"/>
         <s v="Personal Projects"/>
         <s v="Pages &amp; Website Development"/>
         <s v="Organizational Projects"/>
@@ -4988,6 +5067,7 @@
         <s v="Power Pivot"/>
         <s v="VBA (Macros)"/>
         <s v="ArcGIS Toolbox Development"/>
+        <s v="Basic Scripting"/>
         <s v="Tabular Data"/>
         <s v="Spatial Data"/>
         <s v="R Markdown"/>
@@ -5015,10 +5095,10 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Start" numFmtId="165">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2013-09-01T00:00:00" maxDate="2026-01-02T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2015-01-01T00:00:00" maxDate="2026-01-02T00:00:00"/>
     </cacheField>
-    <cacheField name="Years of Experience" numFmtId="166">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.5" maxValue="12.799999999999999"/>
+    <cacheField name="Years of Professional Exposure" numFmtId="166">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.5" maxValue="11.5"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -5030,7 +5110,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="27">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="29">
   <r>
     <x v="0"/>
     <x v="0"/>
@@ -5074,148 +5154,162 @@
     <n v="0.79999999999999993"/>
   </r>
   <r>
+    <x v="0"/>
+    <x v="6"/>
+    <s v="Expert"/>
+    <d v="2023-01-01T00:00:00"/>
+    <n v="3.5"/>
+  </r>
+  <r>
     <x v="1"/>
-    <x v="6"/>
+    <x v="7"/>
     <s v="Intermediate"/>
     <d v="2020-09-01T00:00:00"/>
     <n v="5.8"/>
   </r>
   <r>
     <x v="1"/>
-    <x v="7"/>
+    <x v="8"/>
     <s v="Advanced"/>
     <d v="2021-01-01T00:00:00"/>
     <n v="5.5"/>
   </r>
   <r>
     <x v="1"/>
-    <x v="8"/>
+    <x v="9"/>
     <s v="Intermediate"/>
     <d v="2022-01-01T00:00:00"/>
     <n v="4.5"/>
   </r>
   <r>
     <x v="2"/>
-    <x v="9"/>
-    <s v="Instructor"/>
-    <d v="2013-09-01T00:00:00"/>
-    <n v="12.799999999999999"/>
-  </r>
-  <r>
-    <x v="2"/>
     <x v="10"/>
     <s v="Instructor"/>
-    <d v="2013-09-01T00:00:00"/>
-    <n v="12.799999999999999"/>
+    <d v="2015-01-01T00:00:00"/>
+    <n v="11.5"/>
   </r>
   <r>
     <x v="2"/>
     <x v="11"/>
+    <s v="Instructor"/>
+    <d v="2015-01-01T00:00:00"/>
+    <n v="11.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="12"/>
     <s v="Intermediate"/>
     <d v="2021-01-01T00:00:00"/>
     <n v="5.5"/>
   </r>
   <r>
     <x v="2"/>
-    <x v="12"/>
+    <x v="13"/>
     <s v="Instructor"/>
     <d v="2024-01-01T00:00:00"/>
     <n v="2.5"/>
   </r>
   <r>
     <x v="2"/>
-    <x v="13"/>
+    <x v="14"/>
     <s v="Learning"/>
     <d v="2026-01-01T00:00:00"/>
     <n v="0.5"/>
   </r>
   <r>
     <x v="2"/>
-    <x v="14"/>
+    <x v="15"/>
     <s v="Intermediate"/>
     <d v="2024-01-01T00:00:00"/>
     <n v="2.5"/>
   </r>
   <r>
     <x v="2"/>
-    <x v="15"/>
+    <x v="16"/>
     <s v="Learning"/>
     <d v="2024-01-01T00:00:00"/>
     <n v="2.5"/>
   </r>
   <r>
     <x v="3"/>
-    <x v="16"/>
+    <x v="17"/>
     <s v="Learning"/>
     <d v="2026-01-01T00:00:00"/>
     <n v="0.5"/>
   </r>
   <r>
+    <x v="3"/>
+    <x v="18"/>
+    <s v="Intermediate"/>
+    <d v="2025-01-01T00:00:00"/>
+    <n v="1.5"/>
+  </r>
+  <r>
     <x v="4"/>
-    <x v="17"/>
+    <x v="19"/>
     <s v="Instructor"/>
     <d v="2015-06-01T00:00:00"/>
     <n v="11.1"/>
   </r>
   <r>
     <x v="4"/>
-    <x v="18"/>
+    <x v="20"/>
     <s v="Instructor"/>
     <d v="2020-09-01T00:00:00"/>
     <n v="5.8"/>
   </r>
   <r>
     <x v="4"/>
-    <x v="19"/>
+    <x v="21"/>
     <s v="Advanced"/>
     <d v="2022-01-01T00:00:00"/>
     <n v="4.5"/>
   </r>
   <r>
     <x v="4"/>
-    <x v="20"/>
+    <x v="22"/>
     <s v="Learning"/>
     <d v="2025-01-01T00:00:00"/>
     <n v="1.5"/>
   </r>
   <r>
     <x v="5"/>
-    <x v="21"/>
+    <x v="23"/>
     <s v="Instructor"/>
     <d v="2024-01-01T00:00:00"/>
     <n v="2.5"/>
   </r>
   <r>
     <x v="5"/>
-    <x v="22"/>
+    <x v="24"/>
     <s v="Intermediate"/>
     <d v="2023-01-01T00:00:00"/>
     <n v="3.5"/>
   </r>
   <r>
     <x v="5"/>
-    <x v="23"/>
+    <x v="25"/>
     <s v="Learning"/>
     <d v="2026-01-01T00:00:00"/>
     <n v="0.5"/>
   </r>
   <r>
     <x v="5"/>
-    <x v="24"/>
+    <x v="26"/>
     <s v="Instructor"/>
     <d v="2022-01-01T00:00:00"/>
     <n v="4.5"/>
   </r>
   <r>
     <x v="5"/>
-    <x v="25"/>
+    <x v="27"/>
     <s v="Intermediate"/>
     <d v="2025-01-01T00:00:00"/>
     <n v="1.5"/>
   </r>
   <r>
     <x v="5"/>
-    <x v="26"/>
+    <x v="28"/>
     <s v="Intermediate"/>
     <d v="2025-01-01T00:00:00"/>
     <n v="1.5"/>
@@ -5224,79 +5318,72 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D2C8C371-0CF2-4E47-B790-EF157E0D2441}" name="PivotTable1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Categories">
-  <location ref="G1:H35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D2C8C371-0CF2-4E47-B790-EF157E0D2441}" name="PivotTable1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Categories">
+  <location ref="G1:H37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="17">
+        <item m="1" x="11"/>
+        <item x="5"/>
+        <item m="1" x="10"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item m="1" x="14"/>
+        <item m="1" x="9"/>
+        <item m="1" x="13"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item m="1" x="7"/>
+        <item m="1" x="15"/>
         <item m="1" x="8"/>
-        <item m="1" x="15"/>
-        <item m="1" x="7"/>
-        <item m="1" x="10"/>
-        <item m="1" x="13"/>
+        <item m="1" x="6"/>
         <item m="1" x="12"/>
-        <item m="1" x="14"/>
-        <item x="1"/>
-        <item m="1" x="9"/>
-        <item m="1" x="11"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item m="1" x="6"/>
         <item t="default"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
     </pivotField>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="39">
-        <item m="1" x="35"/>
+      <items count="41">
+        <item m="1" x="37"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item m="1" x="39"/>
+        <item m="1" x="38"/>
+        <item m="1" x="31"/>
+        <item x="0"/>
         <item x="21"/>
+        <item m="1" x="36"/>
+        <item x="19"/>
         <item x="20"/>
-        <item m="1" x="37"/>
-        <item m="1" x="36"/>
-        <item m="1" x="29"/>
-        <item x="0"/>
-        <item x="19"/>
-        <item m="1" x="34"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="6"/>
         <item x="7"/>
         <item x="8"/>
         <item x="9"/>
         <item x="10"/>
-        <item x="22"/>
-        <item x="23"/>
+        <item x="11"/>
         <item x="24"/>
-        <item x="11"/>
+        <item x="25"/>
+        <item x="26"/>
         <item x="12"/>
         <item x="13"/>
+        <item x="14"/>
         <item x="1"/>
-        <item m="1" x="31"/>
-        <item m="1" x="32"/>
         <item m="1" x="33"/>
+        <item m="1" x="34"/>
+        <item m="1" x="35"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
-        <item m="1" x="30"/>
-        <item x="14"/>
+        <item m="1" x="32"/>
         <item x="15"/>
         <item x="16"/>
-        <item m="1" x="27"/>
-        <item m="1" x="28"/>
-        <item x="25"/>
-        <item x="26"/>
+        <item x="17"/>
+        <item m="1" x="29"/>
+        <item m="1" x="30"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="6"/>
+        <item x="18"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -5311,15 +5398,60 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="2" showAll="0"/>
+    <pivotField dataField="1" numFmtId="166" showAll="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
     <field x="1"/>
   </rowFields>
-  <rowItems count="34">
+  <rowItems count="36">
     <i>
-      <x v="11"/>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="36"/>
+    </i>
+    <i r="1">
+      <x v="37"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="39"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i r="1">
       <x v="15"/>
@@ -5343,6 +5475,18 @@
       <x v="21"/>
     </i>
     <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i>
       <x v="10"/>
     </i>
     <i r="1">
@@ -5358,64 +5502,13 @@
       <x v="26"/>
     </i>
     <i r="1">
+      <x v="38"/>
+    </i>
+    <i r="1">
       <x v="29"/>
     </i>
     <i r="1">
       <x v="27"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-    </i>
-    <i r="1">
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i r="1">
-      <x v="18"/>
-    </i>
-    <i r="1">
-      <x v="16"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="36"/>
-    </i>
-    <i r="1">
-      <x v="37"/>
-    </i>
-    <i r="1">
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i r="1">
-      <x v="33"/>
     </i>
     <i t="grand">
       <x/>
@@ -5425,10 +5518,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Experience (Years)" fld="4" baseField="0" baseItem="0" numFmtId="2"/>
+    <dataField name="Professional Exposure (Years)" fld="4" baseField="0" baseItem="0" numFmtId="166"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="5" format="0" series="1">
+    <chartFormat chart="5" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5451,62 +5544,62 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E6C429B5-94AF-4DF8-8EEB-230783D5C112}" name="cv.table" displayName="cv.table" ref="A1:AN92" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E6C429B5-94AF-4DF8-8EEB-230783D5C112}" name="cv.table" displayName="cv.table" ref="A1:AN92" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
   <autoFilter ref="A1:AN92" xr:uid="{51C5574A-10F4-4984-BAF7-4488D8AC8419}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AM92">
     <sortCondition ref="I1:I92"/>
   </sortState>
   <tableColumns count="40">
-    <tableColumn id="7" xr3:uid="{EC86C6DE-554D-4F33-AEC2-DF6E1CA6068F}" name="Organization" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{26CD9B61-38AB-4312-B98A-E2A336BF9AB7}" name="Org_Acr" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{2BE7F400-F53C-40A9-BB7D-530918FE5571}" name="Title" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{33E88F9D-A2A0-44DD-84D2-308042D95210}" name="Title_Acr" dataDxfId="58"/>
-    <tableColumn id="26" xr3:uid="{9B11C92F-E956-4444-BEFF-953F753416F5}" name="CV" dataDxfId="57"/>
-    <tableColumn id="11" xr3:uid="{34502BA5-FB1E-4B40-8788-421DADDD3E97}" name="Branch" dataDxfId="56"/>
-    <tableColumn id="1" xr3:uid="{70612BCC-1448-430F-9D24-28D063F5A2A3}" name="Category" dataDxfId="55"/>
-    <tableColumn id="18" xr3:uid="{5E4EDA0C-2B9B-42CE-A32B-4403948C8E7B}" name="Type" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{6738E286-0938-42F9-B68F-D49892936B3D}" name="Start" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{F83278BD-725D-4108-95A1-F217E27DC898}" name="End" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{802621DE-7866-4555-8E12-DD03949FA7E7}" name="Start_Month" dataDxfId="51">
+    <tableColumn id="7" xr3:uid="{EC86C6DE-554D-4F33-AEC2-DF6E1CA6068F}" name="Organization" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{26CD9B61-38AB-4312-B98A-E2A336BF9AB7}" name="Org_Acr" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{2BE7F400-F53C-40A9-BB7D-530918FE5571}" name="Title" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{33E88F9D-A2A0-44DD-84D2-308042D95210}" name="Title_Acr" dataDxfId="60"/>
+    <tableColumn id="26" xr3:uid="{9B11C92F-E956-4444-BEFF-953F753416F5}" name="CV" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{34502BA5-FB1E-4B40-8788-421DADDD3E97}" name="Branch" dataDxfId="58"/>
+    <tableColumn id="1" xr3:uid="{70612BCC-1448-430F-9D24-28D063F5A2A3}" name="Category" dataDxfId="57"/>
+    <tableColumn id="18" xr3:uid="{5E4EDA0C-2B9B-42CE-A32B-4403948C8E7B}" name="Type" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{6738E286-0938-42F9-B68F-D49892936B3D}" name="Start" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{F83278BD-725D-4108-95A1-F217E27DC898}" name="End" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{802621DE-7866-4555-8E12-DD03949FA7E7}" name="Start_Month" dataDxfId="53">
       <calculatedColumnFormula>MONTH(cv.table[[#This Row],[Start]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{C6566D99-33F8-4C29-9F77-57CB96E0A79F}" name="Start_Year" dataDxfId="50">
+    <tableColumn id="20" xr3:uid="{C6566D99-33F8-4C29-9F77-57CB96E0A79F}" name="Start_Year" dataDxfId="52">
       <calculatedColumnFormula>YEAR(cv.table[[#This Row],[Start]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{6BF152A0-7851-42D9-985D-3CC266F2660D}" name="End_Month" dataDxfId="49">
+    <tableColumn id="22" xr3:uid="{6BF152A0-7851-42D9-985D-3CC266F2660D}" name="End_Month" dataDxfId="51">
       <calculatedColumnFormula>MONTH(cv.table[[#This Row],[End]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{FEEC95E2-B833-448E-AC76-6DBAE4E45591}" name="End_Year" dataDxfId="48">
+    <tableColumn id="21" xr3:uid="{FEEC95E2-B833-448E-AC76-6DBAE4E45591}" name="End_Year" dataDxfId="50">
       <calculatedColumnFormula>YEAR(cv.table[[#This Row],[End]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7BB222DF-5EE2-4BC9-9EF1-E1A53AFE31F4}" name="Time" dataDxfId="47">
+    <tableColumn id="5" xr3:uid="{7BB222DF-5EE2-4BC9-9EF1-E1A53AFE31F4}" name="Time" dataDxfId="49">
       <calculatedColumnFormula>IF((P2="Days"),((J2-I2+1)),IF(P2="Months",((J2-I2)/30),((J2-I2)/365)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{436D180E-D520-4622-BF48-C117C2F3D72D}" name="Time_Unit" dataDxfId="46"/>
-    <tableColumn id="14" xr3:uid="{0AC0D461-4004-4A64-B5A7-5BCBB135C7C9}" name="Loc_Small" dataDxfId="45"/>
-    <tableColumn id="15" xr3:uid="{604F7BAB-42A3-455E-8C18-202B68AEBC37}" name="Loc_Large" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{1CAEFFF7-88CF-4AB8-88EF-1DC65D78A14C}" name="Description" dataDxfId="43"/>
-    <tableColumn id="19" xr3:uid="{B4A2DCCB-9505-42D1-97AE-1B44581F30F1}" name="Tasks" dataDxfId="42"/>
-    <tableColumn id="16" xr3:uid="{9AA8F708-1C30-48AB-8EDD-8C5BF442D6ED}" name="Lessons" dataDxfId="41"/>
-    <tableColumn id="17" xr3:uid="{CAB8C078-3C62-4846-9AC3-0B17AD693416}" name="Achievements" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{982B9A83-407B-47DD-AE12-B9AF5B9B6C73}" name="Notes" dataDxfId="39"/>
-    <tableColumn id="23" xr3:uid="{4C96C715-152C-4914-BB38-FEFF25E58297}" name="M1" dataDxfId="38"/>
-    <tableColumn id="31" xr3:uid="{ABB7B8F1-D658-471C-B518-50B31EDEA024}" name="M1_Type" dataDxfId="37"/>
-    <tableColumn id="25" xr3:uid="{AB48772A-9139-4A74-BF34-9532AF007D28}" name="M1_Desc" dataDxfId="36"/>
-    <tableColumn id="27" xr3:uid="{AA368EEC-19E0-4A9A-90A5-B309B7AE3A50}" name="M2" dataDxfId="35"/>
-    <tableColumn id="39" xr3:uid="{CDFAF1DD-71C7-4BE5-985F-753C0AC61716}" name="M2_Type" dataDxfId="34"/>
-    <tableColumn id="28" xr3:uid="{65DF71FF-E9EE-4AAB-A467-1B0F813F20A6}" name="M2_Desc" dataDxfId="33"/>
-    <tableColumn id="29" xr3:uid="{C2677FEE-8349-4A02-B596-66E45AD44952}" name="M3" dataDxfId="32"/>
-    <tableColumn id="38" xr3:uid="{70C3692F-FB1A-483A-8240-B37C7497B7B9}" name="M3_Type" dataDxfId="31"/>
-    <tableColumn id="30" xr3:uid="{1E758BB4-3C89-4653-80DA-C549531B5244}" name="M3_Desc" dataDxfId="30"/>
-    <tableColumn id="32" xr3:uid="{FEE44D7E-69A0-4B71-AB66-1461C45267FF}" name="L1" dataDxfId="29"/>
-    <tableColumn id="33" xr3:uid="{21C268AA-32E8-4627-82E0-7A62468157B5}" name="L1_Desc" dataDxfId="28"/>
-    <tableColumn id="34" xr3:uid="{E85C2701-53A9-4B93-B733-9B7CD3138938}" name="L2" dataDxfId="27"/>
-    <tableColumn id="35" xr3:uid="{8E33C990-20D6-41EA-81EB-AF8C09425D76}" name="L2_Desc" dataDxfId="26"/>
-    <tableColumn id="36" xr3:uid="{FF798E68-0DB4-421A-AE12-25569247C412}" name="L3" dataDxfId="25"/>
-    <tableColumn id="37" xr3:uid="{BF4D3938-CF08-433F-8B81-A515F3E1BBB7}" name="L3_Desc" dataDxfId="24"/>
-    <tableColumn id="40" xr3:uid="{253CE8A7-249E-41AF-AF8F-0BF5333B36DA}" name="Org_Link" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{7227EDDE-23E8-491F-9948-DDACA373C3A1}" name="CV_List" dataDxfId="22">
+    <tableColumn id="6" xr3:uid="{436D180E-D520-4622-BF48-C117C2F3D72D}" name="Time_Unit" dataDxfId="48"/>
+    <tableColumn id="14" xr3:uid="{0AC0D461-4004-4A64-B5A7-5BCBB135C7C9}" name="Loc_Small" dataDxfId="47"/>
+    <tableColumn id="15" xr3:uid="{604F7BAB-42A3-455E-8C18-202B68AEBC37}" name="Loc_Large" dataDxfId="46"/>
+    <tableColumn id="12" xr3:uid="{1CAEFFF7-88CF-4AB8-88EF-1DC65D78A14C}" name="Description" dataDxfId="45"/>
+    <tableColumn id="19" xr3:uid="{B4A2DCCB-9505-42D1-97AE-1B44581F30F1}" name="Tasks" dataDxfId="44"/>
+    <tableColumn id="16" xr3:uid="{9AA8F708-1C30-48AB-8EDD-8C5BF442D6ED}" name="Lessons" dataDxfId="43"/>
+    <tableColumn id="17" xr3:uid="{CAB8C078-3C62-4846-9AC3-0B17AD693416}" name="Achievements" dataDxfId="42"/>
+    <tableColumn id="13" xr3:uid="{982B9A83-407B-47DD-AE12-B9AF5B9B6C73}" name="Notes" dataDxfId="41"/>
+    <tableColumn id="23" xr3:uid="{4C96C715-152C-4914-BB38-FEFF25E58297}" name="M1" dataDxfId="40"/>
+    <tableColumn id="31" xr3:uid="{ABB7B8F1-D658-471C-B518-50B31EDEA024}" name="M1_Type" dataDxfId="39"/>
+    <tableColumn id="25" xr3:uid="{AB48772A-9139-4A74-BF34-9532AF007D28}" name="M1_Desc" dataDxfId="38"/>
+    <tableColumn id="27" xr3:uid="{AA368EEC-19E0-4A9A-90A5-B309B7AE3A50}" name="M2" dataDxfId="37"/>
+    <tableColumn id="39" xr3:uid="{CDFAF1DD-71C7-4BE5-985F-753C0AC61716}" name="M2_Type" dataDxfId="36"/>
+    <tableColumn id="28" xr3:uid="{65DF71FF-E9EE-4AAB-A467-1B0F813F20A6}" name="M2_Desc" dataDxfId="35"/>
+    <tableColumn id="29" xr3:uid="{C2677FEE-8349-4A02-B596-66E45AD44952}" name="M3" dataDxfId="34"/>
+    <tableColumn id="38" xr3:uid="{70C3692F-FB1A-483A-8240-B37C7497B7B9}" name="M3_Type" dataDxfId="33"/>
+    <tableColumn id="30" xr3:uid="{1E758BB4-3C89-4653-80DA-C549531B5244}" name="M3_Desc" dataDxfId="32"/>
+    <tableColumn id="32" xr3:uid="{FEE44D7E-69A0-4B71-AB66-1461C45267FF}" name="L1" dataDxfId="31"/>
+    <tableColumn id="33" xr3:uid="{21C268AA-32E8-4627-82E0-7A62468157B5}" name="L1_Desc" dataDxfId="30"/>
+    <tableColumn id="34" xr3:uid="{E85C2701-53A9-4B93-B733-9B7CD3138938}" name="L2" dataDxfId="29"/>
+    <tableColumn id="35" xr3:uid="{8E33C990-20D6-41EA-81EB-AF8C09425D76}" name="L2_Desc" dataDxfId="28"/>
+    <tableColumn id="36" xr3:uid="{FF798E68-0DB4-421A-AE12-25569247C412}" name="L3" dataDxfId="27"/>
+    <tableColumn id="37" xr3:uid="{BF4D3938-CF08-433F-8B81-A515F3E1BBB7}" name="L3_Desc" dataDxfId="26"/>
+    <tableColumn id="40" xr3:uid="{253CE8A7-249E-41AF-AF8F-0BF5333B36DA}" name="Org_Link" dataDxfId="25"/>
+    <tableColumn id="24" xr3:uid="{7227EDDE-23E8-491F-9948-DDACA373C3A1}" name="CV_List" dataDxfId="24">
       <calculatedColumnFormula>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5515,17 +5608,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EA82C731-37AB-4BD9-A9C7-425663939105}" name="Table2" displayName="Table2" ref="A1:E28" totalsRowShown="0">
-  <autoFilter ref="A1:E28" xr:uid="{EA82C731-37AB-4BD9-A9C7-425663939105}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E26">
-    <sortCondition ref="A1:A26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EA82C731-37AB-4BD9-A9C7-425663939105}" name="Table2" displayName="Table2" ref="A1:E30" totalsRowShown="0">
+  <autoFilter ref="A1:E30" xr:uid="{EA82C731-37AB-4BD9-A9C7-425663939105}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E30">
+    <sortCondition ref="A1:A30"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{DDB5D190-EAF5-4053-B13F-BF9B72D0EA69}" name="Category"/>
     <tableColumn id="2" xr3:uid="{2523D3CF-788F-45BB-B72F-086EF71557AB}" name="Skill"/>
     <tableColumn id="8" xr3:uid="{B9516D00-F602-459E-9ACF-C72D7D50B6E6}" name="Self-identified Level"/>
-    <tableColumn id="3" xr3:uid="{7E897B0B-F15B-4405-9756-3C2BCA461366}" name="Start" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{D69837BC-B8F5-4FBC-AA68-E8F2B0D0C8D5}" name="Years of Professional Exposure" dataDxfId="64">
+    <tableColumn id="3" xr3:uid="{7E897B0B-F15B-4405-9756-3C2BCA461366}" name="Start" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{D69837BC-B8F5-4FBC-AA68-E8F2B0D0C8D5}" name="Years of Professional Exposure" dataDxfId="22">
       <calculatedColumnFormula>ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5918,7 +6011,7 @@
         <v>78</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>227</v>
@@ -5978,55 +6071,55 @@
         <v>9</v>
       </c>
       <c r="X1" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="Y1" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="AF1" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="AG1" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AH1" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="AL1" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="AM1" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="2" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
@@ -6039,7 +6132,7 @@
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F2" s="17" t="s">
         <v>65</v>
@@ -6086,13 +6179,13 @@
         <v>51</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="T2" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="U2" s="17" t="s">
         <v>241</v>
-      </c>
-      <c r="U2" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="V2" s="24"/>
       <c r="W2" s="24"/>
@@ -6112,7 +6205,7 @@
       <c r="AK2" s="17"/>
       <c r="AL2" s="24"/>
       <c r="AM2" s="18"/>
-      <c r="AN2" s="44" t="str">
+      <c r="AN2" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Line Kitchen Staff (Various Restaurants)</v>
       </c>
@@ -6129,10 +6222,10 @@
       </c>
       <c r="D3" s="25"/>
       <c r="E3" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G3" s="17" t="s">
         <v>30</v>
@@ -6196,7 +6289,7 @@
       <c r="AK3" s="17"/>
       <c r="AL3" s="24"/>
       <c r="AM3" s="18"/>
-      <c r="AN3" s="44" t="str">
+      <c r="AN3" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>General Labourer (DMA Contracting)</v>
       </c>
@@ -6211,13 +6304,13 @@
       </c>
       <c r="D4" s="25"/>
       <c r="E4" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H4" s="24" t="s">
         <v>134</v>
@@ -6280,16 +6373,16 @@
       <c r="AK4" s="17"/>
       <c r="AL4" s="24"/>
       <c r="AM4" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="AN4" s="44" t="str">
+        <v>333</v>
+      </c>
+      <c r="AN4" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Defensive Driving Course (Young Driver's of Canada)</v>
       </c>
     </row>
     <row r="5" spans="1:40" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="18" t="s">
@@ -6303,7 +6396,7 @@
         <v>77</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H5" s="24" t="s">
         <v>134</v>
@@ -6313,7 +6406,7 @@
       </c>
       <c r="J5" s="22">
         <f ca="1">NOW()</f>
-        <v>46188.50092766204</v>
+        <v>46188.572873032404</v>
       </c>
       <c r="K5" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -6333,7 +6426,7 @@
       </c>
       <c r="O5" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>13.965755966197371</v>
+        <v>13.965953076801108</v>
       </c>
       <c r="P5" s="17" t="s">
         <v>28</v>
@@ -6365,9 +6458,9 @@
       <c r="AK5" s="17"/>
       <c r="AL5" s="24"/>
       <c r="AM5" s="26" t="s">
-        <v>338</v>
-      </c>
-      <c r="AN5" s="44" t="str">
+        <v>337</v>
+      </c>
+      <c r="AN5" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Ontario G-Class Driver's Licence (Ontario Ministry of Transportation)</v>
       </c>
@@ -6387,7 +6480,7 @@
         <v>228</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>30</v>
@@ -6434,10 +6527,10 @@
         <v>231</v>
       </c>
       <c r="T6" s="17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="U6" s="17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="V6" s="24" t="s">
         <v>232</v>
@@ -6461,7 +6554,7 @@
       <c r="AK6" s="17"/>
       <c r="AL6" s="24"/>
       <c r="AM6" s="17"/>
-      <c r="AN6" s="44" t="str">
+      <c r="AN6" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Service Technician/ Health and Safety Inspector (MBM Installations Inc.)</v>
       </c>
@@ -6527,16 +6620,16 @@
         <v>51</v>
       </c>
       <c r="S7" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="T7" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="U7" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="V7" s="24" t="s">
         <v>245</v>
-      </c>
-      <c r="T7" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="U7" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="V7" s="24" t="s">
-        <v>246</v>
       </c>
       <c r="W7" s="24"/>
       <c r="X7" s="17"/>
@@ -6555,9 +6648,9 @@
       <c r="AK7" s="17"/>
       <c r="AL7" s="24"/>
       <c r="AM7" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN7" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN7" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Honour's Bachelor of Arts and Science (University of Toronto)</v>
       </c>
@@ -6570,7 +6663,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="17" t="s">
@@ -6621,7 +6714,7 @@
         <v>51</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T8" s="17"/>
       <c r="U8" s="17"/>
@@ -6643,14 +6736,14 @@
       <c r="AK8" s="17"/>
       <c r="AL8" s="24"/>
       <c r="AM8" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN8" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN8" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Research Assistant (Agrawal Lab) (University of Toronto)</v>
       </c>
     </row>
-    <row r="9" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" ht="66" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>7</v>
       </c>
@@ -6658,7 +6751,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="17" t="s">
@@ -6671,7 +6764,7 @@
         <v>30</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I9" s="22">
         <v>42125</v>
@@ -6718,7 +6811,7 @@
         <v>236</v>
       </c>
       <c r="V9" s="24" t="s">
-        <v>239</v>
+        <v>685</v>
       </c>
       <c r="W9" s="24"/>
       <c r="X9" s="17"/>
@@ -6737,9 +6830,9 @@
       <c r="AK9" s="17"/>
       <c r="AL9" s="24"/>
       <c r="AM9" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN9" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN9" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Scientific Researcher: Population and Community Ecology (University of Toronto)</v>
       </c>
@@ -6752,19 +6845,19 @@
         <v>18</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D10" s="25" t="s">
         <v>139</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>140</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>185</v>
@@ -6796,7 +6889,7 @@
         <v>1.2547945205479452</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q10" s="17" t="s">
         <v>52</v>
@@ -6805,61 +6898,61 @@
         <v>51</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="V10" s="24" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="W10" s="24"/>
       <c r="X10" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y10" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z10" s="24" t="s">
         <v>367</v>
       </c>
-      <c r="Y10" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z10" s="24" t="s">
-        <v>368</v>
-      </c>
       <c r="AA10" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AB10" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AC10" s="24" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AD10" s="17"/>
       <c r="AE10" s="17"/>
       <c r="AF10" s="24"/>
       <c r="AG10" s="27" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AH10" s="24" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AI10" s="28" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AJ10" s="24" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AK10" s="26" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AL10" s="24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AM10" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN10" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN10" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Daphnia Fishery: Experimental Population Destabilization from Harvesting (University of Toronto)</v>
       </c>
@@ -6876,13 +6969,13 @@
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>140</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H11" s="24" t="s">
         <v>106</v>
@@ -6945,9 +7038,9 @@
       <c r="AK11" s="17"/>
       <c r="AL11" s="24"/>
       <c r="AM11" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN11" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN11" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Laboratory Biosafety (University of Toronto)</v>
       </c>
@@ -7033,9 +7126,9 @@
       <c r="AK12" s="17"/>
       <c r="AL12" s="24"/>
       <c r="AM12" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="AN12" s="44" t="str">
+        <v>330</v>
+      </c>
+      <c r="AN12" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Senior Demonstrator (Scihigh - Lunenfield Research Institute)</v>
       </c>
@@ -7050,13 +7143,13 @@
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H13" s="24" t="s">
         <v>106</v>
@@ -7095,7 +7188,7 @@
         <v>51</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T13" s="17"/>
       <c r="U13" s="17"/>
@@ -7117,9 +7210,9 @@
       <c r="AK13" s="17"/>
       <c r="AL13" s="24"/>
       <c r="AM13" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="AN13" s="44" t="str">
+        <v>336</v>
+      </c>
+      <c r="AN13" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Ontario Working at Heights (Ontario Ministry of Labour)</v>
       </c>
@@ -7138,7 +7231,7 @@
         <v>139</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>140</v>
@@ -7207,25 +7300,25 @@
       <c r="AK14" s="17"/>
       <c r="AL14" s="24"/>
       <c r="AM14" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN14" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN14" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Natural Science and Engineering Research Council Undergraduate Student Research Award Recipient (University of Toronto)</v>
       </c>
     </row>
     <row r="15" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B15" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="D15" s="25" t="s">
         <v>280</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>281</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>228</v>
@@ -7234,7 +7327,7 @@
         <v>140</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H15" s="24" t="s">
         <v>179</v>
@@ -7275,7 +7368,7 @@
         <v>51</v>
       </c>
       <c r="S15" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="T15" s="17"/>
       <c r="U15" s="17"/>
@@ -7297,9 +7390,9 @@
       <c r="AK15" s="17"/>
       <c r="AL15" s="24"/>
       <c r="AM15" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="AN15" s="44" t="str">
+        <v>320</v>
+      </c>
+      <c r="AN15" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Undergraduate Student Research Award (Natural Sciences and Engineering Research Council )</v>
       </c>
@@ -7312,7 +7405,7 @@
         <v>102</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="17" t="s">
@@ -7322,7 +7415,7 @@
         <v>42</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H16" s="24" t="s">
         <v>100</v>
@@ -7363,22 +7456,22 @@
         <v>51</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="U16" s="17"/>
       <c r="V16" s="24"/>
       <c r="W16" s="24"/>
       <c r="X16" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y16" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z16" s="24" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA16" s="17"/>
       <c r="AB16" s="17"/>
@@ -7393,9 +7486,9 @@
       <c r="AK16" s="17"/>
       <c r="AL16" s="24"/>
       <c r="AM16" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="AN16" s="44" t="str">
+        <v>315</v>
+      </c>
+      <c r="AN16" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>2016 Conference (Ontario Ecology, Ethology and Evolution Conference)</v>
       </c>
@@ -7408,7 +7501,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D17" s="25"/>
       <c r="E17" s="17" t="s">
@@ -7418,7 +7511,7 @@
         <v>42</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H17" s="24" t="s">
         <v>100</v>
@@ -7459,22 +7552,22 @@
         <v>51</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="U17" s="17"/>
       <c r="V17" s="24"/>
       <c r="W17" s="24"/>
       <c r="X17" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y17" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z17" s="24" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA17" s="17"/>
       <c r="AB17" s="17"/>
@@ -7489,22 +7582,22 @@
       <c r="AK17" s="17"/>
       <c r="AL17" s="24"/>
       <c r="AM17" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN17" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN17" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>2016 Undergraduate Student Research Fair (University of Toronto)</v>
       </c>
     </row>
     <row r="18" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>130</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D18" s="25"/>
       <c r="E18" s="17" t="s">
@@ -7514,7 +7607,7 @@
         <v>140</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H18" s="24" t="s">
         <v>185</v>
@@ -7555,24 +7648,24 @@
         <v>51</v>
       </c>
       <c r="S18" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="T18" s="17" t="s">
         <v>435</v>
       </c>
-      <c r="T18" s="17" t="s">
-        <v>436</v>
-      </c>
       <c r="U18" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="V18" s="24"/>
       <c r="W18" s="24"/>
       <c r="X18" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="Y18" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z18" s="24" t="s">
         <v>386</v>
-      </c>
-      <c r="Y18" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z18" s="24" t="s">
-        <v>387</v>
       </c>
       <c r="AA18" s="17"/>
       <c r="AB18" s="17"/>
@@ -7587,9 +7680,9 @@
       <c r="AK18" s="17"/>
       <c r="AL18" s="24"/>
       <c r="AM18" s="26" t="s">
-        <v>333</v>
-      </c>
-      <c r="AN18" s="44" t="str">
+        <v>332</v>
+      </c>
+      <c r="AN18" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Turf Wars: Understory Turf Transplant Success (Laurentian University)</v>
       </c>
@@ -7602,7 +7695,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D19" s="25" t="s">
         <v>143</v>
@@ -7614,7 +7707,7 @@
         <v>140</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H19" s="24" t="s">
         <v>185</v>
@@ -7646,7 +7739,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q19" s="17" t="s">
         <v>52</v>
@@ -7655,57 +7748,57 @@
         <v>51</v>
       </c>
       <c r="S19" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="T19" s="17" t="s">
         <v>375</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>376</v>
       </c>
       <c r="U19" s="17"/>
       <c r="V19" s="24" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="W19" s="24"/>
       <c r="X19" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="Y19" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z19" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="AA19" s="17" t="s">
         <v>356</v>
       </c>
-      <c r="Y19" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z19" s="24" t="s">
-        <v>434</v>
-      </c>
-      <c r="AA19" s="17" t="s">
+      <c r="AB19" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="AC19" s="24" t="s">
         <v>357</v>
       </c>
-      <c r="AB19" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="AC19" s="24" t="s">
-        <v>358</v>
-      </c>
       <c r="AD19" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="AE19" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="AE19" s="17" t="s">
-        <v>292</v>
-      </c>
       <c r="AF19" s="24" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG19" s="27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AH19" s="24" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AI19" s="17"/>
       <c r="AJ19" s="24"/>
       <c r="AK19" s="17"/>
       <c r="AL19" s="24"/>
       <c r="AM19" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN19" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN19" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Aphid Farm: Tritrophic Community Interactions (University of Toronto)</v>
       </c>
@@ -7722,7 +7815,7 @@
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>65</v>
@@ -7769,13 +7862,13 @@
         <v>51</v>
       </c>
       <c r="S20" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="T20" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="T20" s="17" t="s">
+      <c r="U20" s="17" t="s">
         <v>249</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>250</v>
       </c>
       <c r="V20" s="24"/>
       <c r="W20" s="24"/>
@@ -7795,9 +7888,9 @@
       <c r="AK20" s="17"/>
       <c r="AL20" s="24"/>
       <c r="AM20" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN20" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN20" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>UofT MedStores Staff (University of Toronto)</v>
       </c>
@@ -7810,7 +7903,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="17" t="s">
@@ -7820,7 +7913,7 @@
         <v>42</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H21" s="24" t="s">
         <v>100</v>
@@ -7861,24 +7954,24 @@
         <v>51</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="T21" s="17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="U21" s="17"/>
       <c r="V21" s="24" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="W21" s="24"/>
       <c r="X21" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y21" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z21" s="24" t="s">
         <v>357</v>
-      </c>
-      <c r="Y21" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z21" s="24" t="s">
-        <v>358</v>
       </c>
       <c r="AA21" s="17"/>
       <c r="AB21" s="17"/>
@@ -7893,9 +7986,9 @@
       <c r="AK21" s="17"/>
       <c r="AL21" s="24"/>
       <c r="AM21" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN21" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN21" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>2017 Undergraduate Student Research Fair  (University of Toronto)</v>
       </c>
@@ -7914,7 +8007,7 @@
         <v>143</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>140</v>
@@ -7983,25 +8076,25 @@
       <c r="AK22" s="17"/>
       <c r="AL22" s="24"/>
       <c r="AM22" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN22" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN22" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Koffler Science Reserve Undergraduate Student Research Award Recipient (University of Toronto)</v>
       </c>
     </row>
     <row r="23" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B23" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>284</v>
-      </c>
       <c r="C23" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>228</v>
@@ -8010,7 +8103,7 @@
         <v>140</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H23" s="24" t="s">
         <v>179</v>
@@ -8051,7 +8144,7 @@
         <v>51</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T23" s="17"/>
       <c r="U23" s="17"/>
@@ -8073,9 +8166,9 @@
       <c r="AK23" s="17"/>
       <c r="AL23" s="24"/>
       <c r="AM23" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="AN23" s="44" t="str">
+        <v>319</v>
+      </c>
+      <c r="AN23" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Undergraduate Student Research Award (Koffler Scientific Reserve)</v>
       </c>
@@ -8088,11 +8181,11 @@
         <v>18</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>140</v>
@@ -8161,9 +8254,9 @@
       <c r="AK24" s="17"/>
       <c r="AL24" s="24"/>
       <c r="AM24" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="AN24" s="44" t="str">
+        <v>305</v>
+      </c>
+      <c r="AN24" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Research Technician (Gilbert Lab) (University of Toronto)</v>
       </c>
@@ -8251,9 +8344,9 @@
       <c r="AK25" s="17"/>
       <c r="AL25" s="24"/>
       <c r="AM25" s="17" t="s">
-        <v>446</v>
-      </c>
-      <c r="AN25" s="44" t="str">
+        <v>445</v>
+      </c>
+      <c r="AN25" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Math and Science Instructor (Oxford Learning Centres Inc.)</v>
       </c>
@@ -8315,16 +8408,16 @@
         <v>51</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="V26" s="24" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="W26" s="24"/>
       <c r="X26" s="17"/>
@@ -8343,9 +8436,9 @@
       <c r="AK26" s="17"/>
       <c r="AL26" s="24"/>
       <c r="AM26" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="AN26" s="44" t="str">
+        <v>310</v>
+      </c>
+      <c r="AN26" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Tree Farm Hand (Earthbound Trees)</v>
       </c>
@@ -8413,10 +8506,10 @@
         <v>171</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="V27" s="24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="W27" s="24"/>
       <c r="X27" s="17"/>
@@ -8435,9 +8528,9 @@
       <c r="AK27" s="17"/>
       <c r="AL27" s="24"/>
       <c r="AM27" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="AN27" s="44" t="str">
+        <v>311</v>
+      </c>
+      <c r="AN27" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Ecological Program Developer (Earthbound Kids)</v>
       </c>
@@ -8450,17 +8543,17 @@
         <v>14</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D28" s="25"/>
       <c r="E28" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>140</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H28" s="24" t="s">
         <v>185</v>
@@ -8501,7 +8594,7 @@
         <v>51</v>
       </c>
       <c r="S28" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="T28" s="17"/>
       <c r="U28" s="17"/>
@@ -8523,9 +8616,9 @@
       <c r="AK28" s="17"/>
       <c r="AL28" s="24"/>
       <c r="AM28" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="AN28" s="44" t="str">
+        <v>306</v>
+      </c>
+      <c r="AN28" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Niagara River Invasive Species Management (Niagara College)</v>
       </c>
@@ -8538,7 +8631,7 @@
         <v>14</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D29" s="25" t="s">
         <v>17</v>
@@ -8591,16 +8684,16 @@
         <v>51</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T29" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="U29" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="U29" s="17" t="s">
+      <c r="V29" s="24" t="s">
         <v>402</v>
-      </c>
-      <c r="V29" s="24" t="s">
-        <v>403</v>
       </c>
       <c r="W29" s="24"/>
       <c r="X29" s="17"/>
@@ -8619,9 +8712,9 @@
       <c r="AK29" s="17"/>
       <c r="AL29" s="24"/>
       <c r="AM29" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="AN29" s="44" t="str">
+        <v>306</v>
+      </c>
+      <c r="AN29" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Post-Graduate Certificate in Ecosystem Restoration (Niagara College)</v>
       </c>
@@ -8634,7 +8727,7 @@
         <v>14</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="17" t="s">
@@ -8644,7 +8737,7 @@
         <v>140</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H30" s="24" t="s">
         <v>185</v>
@@ -8685,24 +8778,24 @@
         <v>51</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="T30" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="U30" s="17" t="s">
         <v>392</v>
-      </c>
-      <c r="U30" s="17" t="s">
-        <v>393</v>
       </c>
       <c r="V30" s="24"/>
       <c r="W30" s="24"/>
       <c r="X30" s="17" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Y30" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z30" s="24" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AA30" s="17"/>
       <c r="AB30" s="17"/>
@@ -8711,19 +8804,19 @@
       <c r="AE30" s="17"/>
       <c r="AF30" s="24"/>
       <c r="AG30" s="26" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AH30" s="24" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AI30" s="17"/>
       <c r="AJ30" s="24"/>
       <c r="AK30" s="17"/>
       <c r="AL30" s="24"/>
       <c r="AM30" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="AN30" s="44" t="str">
+        <v>306</v>
+      </c>
+      <c r="AN30" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Terrestrial Insect Restoration Responses (Niagara College)</v>
       </c>
@@ -8789,13 +8882,13 @@
         <v>51</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T31" s="17" t="s">
         <v>205</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="V31" s="24"/>
       <c r="W31" s="24" t="s">
@@ -8817,16 +8910,16 @@
       <c r="AK31" s="17"/>
       <c r="AL31" s="24"/>
       <c r="AM31" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="AN31" s="44" t="str">
+        <v>326</v>
+      </c>
+      <c r="AN31" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Niagara College Student Association Vice President (Society for Ecological Restoration)</v>
       </c>
     </row>
     <row r="32" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="18" t="s">
@@ -8907,9 +9000,9 @@
       <c r="AK32" s="17"/>
       <c r="AL32" s="24"/>
       <c r="AM32" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="AN32" s="44" t="str">
+        <v>328</v>
+      </c>
+      <c r="AN32" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>River Corridor Restoration Technician (Conservation Halton)</v>
       </c>
@@ -8932,7 +9025,7 @@
         <v>77</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H33" s="24" t="s">
         <v>134</v>
@@ -8942,7 +9035,7 @@
       </c>
       <c r="J33" s="22">
         <f ca="1">NOW()</f>
-        <v>46188.50092766204</v>
+        <v>46188.572873032404</v>
       </c>
       <c r="K33" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -8962,7 +9055,7 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>7.710961445649426</v>
+        <v>7.7111585562531628</v>
       </c>
       <c r="P33" s="17" t="s">
         <v>28</v>
@@ -8972,7 +9065,7 @@
         <v>129</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T33" s="17"/>
       <c r="U33" s="17"/>
@@ -8994,9 +9087,9 @@
       <c r="AK33" s="17"/>
       <c r="AL33" s="24"/>
       <c r="AM33" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="AN33" s="44" t="str">
+        <v>318</v>
+      </c>
+      <c r="AN33" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Restricted Operator's Certificate - Aeronautical Communications  (Industry Canada)</v>
       </c>
@@ -9017,7 +9110,7 @@
         <v>42</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H34" s="24" t="s">
         <v>106</v>
@@ -9056,7 +9149,7 @@
         <v>129</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T34" s="17"/>
       <c r="U34" s="17"/>
@@ -9078,9 +9171,9 @@
       <c r="AK34" s="17"/>
       <c r="AL34" s="24"/>
       <c r="AM34" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="AN34" s="44" t="str">
+        <v>302</v>
+      </c>
+      <c r="AN34" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Wilderness and Remote First Aid/ CPR &amp; AED C (Canadian Red Cross)</v>
       </c>
@@ -9103,7 +9196,7 @@
         <v>42</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H35" s="24" t="s">
         <v>106</v>
@@ -9142,7 +9235,7 @@
         <v>129</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="T35" s="17"/>
       <c r="U35" s="17"/>
@@ -9164,16 +9257,16 @@
       <c r="AK35" s="17"/>
       <c r="AL35" s="24"/>
       <c r="AM35" s="26" t="s">
-        <v>339</v>
-      </c>
-      <c r="AN35" s="44" t="str">
+        <v>338</v>
+      </c>
+      <c r="AN35" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Backpack Electrofishing Crew Lead (Class 2) (Trout Unlimited Canada)</v>
       </c>
     </row>
     <row r="36" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="18" t="s">
@@ -9189,7 +9282,7 @@
         <v>77</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H36" s="24" t="s">
         <v>134</v>
@@ -9230,7 +9323,7 @@
         <v>51</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T36" s="17"/>
       <c r="U36" s="17"/>
@@ -9252,9 +9345,9 @@
       <c r="AK36" s="17"/>
       <c r="AL36" s="24"/>
       <c r="AM36" s="26" t="s">
-        <v>343</v>
-      </c>
-      <c r="AN36" s="44" t="str">
+        <v>342</v>
+      </c>
+      <c r="AN36" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Unmanned Aerial Vehicle Ground School (Waterloo Wellington Flight Centre)</v>
       </c>
@@ -9271,7 +9364,7 @@
       </c>
       <c r="D37" s="25"/>
       <c r="E37" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>65</v>
@@ -9318,10 +9411,10 @@
         <v>51</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="U37" s="17"/>
       <c r="V37" s="24"/>
@@ -9342,9 +9435,9 @@
       <c r="AK37" s="17"/>
       <c r="AL37" s="24"/>
       <c r="AM37" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="AN37" s="44" t="str">
+        <v>306</v>
+      </c>
+      <c r="AN37" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Athletics and Recreation Centre Staff (Niagara College)</v>
       </c>
@@ -9367,7 +9460,7 @@
         <v>42</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H38" s="24" t="s">
         <v>106</v>
@@ -9406,7 +9499,7 @@
         <v>51</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T38" s="17"/>
       <c r="U38" s="17"/>
@@ -9428,9 +9521,9 @@
       <c r="AK38" s="17"/>
       <c r="AL38" s="24"/>
       <c r="AM38" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="AN38" s="44" t="str">
+        <v>314</v>
+      </c>
+      <c r="AN38" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Ontario Benthos Biomonitoring Network Participant (Ontario Ministry of Environment, Conservation and Parks)</v>
       </c>
@@ -9453,7 +9546,7 @@
         <v>77</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H39" s="24" t="s">
         <v>134</v>
@@ -9463,7 +9556,7 @@
       </c>
       <c r="J39" s="22">
         <f ca="1">NOW()</f>
-        <v>46188.50092766204</v>
+        <v>46188.572873032404</v>
       </c>
       <c r="K39" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -9483,7 +9576,7 @@
       </c>
       <c r="O39" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>7.4589066511288777</v>
+        <v>7.4591037617326146</v>
       </c>
       <c r="P39" s="17" t="s">
         <v>28</v>
@@ -9493,7 +9586,7 @@
         <v>129</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T39" s="17"/>
       <c r="U39" s="17"/>
@@ -9515,9 +9608,9 @@
       <c r="AK39" s="17"/>
       <c r="AL39" s="24"/>
       <c r="AM39" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="AN39" s="44" t="str">
+        <v>317</v>
+      </c>
+      <c r="AN39" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Pleasure Craft Operators Card (Transportation Canada)</v>
       </c>
@@ -9540,7 +9633,7 @@
         <v>42</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H40" s="24" t="s">
         <v>100</v>
@@ -9581,14 +9674,14 @@
         <v>51</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="U40" s="17"/>
       <c r="V40" s="24" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="W40" s="24"/>
       <c r="X40" s="17"/>
@@ -9607,9 +9700,9 @@
       <c r="AK40" s="17"/>
       <c r="AL40" s="24"/>
       <c r="AM40" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="AN40" s="44" t="str">
+        <v>331</v>
+      </c>
+      <c r="AN40" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Designing Change for a Living Planet Competition (World Wildlife Fund)</v>
       </c>
@@ -9628,13 +9721,13 @@
         <v>20</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>36</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H41" s="24" t="s">
         <v>46</v>
@@ -9673,7 +9766,7 @@
         <v>129</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="T41" s="17"/>
       <c r="U41" s="17"/>
@@ -9695,9 +9788,9 @@
       <c r="AK41" s="17"/>
       <c r="AL41" s="24"/>
       <c r="AM41" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="AN41" s="44" t="str">
+        <v>316</v>
+      </c>
+      <c r="AN41" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Certified Ecological Restoration Practitioner in Training (Society for Ecological Restoration)</v>
       </c>
@@ -9714,13 +9807,13 @@
         <v>110</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>77</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H42" s="24" t="s">
         <v>106</v>
@@ -9781,9 +9874,9 @@
       <c r="AK42" s="17"/>
       <c r="AL42" s="24"/>
       <c r="AM42" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="AN42" s="44" t="str">
+        <v>339</v>
+      </c>
+      <c r="AN42" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Workplace Hazardous Materials Information System (Ontario Ministry of Labour)</v>
       </c>
@@ -9800,7 +9893,7 @@
       </c>
       <c r="D43" s="25"/>
       <c r="E43" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>42</v>
@@ -9867,9 +9960,9 @@
       <c r="AK43" s="17"/>
       <c r="AL43" s="24"/>
       <c r="AM43" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="AN43" s="44" t="str">
+        <v>334</v>
+      </c>
+      <c r="AN43" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Ed Gregor Stewardship Day Volunteer (Crownest Conservation Society)</v>
       </c>
@@ -9939,13 +10032,13 @@
         <v>155</v>
       </c>
       <c r="U44" s="17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="V44" s="24" t="s">
         <v>151</v>
       </c>
       <c r="W44" s="24" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="X44" s="17"/>
       <c r="Y44" s="17"/>
@@ -9963,9 +10056,9 @@
       <c r="AK44" s="17"/>
       <c r="AL44" s="24"/>
       <c r="AM44" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="AN44" s="44" t="str">
+        <v>308</v>
+      </c>
+      <c r="AN44" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Natural Area Assistant - Waterton (Nature Conservancy Canada)</v>
       </c>
@@ -10029,10 +10122,10 @@
         <v>47</v>
       </c>
       <c r="S45" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="T45" s="17" t="s">
         <v>256</v>
-      </c>
-      <c r="T45" s="17" t="s">
-        <v>257</v>
       </c>
       <c r="U45" s="17"/>
       <c r="V45" s="24"/>
@@ -10053,9 +10146,9 @@
       <c r="AK45" s="17"/>
       <c r="AL45" s="24"/>
       <c r="AM45" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="AN45" s="44" t="str">
+        <v>327</v>
+      </c>
+      <c r="AN45" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Stewardship Event Volunteer (Castle Crown Wilderness Coalition)</v>
       </c>
@@ -10073,7 +10166,7 @@
         <v>228</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G46" s="17" t="s">
         <v>13</v>
@@ -10117,14 +10210,14 @@
         <v>47</v>
       </c>
       <c r="S46" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="T46" s="17" t="s">
         <v>254</v>
-      </c>
-      <c r="T46" s="17" t="s">
-        <v>255</v>
       </c>
       <c r="U46" s="17"/>
       <c r="V46" s="24" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="W46" s="24"/>
       <c r="X46" s="17"/>
@@ -10143,9 +10236,9 @@
       <c r="AK46" s="17"/>
       <c r="AL46" s="24"/>
       <c r="AM46" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="AN46" s="44" t="str">
+        <v>322</v>
+      </c>
+      <c r="AN46" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Rough Runner Event Volunteer (Wildr)</v>
       </c>
@@ -10235,9 +10328,9 @@
       <c r="AK47" s="17"/>
       <c r="AL47" s="24"/>
       <c r="AM47" s="26" t="s">
-        <v>326</v>
-      </c>
-      <c r="AN47" s="44" t="str">
+        <v>325</v>
+      </c>
+      <c r="AN47" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Trail Building and Maintenance Committee Member (Great Divide Trail Association)</v>
       </c>
@@ -10250,17 +10343,17 @@
         <v>80</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D48" s="25"/>
       <c r="E48" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>42</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H48" s="24" t="s">
         <v>74</v>
@@ -10301,7 +10394,7 @@
         <v>47</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T48" s="17"/>
       <c r="U48" s="17"/>
@@ -10323,9 +10416,9 @@
       <c r="AK48" s="17"/>
       <c r="AL48" s="24"/>
       <c r="AM48" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="AN48" s="44" t="str">
+        <v>335</v>
+      </c>
+      <c r="AN48" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Annual Field Tour (Southwest Invasive Managers)</v>
       </c>
@@ -10340,13 +10433,13 @@
       </c>
       <c r="D49" s="25"/>
       <c r="E49" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>77</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H49" s="24" t="s">
         <v>134</v>
@@ -10409,20 +10502,20 @@
       <c r="AK49" s="17"/>
       <c r="AL49" s="24"/>
       <c r="AM49" s="26" t="s">
-        <v>341</v>
-      </c>
-      <c r="AN49" s="44" t="str">
+        <v>340</v>
+      </c>
+      <c r="AN49" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Alberta Class 5 Driver's Licence (Government of Alberta)</v>
       </c>
     </row>
     <row r="50" spans="1:40" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A50" s="18" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B50" s="19"/>
       <c r="C50" s="18" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D50" s="25"/>
       <c r="E50" s="17" t="s">
@@ -10435,7 +10528,7 @@
         <v>30</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I50" s="22">
         <v>43709</v>
@@ -10473,24 +10566,24 @@
         <v>56</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="T50" s="17" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="U50" s="17" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="V50" s="24"/>
       <c r="W50" s="24"/>
       <c r="X50" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y50" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z50" s="24" t="s">
         <v>313</v>
-      </c>
-      <c r="Y50" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z50" s="24" t="s">
-        <v>314</v>
       </c>
       <c r="AA50" s="17"/>
       <c r="AB50" s="17"/>
@@ -10505,7 +10598,7 @@
       <c r="AK50" s="17"/>
       <c r="AL50" s="24"/>
       <c r="AM50" s="18"/>
-      <c r="AN50" s="44" t="str">
+      <c r="AN50" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Biophysical Inventory (Private Land Owner)</v>
       </c>
@@ -10522,13 +10615,13 @@
       </c>
       <c r="D51" s="25"/>
       <c r="E51" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>42</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H51" s="24" t="s">
         <v>74</v>
@@ -10589,9 +10682,9 @@
       <c r="AK51" s="17"/>
       <c r="AL51" s="24"/>
       <c r="AM51" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="AN51" s="44" t="str">
+        <v>324</v>
+      </c>
+      <c r="AN51" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Western Canada Chapter Annual General Meeting (Society for Ecological Restoration)</v>
       </c>
@@ -10604,10 +10697,10 @@
         <v>15</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>228</v>
@@ -10652,13 +10745,13 @@
       </c>
       <c r="Q52" s="17"/>
       <c r="R52" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="S52" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="T52" s="17" t="s">
         <v>263</v>
-      </c>
-      <c r="T52" s="17" t="s">
-        <v>264</v>
       </c>
       <c r="U52" s="17"/>
       <c r="V52" s="24"/>
@@ -10679,9 +10772,9 @@
       <c r="AK52" s="17"/>
       <c r="AL52" s="24"/>
       <c r="AM52" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="AN52" s="44" t="str">
+        <v>324</v>
+      </c>
+      <c r="AN52" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Western Canada Chapter Director (Society for Ecological Restoration)</v>
       </c>
@@ -10767,16 +10860,16 @@
       <c r="AK53" s="17"/>
       <c r="AL53" s="24"/>
       <c r="AM53" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="AN53" s="44" t="str">
+        <v>323</v>
+      </c>
+      <c r="AN53" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>CABIN with STREAM DNA Metabarcoding Sample Collection (Living Lakes Canada)</v>
       </c>
     </row>
     <row r="54" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A54" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B54" s="19"/>
       <c r="C54" s="18" t="s">
@@ -10792,7 +10885,7 @@
         <v>42</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H54" s="24" t="s">
         <v>106</v>
@@ -10831,7 +10924,7 @@
         <v>129</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T54" s="17"/>
       <c r="U54" s="17"/>
@@ -10853,9 +10946,9 @@
       <c r="AK54" s="17"/>
       <c r="AL54" s="24"/>
       <c r="AM54" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="AN54" s="44" t="str">
+        <v>304</v>
+      </c>
+      <c r="AN54" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Canadian Aquatic Biomonitoring Network Field Assistant (Canadian Rivers Institute)</v>
       </c>
@@ -10866,7 +10959,7 @@
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="18" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D55" s="25"/>
       <c r="E55" s="17" t="s">
@@ -10876,7 +10969,7 @@
         <v>77</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H55" s="24" t="s">
         <v>134</v>
@@ -10917,7 +11010,7 @@
         <v>47</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T55" s="17"/>
       <c r="U55" s="17"/>
@@ -10939,9 +11032,9 @@
       <c r="AK55" s="17"/>
       <c r="AL55" s="24"/>
       <c r="AM55" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="AN55" s="44" t="str">
+        <v>300</v>
+      </c>
+      <c r="AN55" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Board Governance Introduction (Alberta Ministry of Culture, Multiculturalism, and the Status of Women)</v>
       </c>
@@ -10954,7 +11047,7 @@
         <v>44</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D56" s="25"/>
       <c r="E56" s="17" t="s">
@@ -10964,7 +11057,7 @@
         <v>42</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H56" s="24" t="s">
         <v>30</v>
@@ -11008,32 +11101,32 @@
         <v>196</v>
       </c>
       <c r="T56" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="U56" s="17" t="s">
         <v>197</v>
       </c>
       <c r="V56" s="24" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="W56" s="24"/>
       <c r="X56" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="Y56" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z56" s="24" t="s">
         <v>354</v>
       </c>
-      <c r="Y56" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z56" s="24" t="s">
-        <v>355</v>
-      </c>
       <c r="AA56" s="17" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AB56" s="17" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AC56" s="24" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AD56" s="17"/>
       <c r="AE56" s="17"/>
@@ -11045,9 +11138,9 @@
       <c r="AK56" s="17"/>
       <c r="AL56" s="24"/>
       <c r="AM56" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="AN56" s="44" t="str">
+        <v>308</v>
+      </c>
+      <c r="AN56" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Rangeland and Riparian Health Database (Nature Conservancy Canada)</v>
       </c>
@@ -11060,7 +11153,7 @@
         <v>15</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D57" s="25"/>
       <c r="E57" s="17" t="s">
@@ -11070,10 +11163,10 @@
         <v>140</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I57" s="22">
         <v>43862</v>
@@ -11106,29 +11199,29 @@
       </c>
       <c r="Q57" s="17"/>
       <c r="R57" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="S57" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="T57" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="U57" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="V57" s="24" t="s">
         <v>408</v>
-      </c>
-      <c r="T57" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="U57" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="V57" s="24" t="s">
-        <v>409</v>
       </c>
       <c r="W57" s="24"/>
       <c r="X57" s="17" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y57" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z57" s="24" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AA57" s="17"/>
       <c r="AB57" s="17"/>
@@ -11137,19 +11230,19 @@
       <c r="AE57" s="17"/>
       <c r="AF57" s="24"/>
       <c r="AG57" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AH57" s="24" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AI57" s="17"/>
       <c r="AJ57" s="24"/>
       <c r="AK57" s="17"/>
       <c r="AL57" s="24"/>
       <c r="AM57" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="AN57" s="44" t="str">
+        <v>324</v>
+      </c>
+      <c r="AN57" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Western Canada Restoration Practitioner Survey (Society for Ecological Restoration)</v>
       </c>
@@ -11237,9 +11330,9 @@
       <c r="AK58" s="17"/>
       <c r="AL58" s="24"/>
       <c r="AM58" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="AN58" s="44" t="str">
+        <v>341</v>
+      </c>
+      <c r="AN58" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Trail Monitor (Mountain Bluebird Trail Conservation Society)</v>
       </c>
@@ -11301,7 +11394,7 @@
         <v>47</v>
       </c>
       <c r="S59" s="17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="T59" s="17"/>
       <c r="U59" s="17"/>
@@ -11323,9 +11416,9 @@
       <c r="AK59" s="17"/>
       <c r="AL59" s="24"/>
       <c r="AM59" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="AN59" s="44" t="str">
+        <v>299</v>
+      </c>
+      <c r="AN59" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Administration Committee Chair (Adaptable Outdoors)</v>
       </c>
@@ -11344,13 +11437,13 @@
         <v>19</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>36</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H60" s="24" t="s">
         <v>46</v>
@@ -11389,7 +11482,7 @@
         <v>47</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T60" s="17"/>
       <c r="U60" s="17"/>
@@ -11411,9 +11504,9 @@
       <c r="AK60" s="17"/>
       <c r="AL60" s="24"/>
       <c r="AM60" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="AN60" s="44" t="str">
+        <v>301</v>
+      </c>
+      <c r="AN60" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Biologist in Training (Alberta Society for Professional Biologists)</v>
       </c>
@@ -11431,7 +11524,7 @@
         <v>228</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G61" s="17" t="s">
         <v>13</v>
@@ -11482,7 +11575,7 @@
       </c>
       <c r="U61" s="17"/>
       <c r="V61" s="24" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="W61" s="24"/>
       <c r="X61" s="17"/>
@@ -11501,9 +11594,9 @@
       <c r="AK61" s="17"/>
       <c r="AL61" s="24"/>
       <c r="AM61" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="AN61" s="44" t="str">
+        <v>321</v>
+      </c>
+      <c r="AN61" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Project Lead - Growing Healthy Food Boxes (Pincher Creek and District Food Centre)</v>
       </c>
@@ -11516,7 +11609,7 @@
         <v>211</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D62" s="25"/>
       <c r="E62" s="17" t="s">
@@ -11526,7 +11619,7 @@
         <v>140</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H62" s="24" t="s">
         <v>185</v>
@@ -11567,26 +11660,26 @@
         <v>47</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="T62" s="17" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="U62" s="17" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="V62" s="24" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="W62" s="24"/>
       <c r="X62" s="17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Y62" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z62" s="24" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AA62" s="17"/>
       <c r="AB62" s="17"/>
@@ -11595,19 +11688,19 @@
       <c r="AE62" s="17"/>
       <c r="AF62" s="24"/>
       <c r="AG62" s="27" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AH62" s="24" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AI62" s="17"/>
       <c r="AJ62" s="24"/>
       <c r="AK62" s="17"/>
       <c r="AL62" s="24"/>
       <c r="AM62" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="AN62" s="44" t="str">
+        <v>345</v>
+      </c>
+      <c r="AN62" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Grassland Birds in the Waterton Foothills Parkland (University of Manitoba)</v>
       </c>
@@ -11620,10 +11713,10 @@
         <v>44</v>
       </c>
       <c r="C63" s="18" t="s">
+        <v>471</v>
+      </c>
+      <c r="D63" s="25" t="s">
         <v>472</v>
-      </c>
-      <c r="D63" s="25" t="s">
-        <v>473</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>228</v>
@@ -11632,7 +11725,7 @@
         <v>140</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H63" s="24" t="s">
         <v>179</v>
@@ -11673,7 +11766,7 @@
         <v>215</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T63" s="17"/>
       <c r="U63" s="17"/>
@@ -11695,9 +11788,9 @@
       <c r="AK63" s="17"/>
       <c r="AL63" s="24"/>
       <c r="AM63" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="AN63" s="44" t="str">
+        <v>308</v>
+      </c>
+      <c r="AN63" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Conservation Science Fellowship (Nature Conservancy Canada)</v>
       </c>
@@ -11763,16 +11856,16 @@
         <v>215</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="T64" s="17" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="U64" s="17" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="V64" s="24" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="W64" s="24"/>
       <c r="X64" s="17"/>
@@ -11791,9 +11884,9 @@
       <c r="AK64" s="17"/>
       <c r="AL64" s="24"/>
       <c r="AM64" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="AN64" s="44" t="str">
+        <v>345</v>
+      </c>
+      <c r="AN64" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Master's of Natural Resources Management (University of Manitoba)</v>
       </c>
@@ -11806,7 +11899,7 @@
         <v>44</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D65" s="29"/>
       <c r="E65" s="17" t="s">
@@ -11816,7 +11909,7 @@
         <v>42</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H65" s="24" t="s">
         <v>188</v>
@@ -11857,13 +11950,13 @@
         <v>47</v>
       </c>
       <c r="S65" s="17" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="T65" s="17"/>
       <c r="U65" s="17"/>
       <c r="V65" s="24"/>
       <c r="W65" s="24" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X65" s="17"/>
       <c r="Y65" s="17"/>
@@ -11875,17 +11968,17 @@
       <c r="AE65" s="17"/>
       <c r="AF65" s="24"/>
       <c r="AG65" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="AH65" s="24" t="s">
         <v>501</v>
-      </c>
-      <c r="AH65" s="24" t="s">
-        <v>502</v>
       </c>
       <c r="AI65" s="17"/>
       <c r="AJ65" s="24"/>
       <c r="AK65" s="17"/>
       <c r="AL65" s="24"/>
       <c r="AM65" s="27"/>
-      <c r="AN65" s="44" t="str">
+      <c r="AN65" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>NCC Magazine (Fall 2020) (Nature Conservancy Canada)</v>
       </c>
@@ -11898,7 +11991,7 @@
         <v>211</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D66" s="29"/>
       <c r="E66" s="17" t="s">
@@ -11908,7 +12001,7 @@
         <v>140</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H66" s="24" t="s">
         <v>185</v>
@@ -11949,24 +12042,24 @@
         <v>215</v>
       </c>
       <c r="S66" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="T66" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="U66" s="17" t="s">
         <v>421</v>
-      </c>
-      <c r="T66" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="U66" s="17" t="s">
-        <v>422</v>
       </c>
       <c r="V66" s="24"/>
       <c r="W66" s="24"/>
       <c r="X66" s="17" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Y66" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z66" s="24" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AA66" s="17"/>
       <c r="AB66" s="17"/>
@@ -11975,34 +12068,34 @@
       <c r="AE66" s="17"/>
       <c r="AF66" s="24"/>
       <c r="AG66" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="AH66" s="24" t="s">
         <v>424</v>
       </c>
-      <c r="AH66" s="24" t="s">
+      <c r="AI66" s="27" t="s">
         <v>425</v>
       </c>
-      <c r="AI66" s="27" t="s">
+      <c r="AJ66" s="24" t="s">
         <v>426</v>
-      </c>
-      <c r="AJ66" s="24" t="s">
-        <v>427</v>
       </c>
       <c r="AK66" s="17"/>
       <c r="AL66" s="24"/>
       <c r="AM66" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="AN66" s="44" t="str">
+        <v>345</v>
+      </c>
+      <c r="AN66" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Using Google Trends to Predict Park Visitation (University of Manitoba)</v>
       </c>
     </row>
     <row r="67" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A67" s="18" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B67" s="30"/>
       <c r="C67" s="18" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D67" s="29"/>
       <c r="E67" s="17" t="s">
@@ -12015,7 +12108,7 @@
         <v>30</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I67" s="22">
         <v>44197</v>
@@ -12047,16 +12140,16 @@
         <v>27</v>
       </c>
       <c r="Q67" s="17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="R67" s="17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="S67" s="17" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="T67" s="17" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="U67" s="17"/>
       <c r="V67" s="24"/>
@@ -12077,22 +12170,22 @@
       <c r="AK67" s="17"/>
       <c r="AL67" s="24"/>
       <c r="AM67" s="27" t="s">
-        <v>588</v>
-      </c>
-      <c r="AN67" s="44" t="str">
+        <v>587</v>
+      </c>
+      <c r="AN67" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Data Analyst (Unlock)</v>
       </c>
     </row>
     <row r="68" spans="1:40" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A68" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="B68" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="B68" s="19" t="s">
-        <v>278</v>
-      </c>
       <c r="C68" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D68" s="25"/>
       <c r="E68" s="17" t="s">
@@ -12105,7 +12198,7 @@
         <v>30</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I68" s="22">
         <v>44207</v>
@@ -12137,41 +12230,41 @@
         <v>27</v>
       </c>
       <c r="Q68" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R68" s="17" t="s">
         <v>82</v>
       </c>
       <c r="S68" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="T68" s="17" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U68" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="V68" s="24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="W68" s="24"/>
       <c r="X68" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="Y68" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z68" s="24" t="s">
         <v>351</v>
       </c>
-      <c r="Y68" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z68" s="24" t="s">
-        <v>352</v>
-      </c>
       <c r="AA68" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="AB68" s="17" t="s">
         <v>579</v>
       </c>
-      <c r="AB68" s="17" t="s">
-        <v>580</v>
-      </c>
       <c r="AC68" s="24" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AD68" s="17"/>
       <c r="AE68" s="17"/>
@@ -12183,9 +12276,9 @@
       <c r="AK68" s="17"/>
       <c r="AL68" s="24"/>
       <c r="AM68" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="AN68" s="44" t="str">
+        <v>307</v>
+      </c>
+      <c r="AN68" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Inventorying Living Heritage Conservation in SK (Heritage Saskatchewan)</v>
       </c>
@@ -12198,7 +12291,7 @@
         <v>15</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D69" s="29"/>
       <c r="E69" s="17" t="s">
@@ -12208,7 +12301,7 @@
         <v>42</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H69" s="24" t="s">
         <v>100</v>
@@ -12244,25 +12337,25 @@
       </c>
       <c r="Q69" s="17"/>
       <c r="R69" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="S69" s="17" t="s">
         <v>459</v>
       </c>
-      <c r="S69" s="17" t="s">
-        <v>460</v>
-      </c>
       <c r="T69" s="17" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="U69" s="17"/>
       <c r="V69" s="24"/>
       <c r="W69" s="24"/>
       <c r="X69" s="17" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y69" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z69" s="24" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AA69" s="17"/>
       <c r="AB69" s="17"/>
@@ -12277,22 +12370,22 @@
       <c r="AK69" s="17"/>
       <c r="AL69" s="24"/>
       <c r="AM69" s="27" t="s">
-        <v>558</v>
-      </c>
-      <c r="AN69" s="44" t="str">
+        <v>557</v>
+      </c>
+      <c r="AN69" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>2021 9th Annual World Conference (Society for Ecological Restoration)</v>
       </c>
     </row>
     <row r="70" spans="1:40" ht="66" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="B70" s="19" t="s">
         <v>441</v>
       </c>
-      <c r="B70" s="19" t="s">
-        <v>442</v>
-      </c>
       <c r="C70" s="18" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D70" s="29"/>
       <c r="E70" s="17" t="s">
@@ -12305,7 +12398,7 @@
         <v>30</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I70" s="22">
         <v>44440</v>
@@ -12337,16 +12430,16 @@
         <v>27</v>
       </c>
       <c r="Q70" s="17" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="R70" s="17" t="s">
         <v>51</v>
       </c>
       <c r="S70" s="17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="T70" s="17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="U70" s="17"/>
       <c r="V70" s="24"/>
@@ -12367,9 +12460,9 @@
       <c r="AK70" s="17"/>
       <c r="AL70" s="24"/>
       <c r="AM70" s="26" t="s">
-        <v>445</v>
-      </c>
-      <c r="AN70" s="44" t="str">
+        <v>444</v>
+      </c>
+      <c r="AN70" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Restoration Assistant (Niagara Peninsula Conservation Authority)</v>
       </c>
@@ -12382,7 +12475,7 @@
         <v>160</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D71" s="29"/>
       <c r="E71" s="17" t="s">
@@ -12392,10 +12485,10 @@
         <v>140</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I71" s="22">
         <v>44440</v>
@@ -12433,10 +12526,10 @@
         <v>47</v>
       </c>
       <c r="S71" s="17" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="T71" s="17" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U71" s="17"/>
       <c r="V71" s="24"/>
@@ -12457,25 +12550,25 @@
       <c r="AK71" s="17"/>
       <c r="AL71" s="24"/>
       <c r="AM71" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="AN71" s="44" t="str">
+        <v>341</v>
+      </c>
+      <c r="AN71" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Mountain Bluebird Nesting Success in Response to Landscape Structure (Mountain Bluebird Trail Conservation Society)</v>
       </c>
     </row>
     <row r="72" spans="1:40" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A72" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="B72" s="19" t="s">
         <v>475</v>
       </c>
-      <c r="B72" s="19" t="s">
-        <v>476</v>
-      </c>
       <c r="C72" s="18" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E72" s="17" t="s">
         <v>228</v>
@@ -12494,7 +12587,7 @@
       </c>
       <c r="J72" s="22">
         <f ca="1">NOW()</f>
-        <v>46188.50092766204</v>
+        <v>46188.572873032404</v>
       </c>
       <c r="K72" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -12514,7 +12607,7 @@
       </c>
       <c r="O72" s="20">
         <f t="shared" ca="1" si="2"/>
-        <v>4.4561669251014804</v>
+        <v>4.4563640357052181</v>
       </c>
       <c r="P72" s="17" t="s">
         <v>28</v>
@@ -12526,16 +12619,16 @@
         <v>51</v>
       </c>
       <c r="S72" s="17" t="s">
+        <v>626</v>
+      </c>
+      <c r="T72" s="17" t="s">
         <v>628</v>
       </c>
-      <c r="T72" s="17" t="s">
-        <v>630</v>
-      </c>
       <c r="U72" s="17" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="V72" s="24" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="W72" s="24"/>
       <c r="X72" s="17"/>
@@ -12548,32 +12641,32 @@
       <c r="AE72" s="17"/>
       <c r="AF72" s="24"/>
       <c r="AG72" s="27" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AH72" s="24" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AI72" s="17"/>
       <c r="AJ72" s="24"/>
       <c r="AK72" s="17"/>
       <c r="AL72" s="24"/>
       <c r="AM72" s="27" t="s">
-        <v>600</v>
-      </c>
-      <c r="AN72" s="44" t="str">
+        <v>599</v>
+      </c>
+      <c r="AN72" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Key Biodiversity Area Assessment and Technical Support Coordinator (Wildlife Conservation Society Canada)</v>
       </c>
     </row>
     <row r="73" spans="1:40" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A73" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="B73" s="19" t="s">
         <v>480</v>
       </c>
-      <c r="B73" s="19" t="s">
+      <c r="C73" s="18" t="s">
         <v>481</v>
-      </c>
-      <c r="C73" s="18" t="s">
-        <v>482</v>
       </c>
       <c r="D73" s="29"/>
       <c r="E73" s="17" t="s">
@@ -12586,7 +12679,7 @@
         <v>30</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I73" s="22">
         <v>44562</v>
@@ -12618,16 +12711,16 @@
         <v>27</v>
       </c>
       <c r="Q73" s="17" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="R73" s="17" t="s">
         <v>47</v>
       </c>
       <c r="S73" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="T73" s="17" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="U73" s="17"/>
       <c r="V73" s="24"/>
@@ -12648,20 +12741,20 @@
       <c r="AK73" s="17"/>
       <c r="AL73" s="24"/>
       <c r="AM73" s="27" t="s">
-        <v>578</v>
-      </c>
-      <c r="AN73" s="44" t="str">
+        <v>577</v>
+      </c>
+      <c r="AN73" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Data Analyst (Blood Tribe Land Management)</v>
       </c>
     </row>
     <row r="74" spans="1:40" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A74" s="18" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B74" s="30"/>
       <c r="C74" s="18" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D74" s="29"/>
       <c r="E74" s="17" t="s">
@@ -12671,10 +12764,10 @@
         <v>140</v>
       </c>
       <c r="G74" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="H74" s="24" t="s">
         <v>489</v>
-      </c>
-      <c r="H74" s="24" t="s">
-        <v>490</v>
       </c>
       <c r="I74" s="22">
         <v>44802</v>
@@ -12708,7 +12801,7 @@
       <c r="Q74" s="17"/>
       <c r="R74" s="17"/>
       <c r="S74" s="17" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="T74" s="17"/>
       <c r="U74" s="17"/>
@@ -12724,30 +12817,30 @@
       <c r="AE74" s="17"/>
       <c r="AF74" s="24"/>
       <c r="AG74" s="27" t="s">
+        <v>505</v>
+      </c>
+      <c r="AH74" s="24" t="s">
         <v>506</v>
-      </c>
-      <c r="AH74" s="24" t="s">
-        <v>507</v>
       </c>
       <c r="AI74" s="17"/>
       <c r="AJ74" s="24"/>
       <c r="AK74" s="17"/>
       <c r="AL74" s="24"/>
       <c r="AM74" s="17"/>
-      <c r="AN74" s="44" t="str">
+      <c r="AN74" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Experimental evidence of size-selective harvest and environmental stochasticity effects on population demography, fluctuations, and nonlinearity (Ecology Letters)</v>
       </c>
     </row>
     <row r="75" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A75" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="B75" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="B75" s="19" t="s">
-        <v>479</v>
-      </c>
       <c r="C75" s="18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D75" s="29"/>
       <c r="E75" s="17" t="s">
@@ -12757,7 +12850,7 @@
         <v>140</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H75" s="24" t="s">
         <v>100</v>
@@ -12796,22 +12889,22 @@
         <v>154</v>
       </c>
       <c r="S75" s="17" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="T75" s="17" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="U75" s="17"/>
       <c r="V75" s="24"/>
       <c r="W75" s="24"/>
       <c r="X75" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="Y75" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z75" s="24" t="s">
         <v>571</v>
-      </c>
-      <c r="Y75" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z75" s="24" t="s">
-        <v>572</v>
       </c>
       <c r="AA75" s="17"/>
       <c r="AB75" s="17"/>
@@ -12826,22 +12919,22 @@
       <c r="AK75" s="17"/>
       <c r="AL75" s="24"/>
       <c r="AM75" s="27" t="s">
-        <v>555</v>
-      </c>
-      <c r="AN75" s="44" t="str">
+        <v>554</v>
+      </c>
+      <c r="AN75" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>2023 Annual Conference: Birds as Bridges (Society for Canadian Orithologists)</v>
       </c>
     </row>
     <row r="76" spans="1:40" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="B76" s="30" t="s">
         <v>494</v>
       </c>
-      <c r="B76" s="30" t="s">
-        <v>495</v>
-      </c>
       <c r="C76" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D76" s="29"/>
       <c r="E76" s="17" t="s">
@@ -12851,7 +12944,7 @@
         <v>42</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H76" s="24" t="s">
         <v>188</v>
@@ -12892,13 +12985,13 @@
         <v>215</v>
       </c>
       <c r="S76" s="17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="T76" s="17"/>
       <c r="U76" s="17"/>
       <c r="V76" s="24"/>
       <c r="W76" s="24" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X76" s="17"/>
       <c r="Y76" s="17"/>
@@ -12910,30 +13003,30 @@
       <c r="AE76" s="17"/>
       <c r="AF76" s="24"/>
       <c r="AG76" s="27" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AH76" s="24" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AI76" s="17"/>
       <c r="AJ76" s="24"/>
       <c r="AK76" s="17"/>
       <c r="AL76" s="24"/>
       <c r="AM76" s="17"/>
-      <c r="AN76" s="44" t="str">
+      <c r="AN76" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Key Biodiversity Areas in Manitoba (CTV News Winnnipeg)</v>
       </c>
     </row>
     <row r="77" spans="1:40" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="18" t="s">
+        <v>631</v>
+      </c>
+      <c r="B77" s="30" t="s">
+        <v>632</v>
+      </c>
+      <c r="C77" s="18" t="s">
         <v>633</v>
-      </c>
-      <c r="B77" s="30" t="s">
-        <v>634</v>
-      </c>
-      <c r="C77" s="18" t="s">
-        <v>635</v>
       </c>
       <c r="D77" s="29"/>
       <c r="E77" s="17" t="s">
@@ -12943,7 +13036,7 @@
         <v>77</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H77" s="24" t="s">
         <v>181</v>
@@ -12975,14 +13068,14 @@
         <v>1</v>
       </c>
       <c r="P77" s="17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q77" s="17"/>
       <c r="R77" s="17" t="s">
         <v>154</v>
       </c>
       <c r="S77" s="17" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="T77" s="17"/>
       <c r="U77" s="17"/>
@@ -12998,30 +13091,30 @@
       <c r="AE77" s="17"/>
       <c r="AF77" s="24"/>
       <c r="AG77" s="27" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AH77" s="24" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AI77" s="17"/>
       <c r="AJ77" s="24"/>
       <c r="AK77" s="17"/>
       <c r="AL77" s="24"/>
       <c r="AM77" s="27" t="s">
-        <v>638</v>
-      </c>
-      <c r="AN77" s="44" t="str">
+        <v>636</v>
+      </c>
+      <c r="AN77" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Website Developer (Moore Manor Designs)</v>
       </c>
     </row>
     <row r="78" spans="1:40" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="18" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B78" s="30"/>
       <c r="C78" s="18" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D78" s="29"/>
       <c r="E78" s="17" t="s">
@@ -13031,7 +13124,7 @@
         <v>77</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H78" s="24" t="s">
         <v>181</v>
@@ -13063,14 +13156,14 @@
         <v>1</v>
       </c>
       <c r="P78" s="17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q78" s="17"/>
       <c r="R78" s="17" t="s">
         <v>154</v>
       </c>
       <c r="S78" s="17" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="T78" s="17"/>
       <c r="U78" s="17"/>
@@ -13086,30 +13179,30 @@
       <c r="AE78" s="17"/>
       <c r="AF78" s="24"/>
       <c r="AG78" s="27" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="AH78" s="24" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="AI78" s="17"/>
       <c r="AJ78" s="24"/>
       <c r="AK78" s="17"/>
       <c r="AL78" s="24"/>
       <c r="AM78" s="27" t="s">
-        <v>660</v>
-      </c>
-      <c r="AN78" s="44" t="str">
+        <v>657</v>
+      </c>
+      <c r="AN78" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Website Developer (Personal Website)</v>
       </c>
     </row>
     <row r="79" spans="1:40" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A79" s="18" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B79" s="30"/>
       <c r="C79" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D79" s="29"/>
       <c r="E79" s="17" t="s">
@@ -13119,7 +13212,7 @@
         <v>42</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H79" s="24" t="s">
         <v>188</v>
@@ -13160,7 +13253,7 @@
         <v>215</v>
       </c>
       <c r="S79" s="17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="T79" s="17"/>
       <c r="U79" s="17"/>
@@ -13176,17 +13269,17 @@
       <c r="AE79" s="17"/>
       <c r="AF79" s="24"/>
       <c r="AG79" s="27" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AH79" s="24" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AI79" s="17"/>
       <c r="AJ79" s="24"/>
       <c r="AK79" s="17"/>
       <c r="AL79" s="24"/>
       <c r="AM79" s="17"/>
-      <c r="AN79" s="44" t="str">
+      <c r="AN79" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Many key biodiversity areas identified in Manitoba (Manitoba Cooperator)</v>
       </c>
@@ -13199,11 +13292,11 @@
         <v>211</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D80" s="29"/>
       <c r="E80" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>42</v>
@@ -13244,16 +13337,16 @@
         <v>29</v>
       </c>
       <c r="Q80" s="17" t="s">
+        <v>591</v>
+      </c>
+      <c r="R80" s="17" t="s">
         <v>592</v>
       </c>
-      <c r="R80" s="17" t="s">
+      <c r="S80" s="17" t="s">
         <v>593</v>
       </c>
-      <c r="S80" s="17" t="s">
+      <c r="T80" s="17" t="s">
         <v>594</v>
-      </c>
-      <c r="T80" s="17" t="s">
-        <v>595</v>
       </c>
       <c r="U80" s="17"/>
       <c r="V80" s="24"/>
@@ -13274,20 +13367,20 @@
       <c r="AK80" s="17"/>
       <c r="AL80" s="24"/>
       <c r="AM80" s="17"/>
-      <c r="AN80" s="44" t="str">
+      <c r="AN80" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Conservation in Small Island Developing States (University of Manitoba)</v>
       </c>
     </row>
     <row r="81" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A81" s="18" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D81" s="29"/>
       <c r="E81" s="17" t="s">
@@ -13297,7 +13390,7 @@
         <v>42</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H81" s="24" t="s">
         <v>100</v>
@@ -13332,28 +13425,28 @@
         <v>29</v>
       </c>
       <c r="Q81" s="17" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R81" s="17" t="s">
         <v>51</v>
       </c>
       <c r="S81" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T81" s="17" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="U81" s="17"/>
       <c r="V81" s="24"/>
       <c r="W81" s="24"/>
       <c r="X81" s="17" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="Y81" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Z81" s="24" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AA81" s="17"/>
       <c r="AB81" s="17"/>
@@ -13368,9 +13461,9 @@
       <c r="AK81" s="17"/>
       <c r="AL81" s="24"/>
       <c r="AM81" s="27" t="s">
-        <v>556</v>
-      </c>
-      <c r="AN81" s="44" t="str">
+        <v>555</v>
+      </c>
+      <c r="AN81" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>2023 Annual Meeting: Methods in Wildlife Research (Ontario Chapter of the Wildlife Society)</v>
       </c>
@@ -13383,7 +13476,7 @@
         <v>211</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D82" s="29"/>
       <c r="E82" s="17" t="s">
@@ -13396,7 +13489,7 @@
         <v>30</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I82" s="22">
         <v>45046</v>
@@ -13428,16 +13521,16 @@
         <v>27</v>
       </c>
       <c r="Q82" s="17" t="s">
+        <v>591</v>
+      </c>
+      <c r="R82" s="17" t="s">
         <v>592</v>
       </c>
-      <c r="R82" s="17" t="s">
-        <v>593</v>
-      </c>
       <c r="S82" s="17" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="T82" s="17" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="U82" s="17"/>
       <c r="V82" s="24"/>
@@ -13458,25 +13551,25 @@
       <c r="AK82" s="17"/>
       <c r="AL82" s="24"/>
       <c r="AM82" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="AN82" s="44" t="str">
+        <v>345</v>
+      </c>
+      <c r="AN82" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Data Analyst (University of Manitoba)</v>
       </c>
     </row>
     <row r="83" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A83" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="B83" s="19" t="s">
         <v>536</v>
       </c>
-      <c r="B83" s="19" t="s">
-        <v>537</v>
-      </c>
       <c r="C83" s="18" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E83" s="17" t="s">
         <v>228</v>
@@ -13521,13 +13614,13 @@
       </c>
       <c r="Q83" s="17"/>
       <c r="R83" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="S83" s="17" t="s">
         <v>542</v>
       </c>
-      <c r="S83" s="17" t="s">
-        <v>543</v>
-      </c>
       <c r="T83" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="U83" s="17"/>
       <c r="V83" s="24"/>
@@ -13548,22 +13641,22 @@
       <c r="AK83" s="17"/>
       <c r="AL83" s="24"/>
       <c r="AM83" s="27" t="s">
-        <v>540</v>
-      </c>
-      <c r="AN83" s="44" t="str">
+        <v>539</v>
+      </c>
+      <c r="AN83" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>North America Regional Director (Society for Conservation Biology)</v>
       </c>
     </row>
     <row r="84" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A84" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="B84" s="19" t="s">
         <v>514</v>
       </c>
-      <c r="B84" s="19" t="s">
-        <v>515</v>
-      </c>
       <c r="C84" s="18" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D84" s="29"/>
       <c r="E84" s="17" t="s">
@@ -13573,7 +13666,7 @@
         <v>42</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H84" s="24" t="s">
         <v>100</v>
@@ -13614,24 +13707,24 @@
         <v>215</v>
       </c>
       <c r="S84" s="17" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="T84" s="17" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="U84" s="17"/>
       <c r="V84" s="24" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="W84" s="24"/>
       <c r="X84" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="Y84" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z84" s="24" t="s">
         <v>573</v>
-      </c>
-      <c r="Y84" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z84" s="24" t="s">
-        <v>574</v>
       </c>
       <c r="AA84" s="17"/>
       <c r="AB84" s="17"/>
@@ -13646,20 +13739,20 @@
       <c r="AK84" s="17"/>
       <c r="AL84" s="24"/>
       <c r="AM84" s="27" t="s">
-        <v>559</v>
-      </c>
-      <c r="AN84" s="44" t="str">
+        <v>558</v>
+      </c>
+      <c r="AN84" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>2023 Joint Annual Meeting with Canadian Botanical Association (Canadian Society for Ecology and Evolution)</v>
       </c>
     </row>
     <row r="85" spans="1:40" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A85" s="18" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B85" s="30"/>
       <c r="C85" s="18" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D85" s="29"/>
       <c r="E85" s="17" t="s">
@@ -13669,7 +13762,7 @@
         <v>42</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H85" s="24" t="s">
         <v>188</v>
@@ -13704,13 +13797,13 @@
         <v>29</v>
       </c>
       <c r="Q85" s="17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="R85" s="17" t="s">
         <v>51</v>
       </c>
       <c r="S85" s="17" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T85" s="17"/>
       <c r="U85" s="17"/>
@@ -13726,17 +13819,17 @@
       <c r="AE85" s="17"/>
       <c r="AF85" s="24"/>
       <c r="AG85" s="27" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AH85" s="24" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AI85" s="17"/>
       <c r="AJ85" s="24"/>
       <c r="AK85" s="17"/>
       <c r="AL85" s="24"/>
       <c r="AM85" s="27"/>
-      <c r="AN85" s="44" t="str">
+      <c r="AN85" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Our World: Ecosystem Restoration - United Nations and Western Canada (Food for the Future (Global News Radio))</v>
       </c>
@@ -13749,7 +13842,7 @@
         <v>44</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D86" s="29"/>
       <c r="E86" s="17" t="s">
@@ -13759,7 +13852,7 @@
         <v>42</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H86" s="24" t="s">
         <v>188</v>
@@ -13794,13 +13887,13 @@
         <v>29</v>
       </c>
       <c r="Q86" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="R86" s="17" t="s">
         <v>545</v>
       </c>
-      <c r="R86" s="17" t="s">
-        <v>546</v>
-      </c>
       <c r="S86" s="17" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="T86" s="17"/>
       <c r="U86" s="17"/>
@@ -13816,17 +13909,17 @@
       <c r="AE86" s="17"/>
       <c r="AF86" s="24"/>
       <c r="AG86" s="27" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AH86" s="24" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AI86" s="17"/>
       <c r="AJ86" s="24"/>
       <c r="AK86" s="17"/>
       <c r="AL86" s="24"/>
       <c r="AM86" s="27"/>
-      <c r="AN86" s="44" t="str">
+      <c r="AN86" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>NCC Magazine (Fall 2023) (Nature Conservancy Canada)</v>
       </c>
@@ -13839,7 +13932,7 @@
         <v>14</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D87" s="29"/>
       <c r="E87" s="17" t="s">
@@ -13859,7 +13952,7 @@
       </c>
       <c r="J87" s="22">
         <f ca="1">NOW()</f>
-        <v>46188.50092766204</v>
+        <v>46188.572873032404</v>
       </c>
       <c r="K87" s="23">
         <f>MONTH(cv.table[[#This Row],[Start]])</f>
@@ -13879,7 +13972,7 @@
       </c>
       <c r="O87" s="20">
         <f t="shared" ca="1" si="2"/>
-        <v>2.4561669251014804</v>
+        <v>2.4563640357052177</v>
       </c>
       <c r="P87" s="17" t="s">
         <v>28</v>
@@ -13891,16 +13984,16 @@
         <v>51</v>
       </c>
       <c r="S87" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="T87" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="U87" s="17" t="s">
         <v>622</v>
       </c>
-      <c r="T87" s="17" t="s">
-        <v>625</v>
-      </c>
-      <c r="U87" s="17" t="s">
+      <c r="V87" s="24" t="s">
         <v>624</v>
-      </c>
-      <c r="V87" s="24" t="s">
-        <v>626</v>
       </c>
       <c r="W87" s="24"/>
       <c r="X87" s="17"/>
@@ -13919,22 +14012,22 @@
       <c r="AK87" s="17"/>
       <c r="AL87" s="24"/>
       <c r="AM87" s="27" t="s">
-        <v>627</v>
-      </c>
-      <c r="AN87" s="44" t="str">
+        <v>625</v>
+      </c>
+      <c r="AN87" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Part-time Professor (Niagara College)</v>
       </c>
     </row>
     <row r="88" spans="1:40" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A88" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="B88" s="19" t="s">
         <v>536</v>
       </c>
-      <c r="B88" s="19" t="s">
-        <v>537</v>
-      </c>
       <c r="C88" s="18" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D88" s="29"/>
       <c r="E88" s="17" t="s">
@@ -13944,10 +14037,10 @@
         <v>42</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I88" s="22">
         <v>45466</v>
@@ -13979,16 +14072,16 @@
         <v>29</v>
       </c>
       <c r="Q88" s="17" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="R88" s="17" t="s">
         <v>56</v>
       </c>
       <c r="S88" s="17" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="T88" s="17" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="U88" s="17"/>
       <c r="V88" s="24"/>
@@ -14009,9 +14102,9 @@
       <c r="AK88" s="17"/>
       <c r="AL88" s="24"/>
       <c r="AM88" s="27" t="s">
-        <v>539</v>
-      </c>
-      <c r="AN88" s="44" t="str">
+        <v>538</v>
+      </c>
+      <c r="AN88" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>2024 SCB North American Congress for Conservation Biology (Society for Conservation Biology)</v>
       </c>
@@ -14024,7 +14117,7 @@
         <v>15</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D89" s="29"/>
       <c r="E89" s="17" t="s">
@@ -14034,10 +14127,10 @@
         <v>42</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I89" s="22">
         <v>45593</v>
@@ -14069,16 +14162,16 @@
         <v>29</v>
       </c>
       <c r="Q89" s="17" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="R89" s="17" t="s">
         <v>56</v>
       </c>
       <c r="S89" s="17" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="T89" s="17" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="U89" s="17"/>
       <c r="V89" s="24"/>
@@ -14099,22 +14192,22 @@
       <c r="AK89" s="17"/>
       <c r="AL89" s="24"/>
       <c r="AM89" s="27" t="s">
-        <v>524</v>
-      </c>
-      <c r="AN89" s="44" t="str">
+        <v>523</v>
+      </c>
+      <c r="AN89" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>2024 SER North America Conference (Society for Ecological Restoration)</v>
       </c>
     </row>
     <row r="90" spans="1:40" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A90" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="B90" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="B90" s="19" t="s">
-        <v>350</v>
-      </c>
       <c r="C90" s="18" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D90" s="29"/>
       <c r="E90" s="17" t="s">
@@ -14127,7 +14220,7 @@
         <v>30</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I90" s="38">
         <v>45597</v>
@@ -14156,7 +14249,7 @@
         <v>1</v>
       </c>
       <c r="P90" s="17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q90" s="17" t="s">
         <v>52</v>
@@ -14165,10 +14258,10 @@
         <v>51</v>
       </c>
       <c r="S90" s="17" t="s">
-        <v>609</v>
+        <v>686</v>
       </c>
       <c r="T90" s="17" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="U90" s="17"/>
       <c r="V90" s="24"/>
@@ -14189,18 +14282,18 @@
       <c r="AK90" s="17"/>
       <c r="AL90" s="24"/>
       <c r="AM90" s="26"/>
-      <c r="AN90" s="44" t="str">
+      <c r="AN90" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Data Analyst (Swim, Drink, Fish)</v>
       </c>
     </row>
     <row r="91" spans="1:40" ht="211.2" x14ac:dyDescent="0.3">
       <c r="A91" s="18" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B91" s="30"/>
       <c r="C91" s="18" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D91" s="29"/>
       <c r="E91" s="17" t="s">
@@ -14210,10 +14303,10 @@
         <v>36</v>
       </c>
       <c r="G91" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="H91" s="24" t="s">
         <v>499</v>
-      </c>
-      <c r="H91" s="24" t="s">
-        <v>500</v>
       </c>
       <c r="I91" s="38">
         <v>45797</v>
@@ -14249,7 +14342,7 @@
         <v>154</v>
       </c>
       <c r="S91" s="17" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="T91" s="17"/>
       <c r="U91" s="17"/>
@@ -14265,28 +14358,28 @@
       <c r="AE91" s="17"/>
       <c r="AF91" s="24"/>
       <c r="AG91" s="27" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="AH91" s="24" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="AI91" s="17"/>
       <c r="AJ91" s="24"/>
       <c r="AK91" s="17"/>
       <c r="AL91" s="24"/>
       <c r="AM91" s="26"/>
-      <c r="AN91" s="44" t="str">
+      <c r="AN91" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>Canada's Mountainous Marvels: Safeguarding Unique Ecosystems and Species (State of the Mountains)</v>
       </c>
     </row>
     <row r="92" spans="1:40" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A92" s="18" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B92" s="30"/>
       <c r="C92" s="18" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D92" s="29"/>
       <c r="E92" s="17" t="s">
@@ -14296,10 +14389,10 @@
         <v>140</v>
       </c>
       <c r="G92" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="H92" s="24" t="s">
         <v>499</v>
-      </c>
-      <c r="H92" s="24" t="s">
-        <v>500</v>
       </c>
       <c r="I92" s="38">
         <v>45938</v>
@@ -14335,7 +14428,7 @@
         <v>215</v>
       </c>
       <c r="S92" s="17" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="T92" s="17"/>
       <c r="U92" s="17"/>
@@ -14351,17 +14444,17 @@
       <c r="AE92" s="17"/>
       <c r="AF92" s="24"/>
       <c r="AG92" s="27" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AH92" s="24" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AI92" s="17"/>
       <c r="AJ92" s="24"/>
       <c r="AK92" s="17"/>
       <c r="AL92" s="24"/>
       <c r="AM92" s="17"/>
-      <c r="AN92" s="44" t="str">
+      <c r="AN92" s="43" t="str">
         <f>_xlfn.CONCAT(cv.table[[#This Row],[Title]], " (", cv.table[[#This Row],[Organization]],")")</f>
         <v>A rare ecological treasure (The Manitoban)</v>
       </c>
@@ -14497,16 +14590,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376035FC-43A2-492E-A452-9F7A1A76C10E}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="37.44140625" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
     <col min="4" max="4" width="25.44140625" customWidth="1"/>
     <col min="5" max="5" width="20.44140625" customWidth="1"/>
     <col min="7" max="7" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -14514,731 +14607,779 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C1" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>684</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>643</v>
+      </c>
+      <c r="H1" t="s">
         <v>687</v>
-      </c>
-      <c r="G1" s="41" t="s">
-        <v>646</v>
-      </c>
-      <c r="H1" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C2" t="s">
-        <v>678</v>
-      </c>
-      <c r="D2" s="40">
+        <v>675</v>
+      </c>
+      <c r="D2" s="39">
         <v>43344</v>
       </c>
-      <c r="E2" s="45">
+      <c r="E2" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
         <v>7.8</v>
       </c>
-      <c r="G2" s="42" t="s">
-        <v>662</v>
-      </c>
-      <c r="H2" s="39">
-        <v>39.099999999999994</v>
+      <c r="G2" s="41" t="s">
+        <v>639</v>
+      </c>
+      <c r="H2" s="44">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B3" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C3" t="s">
-        <v>681</v>
-      </c>
-      <c r="D3" s="40">
+        <v>678</v>
+      </c>
+      <c r="D3" s="39">
         <v>43739</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
         <v>6.8</v>
       </c>
-      <c r="G3" s="43" t="s">
-        <v>656</v>
-      </c>
-      <c r="H3" s="39">
-        <v>12.799999999999999</v>
+      <c r="G3" s="42" t="s">
+        <v>664</v>
+      </c>
+      <c r="H3" s="44">
+        <v>4.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B4" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C4" t="s">
-        <v>681</v>
-      </c>
-      <c r="D4" s="40">
+        <v>678</v>
+      </c>
+      <c r="D4" s="39">
         <v>44075</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
         <v>5.8</v>
       </c>
-      <c r="G4" s="43" t="s">
-        <v>655</v>
-      </c>
-      <c r="H4" s="39">
-        <v>12.799999999999999</v>
+      <c r="G4" s="42" t="s">
+        <v>662</v>
+      </c>
+      <c r="H4" s="44">
+        <v>3.5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B5" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C5" t="s">
-        <v>680</v>
-      </c>
-      <c r="D5" s="40">
+        <v>677</v>
+      </c>
+      <c r="D5" s="39">
         <v>45901</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
         <v>0.79999999999999993</v>
       </c>
-      <c r="G5" s="43" t="s">
-        <v>668</v>
-      </c>
-      <c r="H5" s="39">
-        <v>5.5</v>
+      <c r="G5" s="42" t="s">
+        <v>640</v>
+      </c>
+      <c r="H5" s="44">
+        <v>2.5</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B6" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C6" t="s">
-        <v>680</v>
-      </c>
-      <c r="D6" s="40">
+        <v>677</v>
+      </c>
+      <c r="D6" s="39">
         <v>43739</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
         <v>6.8</v>
       </c>
-      <c r="G6" s="43" t="s">
-        <v>676</v>
-      </c>
-      <c r="H6" s="39">
-        <v>2.5</v>
+      <c r="G6" s="42" t="s">
+        <v>682</v>
+      </c>
+      <c r="H6" s="44">
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B7" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C7" t="s">
-        <v>682</v>
-      </c>
-      <c r="D7" s="40">
+        <v>679</v>
+      </c>
+      <c r="D7" s="39">
         <v>45901</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
         <v>0.79999999999999993</v>
       </c>
-      <c r="G7" s="43" t="s">
-        <v>677</v>
-      </c>
-      <c r="H7" s="39">
-        <v>2.5</v>
+      <c r="G7" s="42" t="s">
+        <v>683</v>
+      </c>
+      <c r="H7" s="44">
+        <v>1.5</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="B8" t="s">
-        <v>652</v>
+        <v>688</v>
       </c>
       <c r="C8" t="s">
-        <v>680</v>
-      </c>
-      <c r="D8" s="40">
-        <v>44075</v>
-      </c>
-      <c r="E8" s="45">
+        <v>675</v>
+      </c>
+      <c r="D8" s="39">
+        <v>44927</v>
+      </c>
+      <c r="E8" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>5.8</v>
-      </c>
-      <c r="G8" s="43" t="s">
-        <v>669</v>
-      </c>
-      <c r="H8" s="39">
-        <v>2.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>663</v>
+      </c>
+      <c r="H8" s="44">
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B9" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C9" t="s">
-        <v>683</v>
-      </c>
-      <c r="D9" s="40">
-        <v>44197</v>
-      </c>
-      <c r="E9" s="45">
+        <v>677</v>
+      </c>
+      <c r="D9" s="39">
+        <v>44075</v>
+      </c>
+      <c r="E9" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>5.5</v>
-      </c>
-      <c r="G9" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="H9" s="39">
-        <v>0.5</v>
+        <v>5.8</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>660</v>
+      </c>
+      <c r="H9" s="44">
+        <v>22.900000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B10" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C10" t="s">
         <v>680</v>
       </c>
-      <c r="D10" s="40">
-        <v>44562</v>
-      </c>
-      <c r="E10" s="45">
+      <c r="D10" s="39">
+        <v>44197</v>
+      </c>
+      <c r="E10" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>664</v>
-      </c>
-      <c r="H10" s="39">
-        <v>28.8</v>
+        <v>646</v>
+      </c>
+      <c r="H10" s="44">
+        <v>11.1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="B11" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C11" t="s">
-        <v>681</v>
-      </c>
-      <c r="D11" s="40">
-        <v>41518</v>
-      </c>
-      <c r="E11" s="45">
+        <v>677</v>
+      </c>
+      <c r="D11" s="39">
+        <v>44562</v>
+      </c>
+      <c r="E11" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>12.799999999999999</v>
-      </c>
-      <c r="G11" s="43" t="s">
-        <v>648</v>
-      </c>
-      <c r="H11" s="39">
-        <v>7.8</v>
+        <v>4.5</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>647</v>
+      </c>
+      <c r="H11" s="44">
+        <v>5.8</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B12" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C12" t="s">
-        <v>681</v>
-      </c>
-      <c r="D12" s="40">
-        <v>41518</v>
-      </c>
-      <c r="E12" s="45">
+        <v>678</v>
+      </c>
+      <c r="D12" s="39">
+        <v>42005</v>
+      </c>
+      <c r="E12" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>12.799999999999999</v>
-      </c>
-      <c r="G12" s="43" t="s">
-        <v>672</v>
-      </c>
-      <c r="H12" s="39">
-        <v>6.8</v>
+        <v>11.5</v>
+      </c>
+      <c r="G12" s="42" t="s">
+        <v>644</v>
+      </c>
+      <c r="H12" s="44">
+        <v>4.5</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B13" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="C13" t="s">
-        <v>680</v>
-      </c>
-      <c r="D13" s="40">
-        <v>44197</v>
-      </c>
-      <c r="E13" s="45">
+        <v>678</v>
+      </c>
+      <c r="D13" s="39">
+        <v>42005</v>
+      </c>
+      <c r="E13" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>5.5</v>
-      </c>
-      <c r="G13" s="43" t="s">
-        <v>671</v>
-      </c>
-      <c r="H13" s="39">
-        <v>6.8</v>
+        <v>11.5</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>638</v>
+      </c>
+      <c r="H13" s="44">
+        <v>1.5</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B14" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C14" t="s">
-        <v>681</v>
-      </c>
-      <c r="D14" s="40">
-        <v>45292</v>
-      </c>
-      <c r="E14" s="45">
+        <v>677</v>
+      </c>
+      <c r="D14" s="39">
+        <v>44197</v>
+      </c>
+      <c r="E14" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>2.5</v>
-      </c>
-      <c r="G14" s="43" t="s">
-        <v>673</v>
-      </c>
-      <c r="H14" s="39">
-        <v>5.8</v>
+        <v>5.5</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>641</v>
+      </c>
+      <c r="H14" s="44">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B15" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C15" t="s">
-        <v>682</v>
-      </c>
-      <c r="D15" s="40">
-        <v>46023</v>
-      </c>
-      <c r="E15" s="45">
+        <v>678</v>
+      </c>
+      <c r="D15" s="39">
+        <v>45292</v>
+      </c>
+      <c r="E15" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="43" t="s">
-        <v>675</v>
-      </c>
-      <c r="H15" s="39">
-        <v>0.79999999999999993</v>
+        <v>2.5</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>689</v>
+      </c>
+      <c r="H15" s="44">
+        <v>1.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B16" t="s">
+        <v>667</v>
+      </c>
+      <c r="C16" t="s">
+        <v>679</v>
+      </c>
+      <c r="D16" s="39">
+        <v>46023</v>
+      </c>
+      <c r="E16" s="44">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="42" t="s">
         <v>676</v>
       </c>
-      <c r="C16" t="s">
-        <v>680</v>
-      </c>
-      <c r="D16" s="40">
-        <v>45292</v>
-      </c>
-      <c r="E16" s="45">
-        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>2.5</v>
-      </c>
-      <c r="G16" s="43" t="s">
-        <v>674</v>
-      </c>
-      <c r="H16" s="39">
-        <v>0.79999999999999993</v>
+      <c r="H16" s="44">
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B17" t="s">
+        <v>673</v>
+      </c>
+      <c r="C17" t="s">
         <v>677</v>
       </c>
-      <c r="C17" t="s">
-        <v>682</v>
-      </c>
-      <c r="D17" s="40">
+      <c r="D17" s="39">
         <v>45292</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
         <v>2.5</v>
       </c>
-      <c r="G17" s="42" t="s">
-        <v>663</v>
-      </c>
-      <c r="H17" s="39">
-        <v>22.900000000000002</v>
+      <c r="G17" s="41" t="s">
+        <v>659</v>
+      </c>
+      <c r="H17" s="44">
+        <v>36.5</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="B18" t="s">
+        <v>674</v>
+      </c>
+      <c r="C18" t="s">
         <v>679</v>
       </c>
-      <c r="C18" t="s">
-        <v>682</v>
-      </c>
-      <c r="D18" s="40">
-        <v>46023</v>
-      </c>
-      <c r="E18" s="45">
+      <c r="D18" s="39">
+        <v>45292</v>
+      </c>
+      <c r="E18" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>0.5</v>
-      </c>
-      <c r="G18" s="43" t="s">
-        <v>649</v>
-      </c>
-      <c r="H18" s="39">
-        <v>11.1</v>
+        <v>2.5</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>653</v>
+      </c>
+      <c r="H18" s="44">
+        <v>11.5</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>663</v>
+        <v>641</v>
       </c>
       <c r="B19" t="s">
-        <v>649</v>
+        <v>676</v>
       </c>
       <c r="C19" t="s">
-        <v>681</v>
-      </c>
-      <c r="D19" s="40">
-        <v>42156</v>
-      </c>
-      <c r="E19" s="45">
+        <v>679</v>
+      </c>
+      <c r="D19" s="39">
+        <v>46023</v>
+      </c>
+      <c r="E19" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>11.1</v>
-      </c>
-      <c r="G19" s="43" t="s">
-        <v>650</v>
-      </c>
-      <c r="H19" s="39">
-        <v>5.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>652</v>
+      </c>
+      <c r="H19" s="44">
+        <v>11.5</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>663</v>
+        <v>641</v>
       </c>
       <c r="B20" t="s">
-        <v>650</v>
+        <v>689</v>
       </c>
       <c r="C20" t="s">
-        <v>681</v>
-      </c>
-      <c r="D20" s="40">
-        <v>44075</v>
-      </c>
-      <c r="E20" s="45">
+        <v>677</v>
+      </c>
+      <c r="D20" s="39">
+        <v>45658</v>
+      </c>
+      <c r="E20" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>5.8</v>
-      </c>
-      <c r="G20" s="43" t="s">
-        <v>647</v>
-      </c>
-      <c r="H20" s="39">
-        <v>4.5</v>
+        <v>1.5</v>
+      </c>
+      <c r="G20" s="42" t="s">
+        <v>665</v>
+      </c>
+      <c r="H20" s="44">
+        <v>5.5</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B21" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C21" t="s">
-        <v>683</v>
-      </c>
-      <c r="D21" s="40">
-        <v>44562</v>
-      </c>
-      <c r="E21" s="45">
+        <v>678</v>
+      </c>
+      <c r="D21" s="39">
+        <v>42156</v>
+      </c>
+      <c r="E21" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>4.5</v>
-      </c>
-      <c r="G21" s="43" t="s">
-        <v>640</v>
-      </c>
-      <c r="H21" s="39">
-        <v>1.5</v>
+        <v>11.1</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>673</v>
+      </c>
+      <c r="H21" s="44">
+        <v>2.5</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B22" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="C22" t="s">
-        <v>682</v>
-      </c>
-      <c r="D22" s="40">
-        <v>45658</v>
-      </c>
-      <c r="E22" s="45">
+        <v>678</v>
+      </c>
+      <c r="D22" s="39">
+        <v>44075</v>
+      </c>
+      <c r="E22" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="G22" s="42" t="s">
-        <v>651</v>
-      </c>
-      <c r="H22" s="39">
-        <v>15.8</v>
+        <v>674</v>
+      </c>
+      <c r="H22" s="44">
+        <v>2.5</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>641</v>
+        <v>660</v>
       </c>
       <c r="B23" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C23" t="s">
-        <v>681</v>
-      </c>
-      <c r="D23" s="40">
-        <v>45292</v>
-      </c>
-      <c r="E23" s="45">
+        <v>680</v>
+      </c>
+      <c r="D23" s="39">
+        <v>44562</v>
+      </c>
+      <c r="E23" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>4.5</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>666</v>
+      </c>
+      <c r="H23" s="44">
         <v>2.5</v>
-      </c>
-      <c r="G23" s="43" t="s">
-        <v>652</v>
-      </c>
-      <c r="H23" s="39">
-        <v>5.8</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>641</v>
+        <v>660</v>
       </c>
       <c r="B24" t="s">
-        <v>665</v>
+        <v>638</v>
       </c>
       <c r="C24" t="s">
-        <v>680</v>
-      </c>
-      <c r="D24" s="40">
-        <v>44927</v>
-      </c>
-      <c r="E24" s="45">
+        <v>679</v>
+      </c>
+      <c r="D24" s="39">
+        <v>45658</v>
+      </c>
+      <c r="E24" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>3.5</v>
-      </c>
-      <c r="G24" s="43" t="s">
-        <v>653</v>
-      </c>
-      <c r="H24" s="39">
-        <v>5.5</v>
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="42" t="s">
+        <v>667</v>
+      </c>
+      <c r="H24" s="44">
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B25" t="s">
-        <v>666</v>
+        <v>640</v>
       </c>
       <c r="C25" t="s">
-        <v>682</v>
-      </c>
-      <c r="D25" s="40">
-        <v>46023</v>
-      </c>
-      <c r="E25" s="45">
+        <v>678</v>
+      </c>
+      <c r="D25" s="39">
+        <v>45292</v>
+      </c>
+      <c r="E25" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>0.5</v>
-      </c>
-      <c r="G25" s="43" t="s">
-        <v>654</v>
-      </c>
-      <c r="H25" s="39">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="G25" s="41" t="s">
+        <v>648</v>
+      </c>
+      <c r="H25" s="44">
+        <v>15.8</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B26" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C26" t="s">
-        <v>681</v>
-      </c>
-      <c r="D26" s="40">
-        <v>44562</v>
-      </c>
-      <c r="E26" s="45">
+        <v>677</v>
+      </c>
+      <c r="D26" s="39">
+        <v>44927</v>
+      </c>
+      <c r="E26" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G26" s="42" t="s">
-        <v>641</v>
-      </c>
-      <c r="H26" s="39">
-        <v>14</v>
+        <v>649</v>
+      </c>
+      <c r="H26" s="44">
+        <v>5.8</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B27" t="s">
-        <v>685</v>
+        <v>663</v>
       </c>
       <c r="C27" t="s">
-        <v>680</v>
-      </c>
-      <c r="D27" s="40">
-        <v>45658</v>
-      </c>
-      <c r="E27" s="45">
+        <v>679</v>
+      </c>
+      <c r="D27" s="39">
+        <v>46023</v>
+      </c>
+      <c r="E27" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
-        <v>1.5</v>
-      </c>
-      <c r="G27" s="43" t="s">
-        <v>667</v>
-      </c>
-      <c r="H27" s="39">
-        <v>4.5</v>
+        <v>0.5</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>650</v>
+      </c>
+      <c r="H27" s="44">
+        <v>5.5</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B28" t="s">
-        <v>686</v>
+        <v>664</v>
       </c>
       <c r="C28" t="s">
-        <v>680</v>
-      </c>
-      <c r="D28" s="40">
+        <v>678</v>
+      </c>
+      <c r="D28" s="39">
+        <v>44562</v>
+      </c>
+      <c r="E28" s="44">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
+        <v>4.5</v>
+      </c>
+      <c r="G28" s="42" t="s">
+        <v>651</v>
+      </c>
+      <c r="H28" s="44">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>639</v>
+      </c>
+      <c r="B29" t="s">
+        <v>682</v>
+      </c>
+      <c r="C29" t="s">
+        <v>677</v>
+      </c>
+      <c r="D29" s="39">
         <v>45658</v>
       </c>
-      <c r="E28" s="45">
+      <c r="E29" s="44">
         <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
         <v>1.5</v>
       </c>
-      <c r="G28" s="43" t="s">
-        <v>665</v>
-      </c>
-      <c r="H28" s="39">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G29" s="43" t="s">
-        <v>642</v>
-      </c>
-      <c r="H29" s="39">
-        <v>2.5</v>
+      <c r="G29" s="41" t="s">
+        <v>661</v>
+      </c>
+      <c r="H29" s="44">
+        <v>32.299999999999997</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G30" s="43" t="s">
-        <v>685</v>
-      </c>
-      <c r="H30" s="39">
+      <c r="A30" t="s">
+        <v>639</v>
+      </c>
+      <c r="B30" t="s">
+        <v>683</v>
+      </c>
+      <c r="C30" t="s">
+        <v>677</v>
+      </c>
+      <c r="D30" s="39">
+        <v>45658</v>
+      </c>
+      <c r="E30" s="44">
+        <f ca="1">ROUNDUP((NOW()-Table2[[#This Row],[Start]])/365,1)</f>
         <v>1.5</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>645</v>
+      </c>
+      <c r="H30" s="44">
+        <v>7.8</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G31" s="43" t="s">
-        <v>686</v>
-      </c>
-      <c r="H31" s="39">
-        <v>1.5</v>
+      <c r="G31" s="42" t="s">
+        <v>669</v>
+      </c>
+      <c r="H31" s="44">
+        <v>6.8</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G32" s="43" t="s">
-        <v>666</v>
-      </c>
-      <c r="H32" s="39">
-        <v>0.5</v>
+      <c r="G32" s="42" t="s">
+        <v>668</v>
+      </c>
+      <c r="H32" s="44">
+        <v>6.8</v>
       </c>
     </row>
     <row r="33" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G33" s="42" t="s">
-        <v>643</v>
-      </c>
-      <c r="H33" s="39">
-        <v>0.5</v>
+        <v>670</v>
+      </c>
+      <c r="H33" s="44">
+        <v>5.8</v>
       </c>
     </row>
     <row r="34" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G34" s="43" t="s">
-        <v>679</v>
-      </c>
-      <c r="H34" s="39">
-        <v>0.5</v>
+      <c r="G34" s="42" t="s">
+        <v>688</v>
+      </c>
+      <c r="H34" s="44">
+        <v>3.5</v>
       </c>
     </row>
     <row r="35" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G35" s="42" t="s">
-        <v>645</v>
-      </c>
-      <c r="H35" s="39">
-        <v>121.09999999999998</v>
+        <v>672</v>
+      </c>
+      <c r="H35" s="44">
+        <v>0.79999999999999993</v>
+      </c>
+    </row>
+    <row r="36" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G36" s="42" t="s">
+        <v>671</v>
+      </c>
+      <c r="H36" s="44">
+        <v>0.79999999999999993</v>
+      </c>
+    </row>
+    <row r="37" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G37" s="41" t="s">
+        <v>642</v>
+      </c>
+      <c r="H37" s="44">
+        <v>123.49999999999999</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C28" xr:uid="{E4AEB1FF-66B5-4FE5-B190-7572A8D46C61}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C30" xr:uid="{E4AEB1FF-66B5-4FE5-B190-7572A8D46C61}">
       <formula1>"Learning,Intermediate,Advanced,Expert,Instructor"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15268,16 +15409,16 @@
         <v>0</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>5</v>
@@ -15286,16 +15427,16 @@
         <v>30</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M1" s="10" t="s">
         <v>13</v>
@@ -15306,10 +15447,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>46</v>
@@ -15336,7 +15477,7 @@
         <v>182</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>181</v>
@@ -15353,7 +15494,7 @@
         <v>94</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>184</v>
@@ -15374,13 +15515,13 @@
         <v>92</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J3" s="13" t="s">
         <v>184</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L3" s="13" t="s">
         <v>185</v>
@@ -15397,7 +15538,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>184</v>
@@ -15415,7 +15556,7 @@
         <v>176</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I4" s="13"/>
       <c r="J4" s="13" t="s">
@@ -15437,7 +15578,7 @@
         <v>77</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>184</v>
@@ -15447,7 +15588,7 @@
         <v>184</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G5" s="13" t="s">
         <v>216</v>
@@ -15461,7 +15602,7 @@
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M5" s="14" t="s">
         <v>178</v>
@@ -15553,7 +15694,7 @@
         <v>140</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>184</v>
@@ -15671,7 +15812,7 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="36"/>
       <c r="B11" s="16" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
@@ -15689,7 +15830,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="36"/>
       <c r="B12" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
